--- a/정보통신사업부 견적서 양식_ver2.xlsx
+++ b/정보통신사업부 견적서 양식_ver2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Master\Documents\Project\견적서 자동화 프로젝트\정보통신사업부\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Master\Documents\Project\견적서 자동화 프로젝트\정보통신사업부\.claude\worktrees\blissful-kalam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC5B3846-3825-46DC-AC28-CA86B28189C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65C6B104-CBEC-43D0-832E-EF307D08EDB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="854" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="854" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VXXXXX" sheetId="6" state="veryHidden" r:id="rId1"/>
@@ -8365,7 +8365,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="670">
+  <cellXfs count="673">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -9349,6 +9349,72 @@
     <xf numFmtId="231" fontId="133" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="129" fillId="31" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="31" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="178" fontId="116" fillId="32" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="116" fillId="32" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="116" fillId="32" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="163" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="163" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="108" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="108" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="108" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="108" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="108" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="108" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="108" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -9358,6 +9424,228 @@
     <xf numFmtId="0" fontId="108" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="32" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="32" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="117" fillId="31" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="117" fillId="31" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="117" fillId="31" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="31" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="31" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="31" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="32" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="30" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="30" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="30" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="118" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="118" fillId="0" borderId="0" xfId="1267" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="32" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="32" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="32" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="32" borderId="161" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="32" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="32" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="231" fontId="108" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="231" fontId="108" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="31" fontId="116" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="31" fontId="116" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="32" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="32" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="31" fontId="108" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="31" fontId="112" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="32" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="32" borderId="162" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="165" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="232" fontId="116" fillId="29" borderId="31" xfId="1267" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="130" fillId="31" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="32" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="32" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="130" fillId="31" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="130" fillId="31" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="130" fillId="31" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="31" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="31" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="178" fontId="128" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
@@ -9385,72 +9673,6 @@
     <xf numFmtId="178" fontId="116" fillId="32" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="108" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="108" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="108" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="232" fontId="116" fillId="29" borderId="31" xfId="1267" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="130" fillId="31" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="32" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="32" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="130" fillId="31" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="130" fillId="31" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="130" fillId="31" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="32" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="32" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="178" fontId="128" fillId="0" borderId="35" xfId="1267" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -9484,246 +9706,177 @@
     <xf numFmtId="178" fontId="108" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="31" fontId="116" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="31" fontId="116" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="31" fontId="108" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="31" fontId="112" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="32" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="32" borderId="162" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="163" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="165" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="32" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="32" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="32" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="32" borderId="161" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="32" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="32" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="231" fontId="108" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="231" fontId="108" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="116" fillId="30" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="116" fillId="30" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="116" fillId="30" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="118" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="118" fillId="0" borderId="0" xfId="1267" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="116" fillId="32" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="116" fillId="32" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="117" fillId="31" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="117" fillId="31" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="117" fillId="31" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="31" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="31" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="31" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="116" fillId="32" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="129" fillId="31" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="129" fillId="31" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="129" fillId="31" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="129" fillId="31" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="178" fontId="116" fillId="32" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="116" fillId="32" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="116" fillId="32" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="163" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="164" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="166" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="108" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="108" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="108" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="126" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="126" fillId="0" borderId="168" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="127" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="128" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="129" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="126" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="126" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="125" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="125" fillId="0" borderId="168" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="126" fillId="0" borderId="33" xfId="1267" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="126" fillId="0" borderId="168" xfId="1267" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="229" fontId="123" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="229" fontId="123" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="126" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="126" fillId="0" borderId="168" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="140" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="141" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="142" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="143" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="141" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="28" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="28" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="28" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="125" fillId="28" borderId="177" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="125" fillId="28" borderId="178" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="32" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="32" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="134" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="129" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="124" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="139" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="132" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="127" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="128" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="129" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="32" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="32" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="125" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="130" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="124" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="131" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="132" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="229" fontId="123" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -9748,12 +9901,6 @@
     <xf numFmtId="178" fontId="125" fillId="28" borderId="167" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="126" fillId="0" borderId="33" xfId="1267" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="126" fillId="0" borderId="168" xfId="1267" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="136" fillId="28" borderId="170" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -9772,157 +9919,40 @@
     <xf numFmtId="0" fontId="125" fillId="0" borderId="168" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="229" fontId="123" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="126" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="126" fillId="0" borderId="168" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="140" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="141" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="142" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="143" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="141" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="28" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="28" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="28" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="125" fillId="28" borderId="177" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="125" fillId="28" borderId="178" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="32" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="32" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="134" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="129" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="124" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="139" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="132" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="127" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="128" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="129" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="32" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="32" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="125" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="130" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="124" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="131" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="132" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="126" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="126" fillId="0" borderId="168" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="127" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="128" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="129" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="125" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="125" fillId="0" borderId="168" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="125" fillId="37" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="125" fillId="37" borderId="169" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="37" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="37" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="37" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="37" borderId="171" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="37" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="37" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="229" fontId="126" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="229" fontId="126" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="229" fontId="123" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="229" fontId="123" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="136" fillId="37" borderId="170" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -9946,12 +9976,6 @@
     <xf numFmtId="178" fontId="125" fillId="37" borderId="167" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="229" fontId="123" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="229" fontId="123" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="126" fillId="29" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -9961,35 +9985,86 @@
     <xf numFmtId="0" fontId="126" fillId="29" borderId="168" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="37" borderId="171" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="130" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="124" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="140" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="143" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="141" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="148" fillId="32" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="148" fillId="32" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="127" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="129" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="125" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="124" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="142" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="141" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="148" fillId="32" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="148" fillId="32" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="134" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="128" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="129" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="34" borderId="171" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="37" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="123" fillId="34" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="37" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="123" fillId="34" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="229" fontId="126" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="229" fontId="126" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="125" fillId="37" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="125" fillId="37" borderId="169" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="37" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="37" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="37" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="137" fillId="34" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="34" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="34" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="125" fillId="34" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="125" fillId="34" borderId="169" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="136" fillId="34" borderId="170" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -10006,103 +10081,58 @@
     <xf numFmtId="178" fontId="125" fillId="34" borderId="167" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="137" fillId="34" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="34" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="34" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="125" fillId="34" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="125" fillId="34" borderId="169" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="34" borderId="171" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="34" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="34" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="130" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="124" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="140" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="143" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="141" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="148" fillId="32" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="148" fillId="32" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="127" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="142" fillId="0" borderId="101" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="142" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="142" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="129" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="125" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="124" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="142" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="141" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="148" fillId="32" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="148" fillId="32" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="134" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="128" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="129" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="34" borderId="99" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="34" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="34" borderId="100" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="34" borderId="101" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="34" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="34" borderId="93" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="122" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10123,6 +10153,54 @@
     <xf numFmtId="0" fontId="122" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="101" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="101" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="34" borderId="99" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="34" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="34" borderId="100" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="34" borderId="101" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="34" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="34" borderId="93" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="122" fillId="0" borderId="101" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -10159,103 +10237,19 @@
     <xf numFmtId="41" fontId="141" fillId="0" borderId="93" xfId="1267" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="101" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="142" fillId="0" borderId="101" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="142" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="142" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="101" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="153" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="152" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="152" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="152" fillId="0" borderId="106" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="152" fillId="0" borderId="153" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="152" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="152" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="158" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -10298,6 +10292,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="167" fillId="35" borderId="28" xfId="1267" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="164" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="166" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="162" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="165" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -14957,11 +14966,11 @@
       </c>
     </row>
     <row r="9" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="656"/>
-      <c r="B9" s="656"/>
-      <c r="C9" s="656"/>
-      <c r="D9" s="656"/>
-      <c r="E9" s="656"/>
+      <c r="A9" s="654"/>
+      <c r="B9" s="654"/>
+      <c r="C9" s="654"/>
+      <c r="D9" s="654"/>
+      <c r="E9" s="654"/>
       <c r="F9" s="234">
         <f>SUM(F2:F8)</f>
         <v>70200000</v>
@@ -15014,39 +15023,39 @@
       <c r="L1" s="259"/>
     </row>
     <row r="2" spans="1:14" s="249" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A2" s="659" t="s">
+      <c r="A2" s="657" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="661" t="s">
+      <c r="B2" s="659" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="663" t="s">
+      <c r="C2" s="661" t="s">
         <v>78</v>
       </c>
-      <c r="D2" s="659" t="s">
+      <c r="D2" s="657" t="s">
         <v>84</v>
       </c>
-      <c r="E2" s="665"/>
-      <c r="F2" s="666" t="s">
+      <c r="E2" s="663"/>
+      <c r="F2" s="664" t="s">
         <v>82</v>
       </c>
-      <c r="G2" s="663"/>
-      <c r="H2" s="667" t="s">
+      <c r="G2" s="661"/>
+      <c r="H2" s="665" t="s">
         <v>87</v>
       </c>
-      <c r="I2" s="668"/>
-      <c r="J2" s="669"/>
-      <c r="K2" s="657" t="s">
+      <c r="I2" s="666"/>
+      <c r="J2" s="667"/>
+      <c r="K2" s="655" t="s">
         <v>259</v>
       </c>
-      <c r="L2" s="657" t="s">
+      <c r="L2" s="655" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:14" s="249" customFormat="1" ht="22.5" customHeight="1" thickBot="1">
-      <c r="A3" s="660"/>
-      <c r="B3" s="662"/>
-      <c r="C3" s="664"/>
+      <c r="A3" s="658"/>
+      <c r="B3" s="660"/>
+      <c r="C3" s="662"/>
       <c r="D3" s="250" t="s">
         <v>83</v>
       </c>
@@ -15068,8 +15077,8 @@
       <c r="J3" s="256" t="s">
         <v>86</v>
       </c>
-      <c r="K3" s="658"/>
-      <c r="L3" s="658"/>
+      <c r="K3" s="656"/>
+      <c r="L3" s="656"/>
     </row>
     <row r="4" spans="1:14" s="249" customFormat="1" ht="22.5" customHeight="1">
       <c r="A4" s="263" t="s">
@@ -15345,40 +15354,40 @@
       <c r="N11" s="262"/>
     </row>
     <row r="12" spans="1:14" s="249" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A12" s="659" t="s">
+      <c r="A12" s="657" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="661" t="s">
+      <c r="B12" s="659" t="s">
         <v>90</v>
       </c>
-      <c r="C12" s="663" t="s">
+      <c r="C12" s="661" t="s">
         <v>78</v>
       </c>
-      <c r="D12" s="659" t="s">
+      <c r="D12" s="657" t="s">
         <v>84</v>
       </c>
-      <c r="E12" s="665"/>
-      <c r="F12" s="666" t="s">
+      <c r="E12" s="663"/>
+      <c r="F12" s="664" t="s">
         <v>82</v>
       </c>
-      <c r="G12" s="663"/>
-      <c r="H12" s="667" t="s">
+      <c r="G12" s="661"/>
+      <c r="H12" s="665" t="s">
         <v>87</v>
       </c>
-      <c r="I12" s="668"/>
-      <c r="J12" s="669"/>
-      <c r="K12" s="657" t="s">
+      <c r="I12" s="666"/>
+      <c r="J12" s="667"/>
+      <c r="K12" s="655" t="s">
         <v>259</v>
       </c>
-      <c r="L12" s="657" t="s">
+      <c r="L12" s="655" t="s">
         <v>258</v>
       </c>
       <c r="N12" s="257"/>
     </row>
     <row r="13" spans="1:14" s="249" customFormat="1" ht="22.5" customHeight="1" thickBot="1">
-      <c r="A13" s="660"/>
-      <c r="B13" s="662"/>
-      <c r="C13" s="664"/>
+      <c r="A13" s="658"/>
+      <c r="B13" s="660"/>
+      <c r="C13" s="662"/>
       <c r="D13" s="250" t="s">
         <v>83</v>
       </c>
@@ -15400,8 +15409,8 @@
       <c r="J13" s="256" t="s">
         <v>86</v>
       </c>
-      <c r="K13" s="658"/>
-      <c r="L13" s="658"/>
+      <c r="K13" s="656"/>
+      <c r="L13" s="656"/>
       <c r="N13" s="257"/>
     </row>
     <row r="14" spans="1:14" s="249" customFormat="1" ht="22.5" customHeight="1">
@@ -16158,68 +16167,68 @@
       <c r="AB1" s="3"/>
     </row>
     <row r="2" spans="1:28" s="6" customFormat="1" ht="48.75">
-      <c r="A2" s="417" t="s">
+      <c r="A2" s="397" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="418"/>
-      <c r="C2" s="418"/>
-      <c r="D2" s="418"/>
-      <c r="E2" s="418"/>
-      <c r="F2" s="418"/>
-      <c r="G2" s="418"/>
-      <c r="H2" s="418"/>
-      <c r="I2" s="418"/>
-      <c r="J2" s="418"/>
-      <c r="K2" s="418"/>
-      <c r="L2" s="418"/>
-      <c r="M2" s="418"/>
-      <c r="N2" s="418"/>
-      <c r="O2" s="418"/>
-      <c r="P2" s="418"/>
-      <c r="Q2" s="418"/>
-      <c r="R2" s="418"/>
-      <c r="S2" s="418"/>
-      <c r="T2" s="418"/>
-      <c r="U2" s="418"/>
-      <c r="V2" s="418"/>
-      <c r="W2" s="418"/>
-      <c r="X2" s="418"/>
-      <c r="Y2" s="418"/>
-      <c r="Z2" s="418"/>
-      <c r="AA2" s="418"/>
+      <c r="B2" s="398"/>
+      <c r="C2" s="398"/>
+      <c r="D2" s="398"/>
+      <c r="E2" s="398"/>
+      <c r="F2" s="398"/>
+      <c r="G2" s="398"/>
+      <c r="H2" s="398"/>
+      <c r="I2" s="398"/>
+      <c r="J2" s="398"/>
+      <c r="K2" s="398"/>
+      <c r="L2" s="398"/>
+      <c r="M2" s="398"/>
+      <c r="N2" s="398"/>
+      <c r="O2" s="398"/>
+      <c r="P2" s="398"/>
+      <c r="Q2" s="398"/>
+      <c r="R2" s="398"/>
+      <c r="S2" s="398"/>
+      <c r="T2" s="398"/>
+      <c r="U2" s="398"/>
+      <c r="V2" s="398"/>
+      <c r="W2" s="398"/>
+      <c r="X2" s="398"/>
+      <c r="Y2" s="398"/>
+      <c r="Z2" s="398"/>
+      <c r="AA2" s="398"/>
       <c r="AB2" s="5"/>
     </row>
     <row r="3" spans="1:28" s="6" customFormat="1" ht="39.75" customHeight="1">
-      <c r="A3" s="421" t="s">
+      <c r="A3" s="402" t="s">
         <v>285</v>
       </c>
-      <c r="B3" s="422"/>
-      <c r="C3" s="422"/>
-      <c r="D3" s="422"/>
-      <c r="E3" s="422"/>
-      <c r="F3" s="422"/>
-      <c r="G3" s="422"/>
-      <c r="H3" s="422"/>
-      <c r="I3" s="422"/>
-      <c r="J3" s="422"/>
-      <c r="K3" s="422"/>
-      <c r="L3" s="422"/>
-      <c r="M3" s="422"/>
-      <c r="N3" s="422"/>
-      <c r="O3" s="422"/>
-      <c r="P3" s="422"/>
-      <c r="Q3" s="422"/>
-      <c r="R3" s="422"/>
-      <c r="S3" s="422"/>
-      <c r="T3" s="422"/>
-      <c r="U3" s="422"/>
-      <c r="V3" s="422"/>
-      <c r="W3" s="422"/>
-      <c r="X3" s="422"/>
-      <c r="Y3" s="422"/>
-      <c r="Z3" s="422"/>
-      <c r="AA3" s="422"/>
-      <c r="AB3" s="423"/>
+      <c r="B3" s="403"/>
+      <c r="C3" s="403"/>
+      <c r="D3" s="403"/>
+      <c r="E3" s="403"/>
+      <c r="F3" s="403"/>
+      <c r="G3" s="403"/>
+      <c r="H3" s="403"/>
+      <c r="I3" s="403"/>
+      <c r="J3" s="403"/>
+      <c r="K3" s="403"/>
+      <c r="L3" s="403"/>
+      <c r="M3" s="403"/>
+      <c r="N3" s="403"/>
+      <c r="O3" s="403"/>
+      <c r="P3" s="403"/>
+      <c r="Q3" s="403"/>
+      <c r="R3" s="403"/>
+      <c r="S3" s="403"/>
+      <c r="T3" s="403"/>
+      <c r="U3" s="403"/>
+      <c r="V3" s="403"/>
+      <c r="W3" s="403"/>
+      <c r="X3" s="403"/>
+      <c r="Y3" s="403"/>
+      <c r="Z3" s="403"/>
+      <c r="AA3" s="403"/>
+      <c r="AB3" s="404"/>
     </row>
     <row r="4" spans="1:28" s="6" customFormat="1" ht="30" customHeight="1">
       <c r="A4" s="7"/>
@@ -16240,15 +16249,15 @@
       <c r="P4" s="8"/>
       <c r="Q4" s="8"/>
       <c r="R4" s="8"/>
-      <c r="S4" s="419"/>
-      <c r="T4" s="419"/>
-      <c r="U4" s="419"/>
-      <c r="V4" s="419"/>
-      <c r="W4" s="419"/>
-      <c r="X4" s="419"/>
-      <c r="Y4" s="419"/>
-      <c r="Z4" s="419"/>
-      <c r="AA4" s="419"/>
+      <c r="S4" s="399"/>
+      <c r="T4" s="399"/>
+      <c r="U4" s="399"/>
+      <c r="V4" s="399"/>
+      <c r="W4" s="399"/>
+      <c r="X4" s="399"/>
+      <c r="Y4" s="399"/>
+      <c r="Z4" s="399"/>
+      <c r="AA4" s="399"/>
       <c r="AB4" s="9"/>
     </row>
     <row r="5" spans="1:28" s="6" customFormat="1" ht="39.75" customHeight="1">
@@ -16345,38 +16354,38 @@
         <v>72</v>
       </c>
       <c r="D8" s="215"/>
-      <c r="E8" s="434">
+      <c r="E8" s="415">
         <f ca="1">TODAY()</f>
         <v>46104</v>
       </c>
-      <c r="F8" s="434"/>
-      <c r="G8" s="434"/>
-      <c r="H8" s="434"/>
-      <c r="I8" s="434"/>
-      <c r="J8" s="434"/>
-      <c r="K8" s="434"/>
-      <c r="L8" s="435"/>
-      <c r="M8" s="424" t="s">
+      <c r="F8" s="415"/>
+      <c r="G8" s="415"/>
+      <c r="H8" s="415"/>
+      <c r="I8" s="415"/>
+      <c r="J8" s="415"/>
+      <c r="K8" s="415"/>
+      <c r="L8" s="416"/>
+      <c r="M8" s="405" t="s">
         <v>29</v>
       </c>
-      <c r="N8" s="428" t="s">
+      <c r="N8" s="409" t="s">
         <v>70</v>
       </c>
-      <c r="O8" s="428"/>
-      <c r="P8" s="428"/>
-      <c r="Q8" s="429" t="s">
+      <c r="O8" s="409"/>
+      <c r="P8" s="409"/>
+      <c r="Q8" s="410" t="s">
         <v>71</v>
       </c>
-      <c r="R8" s="430"/>
-      <c r="S8" s="430"/>
-      <c r="T8" s="430"/>
-      <c r="U8" s="430"/>
-      <c r="V8" s="430"/>
-      <c r="W8" s="430"/>
-      <c r="X8" s="430"/>
-      <c r="Y8" s="430"/>
-      <c r="Z8" s="430"/>
-      <c r="AA8" s="431"/>
+      <c r="R8" s="411"/>
+      <c r="S8" s="411"/>
+      <c r="T8" s="411"/>
+      <c r="U8" s="411"/>
+      <c r="V8" s="411"/>
+      <c r="W8" s="411"/>
+      <c r="X8" s="411"/>
+      <c r="Y8" s="411"/>
+      <c r="Z8" s="411"/>
+      <c r="AA8" s="412"/>
       <c r="AB8" s="5"/>
     </row>
     <row r="9" spans="1:28" s="6" customFormat="1" ht="32.1" customHeight="1">
@@ -16394,29 +16403,29 @@
       <c r="J9" s="215"/>
       <c r="K9" s="215"/>
       <c r="L9" s="143"/>
-      <c r="M9" s="425"/>
-      <c r="N9" s="416" t="s">
+      <c r="M9" s="406"/>
+      <c r="N9" s="400" t="s">
         <v>24</v>
       </c>
-      <c r="O9" s="416"/>
-      <c r="P9" s="416"/>
-      <c r="Q9" s="420" t="s">
+      <c r="O9" s="400"/>
+      <c r="P9" s="400"/>
+      <c r="Q9" s="401" t="s">
         <v>66</v>
       </c>
-      <c r="R9" s="420"/>
-      <c r="S9" s="420"/>
-      <c r="T9" s="420"/>
-      <c r="U9" s="416" t="s">
+      <c r="R9" s="401"/>
+      <c r="S9" s="401"/>
+      <c r="T9" s="401"/>
+      <c r="U9" s="400" t="s">
         <v>25</v>
       </c>
-      <c r="V9" s="416"/>
-      <c r="W9" s="416"/>
-      <c r="X9" s="457" t="s">
+      <c r="V9" s="400"/>
+      <c r="W9" s="400"/>
+      <c r="X9" s="355" t="s">
         <v>67</v>
       </c>
-      <c r="Y9" s="457"/>
-      <c r="Z9" s="457"/>
-      <c r="AA9" s="458"/>
+      <c r="Y9" s="355"/>
+      <c r="Z9" s="355"/>
+      <c r="AA9" s="356"/>
       <c r="AB9" s="5"/>
     </row>
     <row r="10" spans="1:28" s="6" customFormat="1" ht="32.1" customHeight="1">
@@ -16426,35 +16435,35 @@
         <v>74</v>
       </c>
       <c r="D10" s="215"/>
-      <c r="E10" s="432" t="s">
+      <c r="E10" s="413" t="s">
         <v>209</v>
       </c>
-      <c r="F10" s="432"/>
-      <c r="G10" s="432"/>
-      <c r="H10" s="432"/>
-      <c r="I10" s="432"/>
-      <c r="J10" s="432"/>
-      <c r="K10" s="432"/>
-      <c r="L10" s="433"/>
-      <c r="M10" s="425"/>
-      <c r="N10" s="416" t="s">
+      <c r="F10" s="413"/>
+      <c r="G10" s="413"/>
+      <c r="H10" s="413"/>
+      <c r="I10" s="413"/>
+      <c r="J10" s="413"/>
+      <c r="K10" s="413"/>
+      <c r="L10" s="414"/>
+      <c r="M10" s="406"/>
+      <c r="N10" s="400" t="s">
         <v>26</v>
       </c>
-      <c r="O10" s="416"/>
-      <c r="P10" s="416"/>
-      <c r="Q10" s="420" t="s">
+      <c r="O10" s="400"/>
+      <c r="P10" s="400"/>
+      <c r="Q10" s="401" t="s">
         <v>68</v>
       </c>
-      <c r="R10" s="420"/>
-      <c r="S10" s="420"/>
-      <c r="T10" s="420"/>
-      <c r="U10" s="420"/>
-      <c r="V10" s="420"/>
-      <c r="W10" s="420"/>
-      <c r="X10" s="420"/>
-      <c r="Y10" s="420"/>
-      <c r="Z10" s="420"/>
-      <c r="AA10" s="436"/>
+      <c r="R10" s="401"/>
+      <c r="S10" s="401"/>
+      <c r="T10" s="401"/>
+      <c r="U10" s="401"/>
+      <c r="V10" s="401"/>
+      <c r="W10" s="401"/>
+      <c r="X10" s="401"/>
+      <c r="Y10" s="401"/>
+      <c r="Z10" s="401"/>
+      <c r="AA10" s="417"/>
       <c r="AB10" s="5"/>
     </row>
     <row r="11" spans="1:28" s="6" customFormat="1" ht="32.1" customHeight="1">
@@ -16465,38 +16474,38 @@
       </c>
       <c r="D11" s="217"/>
       <c r="E11" s="215"/>
-      <c r="F11" s="398" t="s">
+      <c r="F11" s="418" t="s">
         <v>107</v>
       </c>
-      <c r="G11" s="398"/>
-      <c r="H11" s="398"/>
-      <c r="I11" s="398"/>
-      <c r="J11" s="398"/>
-      <c r="K11" s="398"/>
-      <c r="L11" s="399"/>
-      <c r="M11" s="425"/>
-      <c r="N11" s="416" t="s">
+      <c r="G11" s="418"/>
+      <c r="H11" s="418"/>
+      <c r="I11" s="418"/>
+      <c r="J11" s="418"/>
+      <c r="K11" s="418"/>
+      <c r="L11" s="419"/>
+      <c r="M11" s="406"/>
+      <c r="N11" s="400" t="s">
         <v>27</v>
       </c>
-      <c r="O11" s="416"/>
-      <c r="P11" s="416"/>
-      <c r="Q11" s="420" t="s">
+      <c r="O11" s="400"/>
+      <c r="P11" s="400"/>
+      <c r="Q11" s="401" t="s">
         <v>28</v>
       </c>
-      <c r="R11" s="420"/>
-      <c r="S11" s="420"/>
-      <c r="T11" s="420"/>
-      <c r="U11" s="416" t="s">
+      <c r="R11" s="401"/>
+      <c r="S11" s="401"/>
+      <c r="T11" s="401"/>
+      <c r="U11" s="400" t="s">
         <v>18</v>
       </c>
-      <c r="V11" s="416"/>
-      <c r="W11" s="416"/>
-      <c r="X11" s="404" t="s">
+      <c r="V11" s="400"/>
+      <c r="W11" s="400"/>
+      <c r="X11" s="426" t="s">
         <v>69</v>
       </c>
-      <c r="Y11" s="404"/>
-      <c r="Z11" s="404"/>
-      <c r="AA11" s="405"/>
+      <c r="Y11" s="426"/>
+      <c r="Z11" s="426"/>
+      <c r="AA11" s="427"/>
       <c r="AB11" s="5"/>
     </row>
     <row r="12" spans="1:28" s="6" customFormat="1" ht="32.1" customHeight="1">
@@ -16512,27 +16521,27 @@
       <c r="J12" s="316"/>
       <c r="K12" s="316"/>
       <c r="L12" s="317"/>
-      <c r="M12" s="426"/>
-      <c r="N12" s="412" t="s">
+      <c r="M12" s="407"/>
+      <c r="N12" s="436" t="s">
         <v>50</v>
       </c>
-      <c r="O12" s="413"/>
-      <c r="P12" s="413"/>
-      <c r="Q12" s="462"/>
-      <c r="R12" s="413"/>
-      <c r="S12" s="413"/>
-      <c r="T12" s="463"/>
-      <c r="U12" s="416" t="s">
+      <c r="O12" s="361"/>
+      <c r="P12" s="361"/>
+      <c r="Q12" s="671"/>
+      <c r="R12" s="360"/>
+      <c r="S12" s="360"/>
+      <c r="T12" s="668"/>
+      <c r="U12" s="400" t="s">
         <v>283</v>
       </c>
-      <c r="V12" s="416"/>
-      <c r="W12" s="416"/>
-      <c r="X12" s="404" t="s">
+      <c r="V12" s="400"/>
+      <c r="W12" s="400"/>
+      <c r="X12" s="426" t="s">
         <v>284</v>
       </c>
-      <c r="Y12" s="404"/>
-      <c r="Z12" s="404"/>
-      <c r="AA12" s="405"/>
+      <c r="Y12" s="426"/>
+      <c r="Z12" s="426"/>
+      <c r="AA12" s="427"/>
       <c r="AB12" s="5"/>
     </row>
     <row r="13" spans="1:28" s="6" customFormat="1" ht="32.1" customHeight="1" thickBot="1">
@@ -16540,35 +16549,35 @@
         <v>49</v>
       </c>
       <c r="B13" s="216"/>
-      <c r="C13" s="366" t="s">
+      <c r="C13" s="432" t="s">
         <v>108</v>
       </c>
-      <c r="D13" s="366"/>
-      <c r="E13" s="366"/>
-      <c r="F13" s="366"/>
-      <c r="G13" s="366"/>
-      <c r="H13" s="366"/>
-      <c r="I13" s="366"/>
-      <c r="J13" s="366"/>
-      <c r="K13" s="366"/>
-      <c r="L13" s="409"/>
-      <c r="M13" s="427"/>
-      <c r="N13" s="414"/>
-      <c r="O13" s="415"/>
-      <c r="P13" s="415"/>
-      <c r="Q13" s="415"/>
-      <c r="R13" s="415"/>
-      <c r="S13" s="415"/>
-      <c r="T13" s="464"/>
-      <c r="U13" s="411" t="s">
+      <c r="D13" s="432"/>
+      <c r="E13" s="432"/>
+      <c r="F13" s="432"/>
+      <c r="G13" s="432"/>
+      <c r="H13" s="432"/>
+      <c r="I13" s="432"/>
+      <c r="J13" s="432"/>
+      <c r="K13" s="432"/>
+      <c r="L13" s="433"/>
+      <c r="M13" s="408"/>
+      <c r="N13" s="437"/>
+      <c r="O13" s="362"/>
+      <c r="P13" s="362"/>
+      <c r="Q13" s="672"/>
+      <c r="R13" s="669"/>
+      <c r="S13" s="669"/>
+      <c r="T13" s="670"/>
+      <c r="U13" s="435" t="s">
         <v>51</v>
       </c>
-      <c r="V13" s="411"/>
-      <c r="W13" s="411"/>
-      <c r="X13" s="406"/>
-      <c r="Y13" s="407"/>
-      <c r="Z13" s="407"/>
-      <c r="AA13" s="408"/>
+      <c r="V13" s="435"/>
+      <c r="W13" s="435"/>
+      <c r="X13" s="428"/>
+      <c r="Y13" s="429"/>
+      <c r="Z13" s="429"/>
+      <c r="AA13" s="430"/>
       <c r="AB13" s="5"/>
     </row>
     <row r="14" spans="1:28" s="6" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -16579,41 +16588,41 @@
       <c r="C14" s="219"/>
       <c r="D14" s="217"/>
       <c r="E14" s="217"/>
-      <c r="F14" s="410"/>
-      <c r="G14" s="410"/>
-      <c r="H14" s="410"/>
-      <c r="I14" s="410"/>
-      <c r="J14" s="410"/>
+      <c r="F14" s="434"/>
+      <c r="G14" s="434"/>
+      <c r="H14" s="434"/>
+      <c r="I14" s="434"/>
+      <c r="J14" s="434"/>
       <c r="K14" s="220"/>
       <c r="L14" s="220"/>
       <c r="M14" s="12"/>
-      <c r="N14" s="403"/>
-      <c r="O14" s="403"/>
-      <c r="P14" s="403"/>
-      <c r="Q14" s="373"/>
-      <c r="R14" s="373"/>
-      <c r="S14" s="373"/>
-      <c r="T14" s="373"/>
-      <c r="U14" s="403"/>
-      <c r="V14" s="403"/>
-      <c r="W14" s="403"/>
-      <c r="X14" s="373"/>
-      <c r="Y14" s="373"/>
-      <c r="Z14" s="373"/>
-      <c r="AA14" s="373"/>
+      <c r="N14" s="425"/>
+      <c r="O14" s="425"/>
+      <c r="P14" s="425"/>
+      <c r="Q14" s="431"/>
+      <c r="R14" s="431"/>
+      <c r="S14" s="431"/>
+      <c r="T14" s="431"/>
+      <c r="U14" s="425"/>
+      <c r="V14" s="425"/>
+      <c r="W14" s="425"/>
+      <c r="X14" s="431"/>
+      <c r="Y14" s="431"/>
+      <c r="Z14" s="431"/>
+      <c r="AA14" s="431"/>
       <c r="AB14" s="5"/>
     </row>
     <row r="15" spans="1:28" s="6" customFormat="1" ht="35.1" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="221"/>
       <c r="C15" s="13"/>
-      <c r="D15" s="382" t="s">
+      <c r="D15" s="420" t="s">
         <v>75</v>
       </c>
-      <c r="E15" s="383"/>
-      <c r="F15" s="383"/>
-      <c r="G15" s="383"/>
-      <c r="H15" s="383"/>
+      <c r="E15" s="421"/>
+      <c r="F15" s="421"/>
+      <c r="G15" s="421"/>
+      <c r="H15" s="421"/>
       <c r="I15" s="14"/>
       <c r="J15" s="66">
         <f>E9</f>
@@ -16642,13 +16651,13 @@
       <c r="A16" s="16"/>
       <c r="B16" s="222"/>
       <c r="C16" s="13"/>
-      <c r="D16" s="382" t="s">
+      <c r="D16" s="420" t="s">
         <v>76</v>
       </c>
-      <c r="E16" s="383"/>
-      <c r="F16" s="383"/>
-      <c r="G16" s="383"/>
-      <c r="H16" s="383"/>
+      <c r="E16" s="421"/>
+      <c r="F16" s="421"/>
+      <c r="G16" s="421"/>
+      <c r="H16" s="421"/>
       <c r="I16" s="14"/>
       <c r="J16" s="65"/>
       <c r="K16" s="14"/>
@@ -16674,64 +16683,64 @@
       <c r="A17" s="16"/>
       <c r="B17" s="222"/>
       <c r="C17" s="13"/>
-      <c r="D17" s="382" t="s">
+      <c r="D17" s="420" t="s">
         <v>196</v>
       </c>
-      <c r="E17" s="383"/>
-      <c r="F17" s="383"/>
-      <c r="G17" s="383"/>
-      <c r="H17" s="383"/>
+      <c r="E17" s="421"/>
+      <c r="F17" s="421"/>
+      <c r="G17" s="421"/>
+      <c r="H17" s="421"/>
       <c r="I17" s="14"/>
-      <c r="J17" s="400"/>
-      <c r="K17" s="401"/>
-      <c r="L17" s="401"/>
-      <c r="M17" s="401"/>
-      <c r="N17" s="401"/>
-      <c r="O17" s="401"/>
-      <c r="P17" s="401"/>
-      <c r="Q17" s="401"/>
-      <c r="R17" s="401"/>
-      <c r="S17" s="401"/>
-      <c r="T17" s="401"/>
-      <c r="U17" s="401"/>
-      <c r="V17" s="401"/>
-      <c r="W17" s="401"/>
-      <c r="X17" s="401"/>
-      <c r="Y17" s="401"/>
-      <c r="Z17" s="401"/>
-      <c r="AA17" s="402"/>
+      <c r="J17" s="422"/>
+      <c r="K17" s="423"/>
+      <c r="L17" s="423"/>
+      <c r="M17" s="423"/>
+      <c r="N17" s="423"/>
+      <c r="O17" s="423"/>
+      <c r="P17" s="423"/>
+      <c r="Q17" s="423"/>
+      <c r="R17" s="423"/>
+      <c r="S17" s="423"/>
+      <c r="T17" s="423"/>
+      <c r="U17" s="423"/>
+      <c r="V17" s="423"/>
+      <c r="W17" s="423"/>
+      <c r="X17" s="423"/>
+      <c r="Y17" s="423"/>
+      <c r="Z17" s="423"/>
+      <c r="AA17" s="424"/>
       <c r="AB17" s="15"/>
     </row>
     <row r="18" spans="1:28" s="17" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A18" s="16"/>
       <c r="B18" s="222"/>
       <c r="C18" s="13"/>
-      <c r="D18" s="382" t="s">
+      <c r="D18" s="420" t="s">
         <v>195</v>
       </c>
-      <c r="E18" s="383"/>
-      <c r="F18" s="383"/>
-      <c r="G18" s="383"/>
-      <c r="H18" s="383"/>
+      <c r="E18" s="421"/>
+      <c r="F18" s="421"/>
+      <c r="G18" s="421"/>
+      <c r="H18" s="421"/>
       <c r="I18" s="14"/>
-      <c r="J18" s="386"/>
-      <c r="K18" s="386"/>
-      <c r="L18" s="386"/>
-      <c r="M18" s="386"/>
-      <c r="N18" s="386"/>
-      <c r="O18" s="386"/>
-      <c r="P18" s="386"/>
-      <c r="Q18" s="386"/>
-      <c r="R18" s="353" t="s">
+      <c r="J18" s="449"/>
+      <c r="K18" s="449"/>
+      <c r="L18" s="449"/>
+      <c r="M18" s="449"/>
+      <c r="N18" s="449"/>
+      <c r="O18" s="449"/>
+      <c r="P18" s="449"/>
+      <c r="Q18" s="449"/>
+      <c r="R18" s="375" t="s">
         <v>55</v>
       </c>
-      <c r="S18" s="354"/>
-      <c r="T18" s="354"/>
-      <c r="U18" s="354"/>
-      <c r="V18" s="355"/>
-      <c r="W18" s="374"/>
-      <c r="X18" s="374"/>
-      <c r="Y18" s="374"/>
+      <c r="S18" s="376"/>
+      <c r="T18" s="376"/>
+      <c r="U18" s="376"/>
+      <c r="V18" s="377"/>
+      <c r="W18" s="438"/>
+      <c r="X18" s="438"/>
+      <c r="Y18" s="438"/>
       <c r="Z18" s="247" t="s">
         <v>56</v>
       </c>
@@ -16742,68 +16751,68 @@
       <c r="A19" s="10"/>
       <c r="B19" s="221"/>
       <c r="C19" s="18"/>
-      <c r="D19" s="377" t="s">
+      <c r="D19" s="442" t="s">
         <v>194</v>
       </c>
-      <c r="E19" s="378"/>
-      <c r="F19" s="378"/>
-      <c r="G19" s="378"/>
-      <c r="H19" s="378"/>
+      <c r="E19" s="443"/>
+      <c r="F19" s="443"/>
+      <c r="G19" s="443"/>
+      <c r="H19" s="443"/>
       <c r="I19" s="19"/>
-      <c r="J19" s="386"/>
-      <c r="K19" s="386"/>
-      <c r="L19" s="386"/>
-      <c r="M19" s="386"/>
-      <c r="N19" s="386"/>
-      <c r="O19" s="386"/>
-      <c r="P19" s="386"/>
-      <c r="Q19" s="386"/>
-      <c r="R19" s="353" t="s">
+      <c r="J19" s="449"/>
+      <c r="K19" s="449"/>
+      <c r="L19" s="449"/>
+      <c r="M19" s="449"/>
+      <c r="N19" s="449"/>
+      <c r="O19" s="449"/>
+      <c r="P19" s="449"/>
+      <c r="Q19" s="449"/>
+      <c r="R19" s="375" t="s">
         <v>198</v>
       </c>
-      <c r="S19" s="354"/>
-      <c r="T19" s="354"/>
-      <c r="U19" s="354"/>
-      <c r="V19" s="355"/>
-      <c r="W19" s="471"/>
-      <c r="X19" s="472"/>
-      <c r="Y19" s="472"/>
-      <c r="Z19" s="472"/>
-      <c r="AA19" s="473"/>
+      <c r="S19" s="376"/>
+      <c r="T19" s="376"/>
+      <c r="U19" s="376"/>
+      <c r="V19" s="377"/>
+      <c r="W19" s="378"/>
+      <c r="X19" s="379"/>
+      <c r="Y19" s="379"/>
+      <c r="Z19" s="379"/>
+      <c r="AA19" s="380"/>
       <c r="AB19" s="15"/>
     </row>
     <row r="20" spans="1:28" s="6" customFormat="1" ht="35.1" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="221"/>
       <c r="C20" s="13"/>
-      <c r="D20" s="382" t="s">
+      <c r="D20" s="420" t="s">
         <v>197</v>
       </c>
-      <c r="E20" s="383"/>
-      <c r="F20" s="383"/>
-      <c r="G20" s="383"/>
-      <c r="H20" s="383"/>
+      <c r="E20" s="421"/>
+      <c r="F20" s="421"/>
+      <c r="G20" s="421"/>
+      <c r="H20" s="421"/>
       <c r="I20" s="14"/>
-      <c r="J20" s="384" t="s">
+      <c r="J20" s="447" t="s">
         <v>264</v>
       </c>
-      <c r="K20" s="384"/>
-      <c r="L20" s="384"/>
-      <c r="M20" s="384"/>
-      <c r="N20" s="384"/>
-      <c r="O20" s="384"/>
-      <c r="P20" s="384"/>
-      <c r="Q20" s="384"/>
-      <c r="R20" s="384"/>
-      <c r="S20" s="384"/>
-      <c r="T20" s="384"/>
-      <c r="U20" s="384"/>
-      <c r="V20" s="384"/>
-      <c r="W20" s="384"/>
-      <c r="X20" s="384"/>
-      <c r="Y20" s="384"/>
-      <c r="Z20" s="384"/>
-      <c r="AA20" s="385"/>
+      <c r="K20" s="447"/>
+      <c r="L20" s="447"/>
+      <c r="M20" s="447"/>
+      <c r="N20" s="447"/>
+      <c r="O20" s="447"/>
+      <c r="P20" s="447"/>
+      <c r="Q20" s="447"/>
+      <c r="R20" s="447"/>
+      <c r="S20" s="447"/>
+      <c r="T20" s="447"/>
+      <c r="U20" s="447"/>
+      <c r="V20" s="447"/>
+      <c r="W20" s="447"/>
+      <c r="X20" s="447"/>
+      <c r="Y20" s="447"/>
+      <c r="Z20" s="447"/>
+      <c r="AA20" s="448"/>
       <c r="AB20" s="15"/>
     </row>
     <row r="21" spans="1:28" s="6" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -16838,46 +16847,46 @@
     <row r="22" spans="1:28" s="23" customFormat="1" ht="47.1" customHeight="1">
       <c r="A22" s="20"/>
       <c r="B22" s="21"/>
-      <c r="C22" s="453" t="s">
+      <c r="C22" s="450" t="s">
         <v>287</v>
       </c>
-      <c r="D22" s="454"/>
-      <c r="E22" s="454"/>
-      <c r="F22" s="454"/>
-      <c r="G22" s="455" t="s">
+      <c r="D22" s="451"/>
+      <c r="E22" s="451"/>
+      <c r="F22" s="451"/>
+      <c r="G22" s="353" t="s">
         <v>288</v>
       </c>
-      <c r="H22" s="455"/>
-      <c r="I22" s="455"/>
-      <c r="J22" s="455"/>
-      <c r="K22" s="456"/>
-      <c r="L22" s="379" t="s">
+      <c r="H22" s="353"/>
+      <c r="I22" s="353"/>
+      <c r="J22" s="353"/>
+      <c r="K22" s="354"/>
+      <c r="L22" s="444" t="s">
         <v>19</v>
       </c>
-      <c r="M22" s="380"/>
-      <c r="N22" s="380"/>
-      <c r="O22" s="381">
+      <c r="M22" s="445"/>
+      <c r="N22" s="445"/>
+      <c r="O22" s="446">
         <f>V22</f>
         <v>0</v>
       </c>
-      <c r="P22" s="381"/>
-      <c r="Q22" s="381"/>
-      <c r="R22" s="381"/>
-      <c r="S22" s="381"/>
+      <c r="P22" s="446"/>
+      <c r="Q22" s="446"/>
+      <c r="R22" s="446"/>
+      <c r="S22" s="446"/>
       <c r="T22" s="69" t="s">
         <v>20</v>
       </c>
       <c r="U22" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="V22" s="376">
+      <c r="V22" s="441">
         <f>T28</f>
         <v>0</v>
       </c>
-      <c r="W22" s="376"/>
-      <c r="X22" s="376"/>
-      <c r="Y22" s="376"/>
-      <c r="Z22" s="376"/>
+      <c r="W22" s="441"/>
+      <c r="X22" s="441"/>
+      <c r="Y22" s="441"/>
+      <c r="Z22" s="441"/>
       <c r="AA22" s="70" t="s">
         <v>31</v>
       </c>
@@ -16889,40 +16898,40 @@
       <c r="C23" s="218" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="370" t="s">
+      <c r="D23" s="366" t="s">
         <v>22</v>
       </c>
-      <c r="E23" s="371"/>
-      <c r="F23" s="371"/>
-      <c r="G23" s="371"/>
-      <c r="H23" s="371"/>
-      <c r="I23" s="371"/>
-      <c r="J23" s="371"/>
-      <c r="K23" s="372"/>
-      <c r="L23" s="365" t="s">
+      <c r="E23" s="367"/>
+      <c r="F23" s="367"/>
+      <c r="G23" s="367"/>
+      <c r="H23" s="367"/>
+      <c r="I23" s="367"/>
+      <c r="J23" s="367"/>
+      <c r="K23" s="368"/>
+      <c r="L23" s="439" t="s">
         <v>33</v>
       </c>
-      <c r="M23" s="366"/>
-      <c r="N23" s="366"/>
-      <c r="O23" s="366"/>
-      <c r="P23" s="365" t="s">
+      <c r="M23" s="432"/>
+      <c r="N23" s="432"/>
+      <c r="O23" s="432"/>
+      <c r="P23" s="439" t="s">
         <v>34</v>
       </c>
-      <c r="Q23" s="366"/>
-      <c r="R23" s="366"/>
-      <c r="S23" s="375"/>
-      <c r="T23" s="365" t="s">
+      <c r="Q23" s="432"/>
+      <c r="R23" s="432"/>
+      <c r="S23" s="440"/>
+      <c r="T23" s="439" t="s">
         <v>23</v>
       </c>
-      <c r="U23" s="366"/>
-      <c r="V23" s="366"/>
-      <c r="W23" s="366"/>
-      <c r="X23" s="375"/>
-      <c r="Y23" s="366" t="s">
+      <c r="U23" s="432"/>
+      <c r="V23" s="432"/>
+      <c r="W23" s="432"/>
+      <c r="X23" s="440"/>
+      <c r="Y23" s="432" t="s">
         <v>38</v>
       </c>
-      <c r="Z23" s="366"/>
-      <c r="AA23" s="375"/>
+      <c r="Z23" s="432"/>
+      <c r="AA23" s="440"/>
       <c r="AB23" s="5"/>
     </row>
     <row r="24" spans="1:28" s="6" customFormat="1" ht="35.1" customHeight="1">
@@ -16931,36 +16940,36 @@
       <c r="C24" s="62">
         <v>1</v>
       </c>
-      <c r="D24" s="465" t="s">
+      <c r="D24" s="363" t="s">
         <v>91</v>
       </c>
-      <c r="E24" s="466"/>
-      <c r="F24" s="466"/>
-      <c r="G24" s="466"/>
-      <c r="H24" s="466"/>
-      <c r="I24" s="466"/>
-      <c r="J24" s="466"/>
-      <c r="K24" s="467"/>
-      <c r="L24" s="370" t="s">
+      <c r="E24" s="364"/>
+      <c r="F24" s="364"/>
+      <c r="G24" s="364"/>
+      <c r="H24" s="364"/>
+      <c r="I24" s="364"/>
+      <c r="J24" s="364"/>
+      <c r="K24" s="365"/>
+      <c r="L24" s="366" t="s">
         <v>89</v>
       </c>
-      <c r="M24" s="371"/>
-      <c r="N24" s="371"/>
-      <c r="O24" s="372"/>
-      <c r="P24" s="367"/>
-      <c r="Q24" s="368"/>
-      <c r="R24" s="368"/>
-      <c r="S24" s="369"/>
-      <c r="T24" s="468"/>
-      <c r="U24" s="469"/>
-      <c r="V24" s="469"/>
-      <c r="W24" s="469"/>
-      <c r="X24" s="470"/>
-      <c r="Y24" s="387" t="s">
+      <c r="M24" s="367"/>
+      <c r="N24" s="367"/>
+      <c r="O24" s="368"/>
+      <c r="P24" s="369"/>
+      <c r="Q24" s="370"/>
+      <c r="R24" s="370"/>
+      <c r="S24" s="371"/>
+      <c r="T24" s="372"/>
+      <c r="U24" s="373"/>
+      <c r="V24" s="373"/>
+      <c r="W24" s="373"/>
+      <c r="X24" s="374"/>
+      <c r="Y24" s="461" t="s">
         <v>105</v>
       </c>
-      <c r="Z24" s="387"/>
-      <c r="AA24" s="388"/>
+      <c r="Z24" s="461"/>
+      <c r="AA24" s="462"/>
       <c r="AB24" s="5"/>
     </row>
     <row r="25" spans="1:28" s="6" customFormat="1" ht="35.1" customHeight="1">
@@ -16969,36 +16978,36 @@
       <c r="C25" s="61">
         <v>2</v>
       </c>
-      <c r="D25" s="465" t="s">
+      <c r="D25" s="363" t="s">
         <v>92</v>
       </c>
-      <c r="E25" s="466"/>
-      <c r="F25" s="466"/>
-      <c r="G25" s="466"/>
-      <c r="H25" s="466"/>
-      <c r="I25" s="466"/>
-      <c r="J25" s="466"/>
-      <c r="K25" s="467"/>
-      <c r="L25" s="389" t="s">
+      <c r="E25" s="364"/>
+      <c r="F25" s="364"/>
+      <c r="G25" s="364"/>
+      <c r="H25" s="364"/>
+      <c r="I25" s="364"/>
+      <c r="J25" s="364"/>
+      <c r="K25" s="365"/>
+      <c r="L25" s="463" t="s">
         <v>44</v>
       </c>
-      <c r="M25" s="390"/>
-      <c r="N25" s="390"/>
-      <c r="O25" s="391"/>
-      <c r="P25" s="392"/>
-      <c r="Q25" s="393"/>
-      <c r="R25" s="393"/>
-      <c r="S25" s="394"/>
-      <c r="T25" s="395"/>
-      <c r="U25" s="396"/>
-      <c r="V25" s="396"/>
-      <c r="W25" s="396"/>
-      <c r="X25" s="397"/>
-      <c r="Y25" s="387" t="s">
+      <c r="M25" s="464"/>
+      <c r="N25" s="464"/>
+      <c r="O25" s="465"/>
+      <c r="P25" s="466"/>
+      <c r="Q25" s="467"/>
+      <c r="R25" s="467"/>
+      <c r="S25" s="468"/>
+      <c r="T25" s="469"/>
+      <c r="U25" s="470"/>
+      <c r="V25" s="470"/>
+      <c r="W25" s="470"/>
+      <c r="X25" s="471"/>
+      <c r="Y25" s="461" t="s">
         <v>265</v>
       </c>
-      <c r="Z25" s="387"/>
-      <c r="AA25" s="388"/>
+      <c r="Z25" s="461"/>
+      <c r="AA25" s="462"/>
       <c r="AB25" s="5"/>
     </row>
     <row r="26" spans="1:28" s="6" customFormat="1" ht="35.1" customHeight="1">
@@ -17007,193 +17016,193 @@
       <c r="C26" s="61">
         <v>3</v>
       </c>
-      <c r="D26" s="465" t="s">
+      <c r="D26" s="363" t="s">
         <v>88</v>
       </c>
-      <c r="E26" s="466"/>
-      <c r="F26" s="466"/>
-      <c r="G26" s="466"/>
-      <c r="H26" s="466"/>
-      <c r="I26" s="466"/>
-      <c r="J26" s="466"/>
-      <c r="K26" s="467"/>
-      <c r="L26" s="370" t="s">
+      <c r="E26" s="364"/>
+      <c r="F26" s="364"/>
+      <c r="G26" s="364"/>
+      <c r="H26" s="364"/>
+      <c r="I26" s="364"/>
+      <c r="J26" s="364"/>
+      <c r="K26" s="365"/>
+      <c r="L26" s="366" t="s">
         <v>44</v>
       </c>
-      <c r="M26" s="371"/>
-      <c r="N26" s="371"/>
-      <c r="O26" s="372"/>
-      <c r="P26" s="367"/>
-      <c r="Q26" s="368"/>
-      <c r="R26" s="368"/>
-      <c r="S26" s="369"/>
-      <c r="T26" s="468"/>
-      <c r="U26" s="469"/>
-      <c r="V26" s="469"/>
-      <c r="W26" s="469"/>
-      <c r="X26" s="470"/>
-      <c r="Y26" s="387"/>
-      <c r="Z26" s="387"/>
-      <c r="AA26" s="388"/>
+      <c r="M26" s="367"/>
+      <c r="N26" s="367"/>
+      <c r="O26" s="368"/>
+      <c r="P26" s="369"/>
+      <c r="Q26" s="370"/>
+      <c r="R26" s="370"/>
+      <c r="S26" s="371"/>
+      <c r="T26" s="372"/>
+      <c r="U26" s="373"/>
+      <c r="V26" s="373"/>
+      <c r="W26" s="373"/>
+      <c r="X26" s="374"/>
+      <c r="Y26" s="461"/>
+      <c r="Z26" s="461"/>
+      <c r="AA26" s="462"/>
       <c r="AB26" s="5"/>
     </row>
     <row r="27" spans="1:28" s="28" customFormat="1" ht="35.1" customHeight="1">
       <c r="A27" s="25"/>
       <c r="B27" s="26"/>
-      <c r="C27" s="444" t="s">
+      <c r="C27" s="381" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="444"/>
-      <c r="E27" s="444"/>
-      <c r="F27" s="444"/>
-      <c r="G27" s="444"/>
-      <c r="H27" s="444"/>
-      <c r="I27" s="444"/>
-      <c r="J27" s="444"/>
-      <c r="K27" s="445"/>
-      <c r="L27" s="452"/>
-      <c r="M27" s="444"/>
-      <c r="N27" s="444"/>
-      <c r="O27" s="445"/>
-      <c r="P27" s="362"/>
-      <c r="Q27" s="363"/>
-      <c r="R27" s="363"/>
-      <c r="S27" s="364"/>
-      <c r="T27" s="459"/>
-      <c r="U27" s="460"/>
-      <c r="V27" s="460"/>
-      <c r="W27" s="460"/>
-      <c r="X27" s="461"/>
-      <c r="Y27" s="387"/>
-      <c r="Z27" s="387"/>
-      <c r="AA27" s="388"/>
+      <c r="D27" s="381"/>
+      <c r="E27" s="381"/>
+      <c r="F27" s="381"/>
+      <c r="G27" s="381"/>
+      <c r="H27" s="381"/>
+      <c r="I27" s="381"/>
+      <c r="J27" s="381"/>
+      <c r="K27" s="382"/>
+      <c r="L27" s="389"/>
+      <c r="M27" s="381"/>
+      <c r="N27" s="381"/>
+      <c r="O27" s="382"/>
+      <c r="P27" s="458"/>
+      <c r="Q27" s="459"/>
+      <c r="R27" s="459"/>
+      <c r="S27" s="460"/>
+      <c r="T27" s="357"/>
+      <c r="U27" s="358"/>
+      <c r="V27" s="358"/>
+      <c r="W27" s="358"/>
+      <c r="X27" s="359"/>
+      <c r="Y27" s="461"/>
+      <c r="Z27" s="461"/>
+      <c r="AA27" s="462"/>
       <c r="AB27" s="27"/>
     </row>
     <row r="28" spans="1:28" s="28" customFormat="1" ht="39.75" customHeight="1">
       <c r="A28" s="25"/>
       <c r="B28" s="26"/>
-      <c r="C28" s="449" t="s">
+      <c r="C28" s="386" t="s">
         <v>93</v>
       </c>
-      <c r="D28" s="450"/>
-      <c r="E28" s="450"/>
-      <c r="F28" s="450"/>
-      <c r="G28" s="450"/>
-      <c r="H28" s="450"/>
-      <c r="I28" s="450"/>
-      <c r="J28" s="450"/>
-      <c r="K28" s="450"/>
-      <c r="L28" s="450"/>
-      <c r="M28" s="450"/>
-      <c r="N28" s="450"/>
-      <c r="O28" s="450"/>
-      <c r="P28" s="450"/>
-      <c r="Q28" s="450"/>
-      <c r="R28" s="450"/>
-      <c r="S28" s="451"/>
-      <c r="T28" s="446"/>
-      <c r="U28" s="447"/>
-      <c r="V28" s="447"/>
-      <c r="W28" s="447"/>
-      <c r="X28" s="448"/>
-      <c r="Y28" s="356" t="s">
+      <c r="D28" s="387"/>
+      <c r="E28" s="387"/>
+      <c r="F28" s="387"/>
+      <c r="G28" s="387"/>
+      <c r="H28" s="387"/>
+      <c r="I28" s="387"/>
+      <c r="J28" s="387"/>
+      <c r="K28" s="387"/>
+      <c r="L28" s="387"/>
+      <c r="M28" s="387"/>
+      <c r="N28" s="387"/>
+      <c r="O28" s="387"/>
+      <c r="P28" s="387"/>
+      <c r="Q28" s="387"/>
+      <c r="R28" s="387"/>
+      <c r="S28" s="388"/>
+      <c r="T28" s="383"/>
+      <c r="U28" s="384"/>
+      <c r="V28" s="384"/>
+      <c r="W28" s="384"/>
+      <c r="X28" s="385"/>
+      <c r="Y28" s="452" t="s">
         <v>207</v>
       </c>
-      <c r="Z28" s="357"/>
-      <c r="AA28" s="358"/>
+      <c r="Z28" s="453"/>
+      <c r="AA28" s="454"/>
       <c r="AB28" s="27"/>
     </row>
     <row r="29" spans="1:28" s="28" customFormat="1" ht="39.75" customHeight="1">
       <c r="A29" s="25"/>
       <c r="B29" s="26"/>
-      <c r="C29" s="449" t="s">
+      <c r="C29" s="386" t="s">
         <v>106</v>
       </c>
-      <c r="D29" s="450"/>
-      <c r="E29" s="450"/>
-      <c r="F29" s="450"/>
-      <c r="G29" s="450"/>
-      <c r="H29" s="450"/>
-      <c r="I29" s="450"/>
-      <c r="J29" s="450"/>
-      <c r="K29" s="450"/>
-      <c r="L29" s="450"/>
-      <c r="M29" s="450"/>
-      <c r="N29" s="450"/>
-      <c r="O29" s="450"/>
-      <c r="P29" s="450"/>
-      <c r="Q29" s="450"/>
-      <c r="R29" s="450"/>
-      <c r="S29" s="451"/>
-      <c r="T29" s="446"/>
-      <c r="U29" s="447"/>
-      <c r="V29" s="447"/>
-      <c r="W29" s="447"/>
-      <c r="X29" s="448"/>
-      <c r="Y29" s="359"/>
-      <c r="Z29" s="360"/>
-      <c r="AA29" s="361"/>
+      <c r="D29" s="387"/>
+      <c r="E29" s="387"/>
+      <c r="F29" s="387"/>
+      <c r="G29" s="387"/>
+      <c r="H29" s="387"/>
+      <c r="I29" s="387"/>
+      <c r="J29" s="387"/>
+      <c r="K29" s="387"/>
+      <c r="L29" s="387"/>
+      <c r="M29" s="387"/>
+      <c r="N29" s="387"/>
+      <c r="O29" s="387"/>
+      <c r="P29" s="387"/>
+      <c r="Q29" s="387"/>
+      <c r="R29" s="387"/>
+      <c r="S29" s="388"/>
+      <c r="T29" s="383"/>
+      <c r="U29" s="384"/>
+      <c r="V29" s="384"/>
+      <c r="W29" s="384"/>
+      <c r="X29" s="385"/>
+      <c r="Y29" s="455"/>
+      <c r="Z29" s="456"/>
+      <c r="AA29" s="457"/>
       <c r="AB29" s="27"/>
     </row>
     <row r="30" spans="1:28" s="6" customFormat="1" ht="24" customHeight="1">
       <c r="A30" s="10"/>
-      <c r="C30" s="440"/>
-      <c r="D30" s="440"/>
-      <c r="E30" s="440"/>
-      <c r="F30" s="440"/>
-      <c r="G30" s="440"/>
-      <c r="H30" s="440"/>
-      <c r="I30" s="440"/>
-      <c r="J30" s="440"/>
-      <c r="K30" s="440"/>
-      <c r="L30" s="441"/>
-      <c r="M30" s="441"/>
-      <c r="N30" s="441"/>
-      <c r="O30" s="441"/>
-      <c r="P30" s="441"/>
-      <c r="Q30" s="441"/>
-      <c r="R30" s="441"/>
-      <c r="S30" s="441"/>
-      <c r="T30" s="442"/>
-      <c r="U30" s="442"/>
-      <c r="V30" s="442"/>
-      <c r="W30" s="442"/>
-      <c r="X30" s="442"/>
-      <c r="Y30" s="443"/>
-      <c r="Z30" s="443"/>
-      <c r="AA30" s="443"/>
+      <c r="C30" s="393"/>
+      <c r="D30" s="393"/>
+      <c r="E30" s="393"/>
+      <c r="F30" s="393"/>
+      <c r="G30" s="393"/>
+      <c r="H30" s="393"/>
+      <c r="I30" s="393"/>
+      <c r="J30" s="393"/>
+      <c r="K30" s="393"/>
+      <c r="L30" s="394"/>
+      <c r="M30" s="394"/>
+      <c r="N30" s="394"/>
+      <c r="O30" s="394"/>
+      <c r="P30" s="394"/>
+      <c r="Q30" s="394"/>
+      <c r="R30" s="394"/>
+      <c r="S30" s="394"/>
+      <c r="T30" s="395"/>
+      <c r="U30" s="395"/>
+      <c r="V30" s="395"/>
+      <c r="W30" s="395"/>
+      <c r="X30" s="395"/>
+      <c r="Y30" s="396"/>
+      <c r="Z30" s="396"/>
+      <c r="AA30" s="396"/>
       <c r="AB30" s="5"/>
     </row>
     <row r="31" spans="1:28" s="6" customFormat="1" ht="33" customHeight="1">
       <c r="A31" s="10"/>
       <c r="B31" s="221"/>
-      <c r="C31" s="437" t="s">
+      <c r="C31" s="390" t="s">
         <v>231</v>
       </c>
-      <c r="D31" s="438"/>
-      <c r="E31" s="438"/>
-      <c r="F31" s="438"/>
-      <c r="G31" s="438"/>
-      <c r="H31" s="438"/>
-      <c r="I31" s="438"/>
-      <c r="J31" s="438"/>
-      <c r="K31" s="438"/>
-      <c r="L31" s="438"/>
-      <c r="M31" s="438"/>
-      <c r="N31" s="438"/>
-      <c r="O31" s="438"/>
-      <c r="P31" s="438"/>
-      <c r="Q31" s="438"/>
-      <c r="R31" s="438"/>
-      <c r="S31" s="438"/>
-      <c r="T31" s="438"/>
-      <c r="U31" s="438"/>
-      <c r="V31" s="438"/>
-      <c r="W31" s="438"/>
-      <c r="X31" s="438"/>
-      <c r="Y31" s="438"/>
-      <c r="Z31" s="438"/>
-      <c r="AA31" s="439"/>
+      <c r="D31" s="391"/>
+      <c r="E31" s="391"/>
+      <c r="F31" s="391"/>
+      <c r="G31" s="391"/>
+      <c r="H31" s="391"/>
+      <c r="I31" s="391"/>
+      <c r="J31" s="391"/>
+      <c r="K31" s="391"/>
+      <c r="L31" s="391"/>
+      <c r="M31" s="391"/>
+      <c r="N31" s="391"/>
+      <c r="O31" s="391"/>
+      <c r="P31" s="391"/>
+      <c r="Q31" s="391"/>
+      <c r="R31" s="391"/>
+      <c r="S31" s="391"/>
+      <c r="T31" s="391"/>
+      <c r="U31" s="391"/>
+      <c r="V31" s="391"/>
+      <c r="W31" s="391"/>
+      <c r="X31" s="391"/>
+      <c r="Y31" s="391"/>
+      <c r="Z31" s="391"/>
+      <c r="AA31" s="392"/>
       <c r="AB31" s="5"/>
     </row>
     <row r="32" spans="1:28" s="31" customFormat="1" ht="33" customHeight="1">
@@ -17392,32 +17401,49 @@
     </row>
   </sheetData>
   <mergeCells count="87">
-    <mergeCell ref="G22:K22"/>
-    <mergeCell ref="X9:AA9"/>
-    <mergeCell ref="T27:X27"/>
-    <mergeCell ref="Q12:T13"/>
-    <mergeCell ref="D26:K26"/>
-    <mergeCell ref="L26:O26"/>
-    <mergeCell ref="P26:S26"/>
-    <mergeCell ref="T26:X26"/>
-    <mergeCell ref="D24:K24"/>
-    <mergeCell ref="D25:K25"/>
-    <mergeCell ref="T24:X24"/>
-    <mergeCell ref="R19:V19"/>
-    <mergeCell ref="W19:AA19"/>
-    <mergeCell ref="C27:K27"/>
-    <mergeCell ref="T29:X29"/>
-    <mergeCell ref="C28:S28"/>
-    <mergeCell ref="C29:S29"/>
-    <mergeCell ref="L27:O27"/>
-    <mergeCell ref="T28:X28"/>
-    <mergeCell ref="C31:AA31"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:K30"/>
-    <mergeCell ref="L30:O30"/>
-    <mergeCell ref="P30:S30"/>
-    <mergeCell ref="T30:X30"/>
-    <mergeCell ref="Y30:AA30"/>
+    <mergeCell ref="R18:V18"/>
+    <mergeCell ref="Y28:AA29"/>
+    <mergeCell ref="P27:S27"/>
+    <mergeCell ref="L23:O23"/>
+    <mergeCell ref="P24:S24"/>
+    <mergeCell ref="Y24:AA24"/>
+    <mergeCell ref="L25:O25"/>
+    <mergeCell ref="P25:S25"/>
+    <mergeCell ref="T25:X25"/>
+    <mergeCell ref="L24:O24"/>
+    <mergeCell ref="Y26:AA26"/>
+    <mergeCell ref="Y27:AA27"/>
+    <mergeCell ref="Y25:AA25"/>
+    <mergeCell ref="D23:K23"/>
+    <mergeCell ref="X14:AA14"/>
+    <mergeCell ref="W18:Y18"/>
+    <mergeCell ref="T23:X23"/>
+    <mergeCell ref="V22:Z22"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="O22:S22"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="J20:AA20"/>
+    <mergeCell ref="J19:Q19"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="J18:Q18"/>
+    <mergeCell ref="Y23:AA23"/>
+    <mergeCell ref="P23:S23"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="Q14:T14"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="F14:J14"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="N12:P13"/>
+    <mergeCell ref="J17:AA17"/>
+    <mergeCell ref="U14:W14"/>
+    <mergeCell ref="X11:AA11"/>
+    <mergeCell ref="X13:AA13"/>
+    <mergeCell ref="X12:AA12"/>
+    <mergeCell ref="U13:W13"/>
+    <mergeCell ref="U12:W12"/>
     <mergeCell ref="A2:AA2"/>
     <mergeCell ref="S4:AA4"/>
     <mergeCell ref="N9:P9"/>
@@ -17434,53 +17460,36 @@
     <mergeCell ref="E8:L8"/>
     <mergeCell ref="Q10:AA10"/>
     <mergeCell ref="N10:P10"/>
+    <mergeCell ref="C31:AA31"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:K30"/>
+    <mergeCell ref="L30:O30"/>
+    <mergeCell ref="P30:S30"/>
+    <mergeCell ref="T30:X30"/>
+    <mergeCell ref="Y30:AA30"/>
+    <mergeCell ref="T29:X29"/>
+    <mergeCell ref="C28:S28"/>
+    <mergeCell ref="C29:S29"/>
+    <mergeCell ref="L27:O27"/>
+    <mergeCell ref="T28:X28"/>
+    <mergeCell ref="G22:K22"/>
+    <mergeCell ref="X9:AA9"/>
+    <mergeCell ref="T27:X27"/>
+    <mergeCell ref="Q12:T13"/>
+    <mergeCell ref="D26:K26"/>
+    <mergeCell ref="L26:O26"/>
+    <mergeCell ref="P26:S26"/>
+    <mergeCell ref="T26:X26"/>
+    <mergeCell ref="D24:K24"/>
+    <mergeCell ref="D25:K25"/>
+    <mergeCell ref="T24:X24"/>
+    <mergeCell ref="R19:V19"/>
+    <mergeCell ref="W19:AA19"/>
+    <mergeCell ref="C27:K27"/>
     <mergeCell ref="F11:L11"/>
     <mergeCell ref="D17:H17"/>
-    <mergeCell ref="J17:AA17"/>
-    <mergeCell ref="U14:W14"/>
-    <mergeCell ref="X11:AA11"/>
-    <mergeCell ref="X13:AA13"/>
-    <mergeCell ref="X12:AA12"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="Q14:T14"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="F14:J14"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="U13:W13"/>
-    <mergeCell ref="N12:P13"/>
-    <mergeCell ref="U12:W12"/>
-    <mergeCell ref="D23:K23"/>
-    <mergeCell ref="X14:AA14"/>
-    <mergeCell ref="W18:Y18"/>
-    <mergeCell ref="T23:X23"/>
-    <mergeCell ref="V22:Z22"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="O22:S22"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="J20:AA20"/>
-    <mergeCell ref="J19:Q19"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="J18:Q18"/>
-    <mergeCell ref="Y23:AA23"/>
-    <mergeCell ref="P23:S23"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="R18:V18"/>
-    <mergeCell ref="Y28:AA29"/>
-    <mergeCell ref="P27:S27"/>
-    <mergeCell ref="L23:O23"/>
-    <mergeCell ref="P24:S24"/>
-    <mergeCell ref="Y24:AA24"/>
-    <mergeCell ref="L25:O25"/>
-    <mergeCell ref="P25:S25"/>
-    <mergeCell ref="T25:X25"/>
-    <mergeCell ref="L24:O24"/>
-    <mergeCell ref="Y26:AA26"/>
-    <mergeCell ref="Y27:AA27"/>
-    <mergeCell ref="Y25:AA25"/>
   </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="95" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.84" bottom="0.34" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="61" orientation="portrait" r:id="rId1"/>
@@ -17510,18 +17519,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="35.25" customHeight="1">
-      <c r="A1" s="474" t="s">
+      <c r="A1" s="528" t="s">
         <v>115</v>
       </c>
-      <c r="B1" s="474"/>
-      <c r="C1" s="474"/>
-      <c r="D1" s="474"/>
-      <c r="E1" s="474"/>
-      <c r="F1" s="474"/>
-      <c r="G1" s="474"/>
-      <c r="H1" s="474"/>
-      <c r="I1" s="474"/>
-      <c r="J1" s="474"/>
+      <c r="B1" s="528"/>
+      <c r="C1" s="528"/>
+      <c r="D1" s="528"/>
+      <c r="E1" s="528"/>
+      <c r="F1" s="528"/>
+      <c r="G1" s="528"/>
+      <c r="H1" s="528"/>
+      <c r="I1" s="528"/>
+      <c r="J1" s="528"/>
     </row>
     <row r="2" spans="1:10" ht="27.95" customHeight="1" thickBot="1">
       <c r="A2" s="37"/>
@@ -17535,11 +17544,11 @@
       <c r="I2" s="37"/>
     </row>
     <row r="3" spans="1:10" ht="27.95" customHeight="1" thickBot="1">
-      <c r="A3" s="488" t="s">
+      <c r="A3" s="537" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="489"/>
-      <c r="C3" s="490"/>
+      <c r="B3" s="538"/>
+      <c r="C3" s="539"/>
       <c r="D3" s="38"/>
       <c r="E3" s="38"/>
       <c r="F3" s="38"/>
@@ -17558,20 +17567,20 @@
       <c r="D4" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="E4" s="479" t="s">
+      <c r="E4" s="530" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="480"/>
+      <c r="F4" s="531"/>
       <c r="G4" s="42" t="s">
         <v>2</v>
       </c>
       <c r="H4" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="I4" s="484" t="s">
+      <c r="I4" s="535" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="485"/>
+      <c r="J4" s="536"/>
     </row>
     <row r="5" spans="1:10" ht="27.95" customHeight="1">
       <c r="A5" s="320" t="s">
@@ -17582,12 +17591,12 @@
         <v>4</v>
       </c>
       <c r="D5" s="45"/>
-      <c r="E5" s="491"/>
-      <c r="F5" s="492"/>
-      <c r="G5" s="492"/>
-      <c r="H5" s="492"/>
-      <c r="I5" s="492"/>
-      <c r="J5" s="493"/>
+      <c r="E5" s="540"/>
+      <c r="F5" s="541"/>
+      <c r="G5" s="541"/>
+      <c r="H5" s="541"/>
+      <c r="I5" s="541"/>
+      <c r="J5" s="542"/>
     </row>
     <row r="6" spans="1:10" ht="27.95" customHeight="1">
       <c r="A6" s="321"/>
@@ -17600,12 +17609,12 @@
       <c r="D6" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="477"/>
-      <c r="F6" s="478"/>
+      <c r="E6" s="485"/>
+      <c r="F6" s="529"/>
       <c r="G6" s="46"/>
       <c r="H6" s="47"/>
-      <c r="I6" s="486"/>
-      <c r="J6" s="487"/>
+      <c r="I6" s="483"/>
+      <c r="J6" s="484"/>
     </row>
     <row r="7" spans="1:10" ht="27.95" customHeight="1">
       <c r="A7" s="321"/>
@@ -17618,12 +17627,12 @@
       <c r="D7" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="477"/>
-      <c r="F7" s="478"/>
+      <c r="E7" s="485"/>
+      <c r="F7" s="529"/>
       <c r="G7" s="46"/>
       <c r="H7" s="47"/>
-      <c r="I7" s="486"/>
-      <c r="J7" s="487"/>
+      <c r="I7" s="483"/>
+      <c r="J7" s="484"/>
     </row>
     <row r="8" spans="1:10" ht="27.95" customHeight="1">
       <c r="A8" s="321"/>
@@ -17636,12 +17645,12 @@
       <c r="D8" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="E8" s="477"/>
-      <c r="F8" s="478"/>
+      <c r="E8" s="485"/>
+      <c r="F8" s="529"/>
       <c r="G8" s="46"/>
       <c r="H8" s="47"/>
-      <c r="I8" s="486"/>
-      <c r="J8" s="487"/>
+      <c r="I8" s="483"/>
+      <c r="J8" s="484"/>
     </row>
     <row r="9" spans="1:10" ht="27.95" customHeight="1">
       <c r="A9" s="321"/>
@@ -17654,26 +17663,26 @@
       <c r="D9" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="E9" s="477"/>
-      <c r="F9" s="478"/>
+      <c r="E9" s="485"/>
+      <c r="F9" s="529"/>
       <c r="G9" s="47"/>
       <c r="H9" s="47"/>
-      <c r="I9" s="486"/>
-      <c r="J9" s="487"/>
+      <c r="I9" s="483"/>
+      <c r="J9" s="484"/>
     </row>
     <row r="10" spans="1:10" ht="27.95" customHeight="1">
-      <c r="A10" s="481" t="s">
+      <c r="A10" s="532" t="s">
         <v>61</v>
       </c>
-      <c r="B10" s="482"/>
-      <c r="C10" s="483"/>
+      <c r="B10" s="533"/>
+      <c r="C10" s="534"/>
       <c r="D10" s="55"/>
-      <c r="E10" s="477"/>
-      <c r="F10" s="494"/>
+      <c r="E10" s="485"/>
+      <c r="F10" s="486"/>
       <c r="G10" s="46"/>
       <c r="H10" s="47"/>
-      <c r="I10" s="486"/>
-      <c r="J10" s="487"/>
+      <c r="I10" s="483"/>
+      <c r="J10" s="484"/>
     </row>
     <row r="11" spans="1:10" ht="27.95" customHeight="1">
       <c r="A11" s="320" t="s">
@@ -17686,18 +17695,18 @@
       <c r="D11" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="E11" s="475" t="s">
+      <c r="E11" s="478" t="s">
         <v>46</v>
       </c>
-      <c r="F11" s="476"/>
+      <c r="F11" s="479"/>
       <c r="G11" s="49">
         <v>0.1</v>
       </c>
       <c r="H11" s="50"/>
-      <c r="I11" s="495" t="s">
+      <c r="I11" s="487" t="s">
         <v>59</v>
       </c>
-      <c r="J11" s="496"/>
+      <c r="J11" s="488"/>
     </row>
     <row r="12" spans="1:10" ht="27.95" customHeight="1">
       <c r="A12" s="320" t="s">
@@ -17710,18 +17719,18 @@
       <c r="D12" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="475" t="s">
+      <c r="E12" s="478" t="s">
         <v>46</v>
       </c>
-      <c r="F12" s="476"/>
+      <c r="F12" s="479"/>
       <c r="G12" s="49">
         <v>1.1000000000000001</v>
       </c>
       <c r="H12" s="50"/>
-      <c r="I12" s="537" t="s">
+      <c r="I12" s="473" t="s">
         <v>17</v>
       </c>
-      <c r="J12" s="538"/>
+      <c r="J12" s="474"/>
     </row>
     <row r="13" spans="1:10" ht="27.95" customHeight="1">
       <c r="A13" s="320" t="s">
@@ -17734,18 +17743,18 @@
       <c r="D13" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="E13" s="475" t="s">
+      <c r="E13" s="478" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="476"/>
+      <c r="F13" s="479"/>
       <c r="G13" s="49">
         <v>0.2</v>
       </c>
       <c r="H13" s="50"/>
-      <c r="I13" s="537" t="s">
+      <c r="I13" s="473" t="s">
         <v>15</v>
       </c>
-      <c r="J13" s="538"/>
+      <c r="J13" s="474"/>
     </row>
     <row r="14" spans="1:10" ht="27.95" customHeight="1">
       <c r="A14" s="320" t="s">
@@ -17756,14 +17765,14 @@
         <v>64</v>
       </c>
       <c r="D14" s="48"/>
-      <c r="E14" s="475" t="s">
+      <c r="E14" s="478" t="s">
         <v>65</v>
       </c>
-      <c r="F14" s="476"/>
+      <c r="F14" s="479"/>
       <c r="G14" s="49"/>
       <c r="H14" s="68"/>
-      <c r="I14" s="542"/>
-      <c r="J14" s="543"/>
+      <c r="I14" s="480"/>
+      <c r="J14" s="481"/>
     </row>
     <row r="15" spans="1:10" ht="27.95" customHeight="1">
       <c r="A15" s="320" t="s">
@@ -17774,12 +17783,12 @@
         <v>77</v>
       </c>
       <c r="D15" s="48"/>
-      <c r="E15" s="475"/>
-      <c r="F15" s="476"/>
-      <c r="G15" s="544"/>
+      <c r="E15" s="478"/>
+      <c r="F15" s="479"/>
+      <c r="G15" s="482"/>
       <c r="H15" s="68"/>
-      <c r="I15" s="542"/>
-      <c r="J15" s="543"/>
+      <c r="I15" s="480"/>
+      <c r="J15" s="481"/>
     </row>
     <row r="16" spans="1:10" ht="7.5" customHeight="1">
       <c r="A16" s="322"/>
@@ -17806,8 +17815,8 @@
       <c r="F17" s="327"/>
       <c r="G17" s="328"/>
       <c r="H17" s="329"/>
-      <c r="I17" s="505"/>
-      <c r="J17" s="506"/>
+      <c r="I17" s="497"/>
+      <c r="J17" s="498"/>
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" thickBot="1">
       <c r="A18" s="37"/>
@@ -17821,18 +17830,18 @@
       <c r="I18" s="37"/>
     </row>
     <row r="19" spans="1:10" ht="24" customHeight="1">
-      <c r="A19" s="502" t="s">
+      <c r="A19" s="494" t="s">
         <v>125</v>
       </c>
-      <c r="B19" s="503"/>
-      <c r="C19" s="503"/>
-      <c r="D19" s="503"/>
-      <c r="E19" s="503"/>
-      <c r="F19" s="503"/>
-      <c r="G19" s="503"/>
-      <c r="H19" s="503"/>
-      <c r="I19" s="503"/>
-      <c r="J19" s="504"/>
+      <c r="B19" s="495"/>
+      <c r="C19" s="495"/>
+      <c r="D19" s="495"/>
+      <c r="E19" s="495"/>
+      <c r="F19" s="495"/>
+      <c r="G19" s="495"/>
+      <c r="H19" s="495"/>
+      <c r="I19" s="495"/>
+      <c r="J19" s="496"/>
     </row>
     <row r="20" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A20" s="103"/>
@@ -17932,120 +17941,120 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="110"/>
-      <c r="B27" s="507" t="s">
+      <c r="B27" s="499" t="s">
         <v>100</v>
       </c>
-      <c r="C27" s="508"/>
-      <c r="D27" s="528" t="s">
+      <c r="C27" s="500"/>
+      <c r="D27" s="520" t="s">
         <v>120</v>
       </c>
-      <c r="E27" s="529"/>
-      <c r="F27" s="529"/>
-      <c r="G27" s="529"/>
-      <c r="H27" s="529"/>
-      <c r="I27" s="508"/>
+      <c r="E27" s="521"/>
+      <c r="F27" s="521"/>
+      <c r="G27" s="521"/>
+      <c r="H27" s="521"/>
+      <c r="I27" s="500"/>
       <c r="J27" s="111"/>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="112"/>
-      <c r="B28" s="509" t="s">
+      <c r="B28" s="501" t="s">
         <v>116</v>
       </c>
-      <c r="C28" s="510"/>
-      <c r="D28" s="519" t="s">
+      <c r="C28" s="502"/>
+      <c r="D28" s="511" t="s">
         <v>126</v>
       </c>
-      <c r="E28" s="520"/>
-      <c r="F28" s="520"/>
-      <c r="G28" s="520"/>
-      <c r="H28" s="520"/>
-      <c r="I28" s="521"/>
+      <c r="E28" s="512"/>
+      <c r="F28" s="512"/>
+      <c r="G28" s="512"/>
+      <c r="H28" s="512"/>
+      <c r="I28" s="513"/>
       <c r="J28" s="113"/>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="112"/>
-      <c r="B29" s="511"/>
-      <c r="C29" s="512"/>
-      <c r="D29" s="522"/>
-      <c r="E29" s="523"/>
-      <c r="F29" s="523"/>
-      <c r="G29" s="523"/>
-      <c r="H29" s="523"/>
-      <c r="I29" s="524"/>
+      <c r="B29" s="503"/>
+      <c r="C29" s="504"/>
+      <c r="D29" s="514"/>
+      <c r="E29" s="515"/>
+      <c r="F29" s="515"/>
+      <c r="G29" s="515"/>
+      <c r="H29" s="515"/>
+      <c r="I29" s="516"/>
       <c r="J29" s="113"/>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="112"/>
-      <c r="B30" s="513"/>
-      <c r="C30" s="514"/>
-      <c r="D30" s="525"/>
-      <c r="E30" s="526"/>
-      <c r="F30" s="526"/>
-      <c r="G30" s="526"/>
-      <c r="H30" s="526"/>
-      <c r="I30" s="527"/>
+      <c r="B30" s="505"/>
+      <c r="C30" s="506"/>
+      <c r="D30" s="517"/>
+      <c r="E30" s="518"/>
+      <c r="F30" s="518"/>
+      <c r="G30" s="518"/>
+      <c r="H30" s="518"/>
+      <c r="I30" s="519"/>
       <c r="J30" s="113"/>
     </row>
     <row r="31" spans="1:10" ht="27.95" customHeight="1">
       <c r="A31" s="112"/>
-      <c r="B31" s="515" t="s">
+      <c r="B31" s="507" t="s">
         <v>117</v>
       </c>
-      <c r="C31" s="516"/>
-      <c r="D31" s="530" t="s">
+      <c r="C31" s="508"/>
+      <c r="D31" s="522" t="s">
         <v>121</v>
       </c>
-      <c r="E31" s="531"/>
-      <c r="F31" s="531"/>
-      <c r="G31" s="531"/>
-      <c r="H31" s="531"/>
-      <c r="I31" s="532"/>
+      <c r="E31" s="523"/>
+      <c r="F31" s="523"/>
+      <c r="G31" s="523"/>
+      <c r="H31" s="523"/>
+      <c r="I31" s="524"/>
       <c r="J31" s="114"/>
     </row>
     <row r="32" spans="1:10" ht="14.1" customHeight="1">
       <c r="A32" s="112"/>
-      <c r="B32" s="517" t="s">
+      <c r="B32" s="509" t="s">
         <v>118</v>
       </c>
-      <c r="C32" s="518"/>
-      <c r="D32" s="533" t="s">
+      <c r="C32" s="510"/>
+      <c r="D32" s="525" t="s">
         <v>122</v>
       </c>
-      <c r="E32" s="534"/>
-      <c r="F32" s="534"/>
-      <c r="G32" s="534"/>
-      <c r="H32" s="534"/>
-      <c r="I32" s="535"/>
+      <c r="E32" s="526"/>
+      <c r="F32" s="526"/>
+      <c r="G32" s="526"/>
+      <c r="H32" s="526"/>
+      <c r="I32" s="527"/>
       <c r="J32" s="114"/>
     </row>
     <row r="33" spans="1:10" ht="14.1" customHeight="1">
       <c r="A33" s="112"/>
-      <c r="B33" s="513"/>
-      <c r="C33" s="514"/>
-      <c r="D33" s="539" t="s">
+      <c r="B33" s="505"/>
+      <c r="C33" s="506"/>
+      <c r="D33" s="475" t="s">
         <v>123</v>
       </c>
-      <c r="E33" s="540"/>
-      <c r="F33" s="540"/>
-      <c r="G33" s="540"/>
-      <c r="H33" s="540"/>
-      <c r="I33" s="541"/>
+      <c r="E33" s="476"/>
+      <c r="F33" s="476"/>
+      <c r="G33" s="476"/>
+      <c r="H33" s="476"/>
+      <c r="I33" s="477"/>
       <c r="J33" s="114"/>
     </row>
     <row r="34" spans="1:10" ht="27.95" customHeight="1">
       <c r="A34" s="112"/>
-      <c r="B34" s="497" t="s">
+      <c r="B34" s="489" t="s">
         <v>119</v>
       </c>
-      <c r="C34" s="498"/>
-      <c r="D34" s="499" t="s">
+      <c r="C34" s="490"/>
+      <c r="D34" s="491" t="s">
         <v>124</v>
       </c>
-      <c r="E34" s="500"/>
-      <c r="F34" s="500"/>
-      <c r="G34" s="500"/>
-      <c r="H34" s="500"/>
-      <c r="I34" s="501"/>
+      <c r="E34" s="492"/>
+      <c r="F34" s="492"/>
+      <c r="G34" s="492"/>
+      <c r="H34" s="492"/>
+      <c r="I34" s="493"/>
       <c r="J34" s="114"/>
     </row>
     <row r="35" spans="1:10" ht="34.5" customHeight="1" thickBot="1">
@@ -18061,16 +18070,16 @@
       <c r="J35" s="332"/>
     </row>
     <row r="36" spans="1:10" ht="30" customHeight="1">
-      <c r="A36" s="536"/>
-      <c r="B36" s="536"/>
-      <c r="C36" s="536"/>
-      <c r="D36" s="536"/>
-      <c r="E36" s="536"/>
-      <c r="F36" s="536"/>
-      <c r="G36" s="536"/>
-      <c r="H36" s="536"/>
-      <c r="I36" s="536"/>
-      <c r="J36" s="536"/>
+      <c r="A36" s="472"/>
+      <c r="B36" s="472"/>
+      <c r="C36" s="472"/>
+      <c r="D36" s="472"/>
+      <c r="E36" s="472"/>
+      <c r="F36" s="472"/>
+      <c r="G36" s="472"/>
+      <c r="H36" s="472"/>
+      <c r="I36" s="472"/>
+      <c r="J36" s="472"/>
     </row>
     <row r="37" spans="1:10"/>
     <row r="38" spans="1:10" hidden="1">
@@ -18078,14 +18087,22 @@
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="A36:J36"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="E5:J5"/>
+    <mergeCell ref="I9:J9"/>
     <mergeCell ref="I10:J10"/>
     <mergeCell ref="E10:F10"/>
     <mergeCell ref="E13:F13"/>
@@ -18102,22 +18119,14 @@
     <mergeCell ref="D27:I27"/>
     <mergeCell ref="D31:I31"/>
     <mergeCell ref="D32:I32"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="E5:J5"/>
-    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="A36:J36"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="E15:G15"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -18151,18 +18160,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="35.25" customHeight="1">
-      <c r="A1" s="474" t="s">
+      <c r="A1" s="528" t="s">
         <v>128</v>
       </c>
-      <c r="B1" s="474"/>
-      <c r="C1" s="474"/>
-      <c r="D1" s="474"/>
-      <c r="E1" s="474"/>
-      <c r="F1" s="474"/>
-      <c r="G1" s="474"/>
-      <c r="H1" s="474"/>
-      <c r="I1" s="474"/>
-      <c r="J1" s="474"/>
+      <c r="B1" s="528"/>
+      <c r="C1" s="528"/>
+      <c r="D1" s="528"/>
+      <c r="E1" s="528"/>
+      <c r="F1" s="528"/>
+      <c r="G1" s="528"/>
+      <c r="H1" s="528"/>
+      <c r="I1" s="528"/>
+      <c r="J1" s="528"/>
     </row>
     <row r="2" spans="1:10" ht="27.95" customHeight="1" thickBot="1">
       <c r="A2" s="37"/>
@@ -18176,11 +18185,11 @@
       <c r="I2" s="37"/>
     </row>
     <row r="3" spans="1:10" ht="27.95" customHeight="1" thickBot="1">
-      <c r="A3" s="545" t="s">
+      <c r="A3" s="555" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="546"/>
-      <c r="C3" s="547"/>
+      <c r="B3" s="556"/>
+      <c r="C3" s="557"/>
       <c r="D3" s="38"/>
       <c r="E3" s="38"/>
       <c r="F3" s="38"/>
@@ -18199,20 +18208,20 @@
       <c r="D4" s="83" t="s">
         <v>41</v>
       </c>
-      <c r="E4" s="548" t="s">
+      <c r="E4" s="558" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="549"/>
+      <c r="F4" s="559"/>
       <c r="G4" s="84" t="s">
         <v>2</v>
       </c>
       <c r="H4" s="84" t="s">
         <v>40</v>
       </c>
-      <c r="I4" s="550" t="s">
+      <c r="I4" s="560" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="551"/>
+      <c r="J4" s="561"/>
     </row>
     <row r="5" spans="1:10" ht="27.95" customHeight="1">
       <c r="A5" s="341" t="s">
@@ -18223,14 +18232,14 @@
         <v>37</v>
       </c>
       <c r="D5" s="87"/>
-      <c r="E5" s="554" t="s">
+      <c r="E5" s="562" t="s">
         <v>286</v>
       </c>
-      <c r="F5" s="555"/>
-      <c r="G5" s="555"/>
-      <c r="H5" s="555"/>
-      <c r="I5" s="555"/>
-      <c r="J5" s="556"/>
+      <c r="F5" s="563"/>
+      <c r="G5" s="563"/>
+      <c r="H5" s="563"/>
+      <c r="I5" s="563"/>
+      <c r="J5" s="564"/>
     </row>
     <row r="6" spans="1:10" ht="27.95" customHeight="1">
       <c r="A6" s="342"/>
@@ -18243,12 +18252,12 @@
       <c r="D6" s="90" t="s">
         <v>53</v>
       </c>
-      <c r="E6" s="552"/>
-      <c r="F6" s="553"/>
+      <c r="E6" s="553"/>
+      <c r="F6" s="554"/>
       <c r="G6" s="46"/>
       <c r="H6" s="54"/>
-      <c r="I6" s="486"/>
-      <c r="J6" s="487"/>
+      <c r="I6" s="483"/>
+      <c r="J6" s="484"/>
     </row>
     <row r="7" spans="1:10" ht="27.95" customHeight="1">
       <c r="A7" s="343"/>
@@ -18261,12 +18270,12 @@
       <c r="D7" s="90" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="552"/>
-      <c r="F7" s="553"/>
+      <c r="E7" s="553"/>
+      <c r="F7" s="554"/>
       <c r="G7" s="46"/>
       <c r="H7" s="54"/>
-      <c r="I7" s="486"/>
-      <c r="J7" s="487"/>
+      <c r="I7" s="483"/>
+      <c r="J7" s="484"/>
     </row>
     <row r="8" spans="1:10" ht="27.95" customHeight="1">
       <c r="A8" s="343"/>
@@ -18279,12 +18288,12 @@
       <c r="D8" s="90" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="552"/>
-      <c r="F8" s="553"/>
+      <c r="E8" s="553"/>
+      <c r="F8" s="554"/>
       <c r="G8" s="46"/>
       <c r="H8" s="54"/>
-      <c r="I8" s="486"/>
-      <c r="J8" s="487"/>
+      <c r="I8" s="483"/>
+      <c r="J8" s="484"/>
     </row>
     <row r="9" spans="1:10" ht="27.95" customHeight="1">
       <c r="A9" s="343"/>
@@ -18297,26 +18306,26 @@
       <c r="D9" s="90" t="s">
         <v>53</v>
       </c>
-      <c r="E9" s="552"/>
-      <c r="F9" s="553"/>
+      <c r="E9" s="553"/>
+      <c r="F9" s="554"/>
       <c r="G9" s="47"/>
       <c r="H9" s="54"/>
-      <c r="I9" s="486"/>
-      <c r="J9" s="487"/>
+      <c r="I9" s="483"/>
+      <c r="J9" s="484"/>
     </row>
     <row r="10" spans="1:10" ht="27.95" customHeight="1">
-      <c r="A10" s="557" t="s">
+      <c r="A10" s="548" t="s">
         <v>60</v>
       </c>
-      <c r="B10" s="558"/>
-      <c r="C10" s="559"/>
+      <c r="B10" s="549"/>
+      <c r="C10" s="550"/>
       <c r="D10" s="90"/>
-      <c r="E10" s="560"/>
-      <c r="F10" s="561"/>
+      <c r="E10" s="551"/>
+      <c r="F10" s="552"/>
       <c r="G10" s="56"/>
       <c r="H10" s="54"/>
-      <c r="I10" s="486"/>
-      <c r="J10" s="487"/>
+      <c r="I10" s="483"/>
+      <c r="J10" s="484"/>
     </row>
     <row r="11" spans="1:10" ht="27.95" customHeight="1">
       <c r="A11" s="341" t="s">
@@ -18329,18 +18338,18 @@
       <c r="D11" s="246" t="s">
         <v>261</v>
       </c>
-      <c r="E11" s="475" t="s">
+      <c r="E11" s="478" t="s">
         <v>52</v>
       </c>
-      <c r="F11" s="476"/>
+      <c r="F11" s="479"/>
       <c r="G11" s="72">
         <v>0.1</v>
       </c>
       <c r="H11" s="50"/>
-      <c r="I11" s="495" t="s">
+      <c r="I11" s="487" t="s">
         <v>59</v>
       </c>
-      <c r="J11" s="496"/>
+      <c r="J11" s="488"/>
     </row>
     <row r="12" spans="1:10" ht="27.95" customHeight="1">
       <c r="A12" s="341" t="s">
@@ -18353,18 +18362,18 @@
       <c r="D12" s="246" t="s">
         <v>261</v>
       </c>
-      <c r="E12" s="475" t="s">
+      <c r="E12" s="478" t="s">
         <v>52</v>
       </c>
-      <c r="F12" s="476"/>
+      <c r="F12" s="479"/>
       <c r="G12" s="72">
         <v>1.1000000000000001</v>
       </c>
       <c r="H12" s="50"/>
-      <c r="I12" s="537" t="s">
+      <c r="I12" s="473" t="s">
         <v>17</v>
       </c>
-      <c r="J12" s="538"/>
+      <c r="J12" s="474"/>
     </row>
     <row r="13" spans="1:10" ht="27.95" customHeight="1">
       <c r="A13" s="341" t="s">
@@ -18377,18 +18386,18 @@
       <c r="D13" s="246" t="s">
         <v>261</v>
       </c>
-      <c r="E13" s="475" t="s">
+      <c r="E13" s="478" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="476"/>
+      <c r="F13" s="479"/>
       <c r="G13" s="49">
         <v>0.2</v>
       </c>
       <c r="H13" s="50"/>
-      <c r="I13" s="537" t="s">
+      <c r="I13" s="473" t="s">
         <v>15</v>
       </c>
-      <c r="J13" s="538"/>
+      <c r="J13" s="474"/>
     </row>
     <row r="14" spans="1:10" ht="27.95" customHeight="1">
       <c r="A14" s="344" t="s">
@@ -18399,14 +18408,14 @@
         <v>7</v>
       </c>
       <c r="D14" s="87"/>
-      <c r="E14" s="475" t="s">
+      <c r="E14" s="478" t="s">
         <v>65</v>
       </c>
-      <c r="F14" s="476"/>
+      <c r="F14" s="479"/>
       <c r="G14" s="49"/>
       <c r="H14" s="68"/>
-      <c r="I14" s="542"/>
-      <c r="J14" s="543"/>
+      <c r="I14" s="480"/>
+      <c r="J14" s="481"/>
     </row>
     <row r="15" spans="1:10" ht="27.95" customHeight="1">
       <c r="A15" s="344" t="s">
@@ -18417,12 +18426,12 @@
         <v>81</v>
       </c>
       <c r="D15" s="87"/>
-      <c r="E15" s="475"/>
-      <c r="F15" s="476"/>
-      <c r="G15" s="544"/>
+      <c r="E15" s="478"/>
+      <c r="F15" s="479"/>
+      <c r="G15" s="482"/>
       <c r="H15" s="51"/>
-      <c r="I15" s="542"/>
-      <c r="J15" s="543"/>
+      <c r="I15" s="480"/>
+      <c r="J15" s="481"/>
     </row>
     <row r="16" spans="1:10" ht="7.5" customHeight="1">
       <c r="A16" s="338"/>
@@ -18449,8 +18458,8 @@
       <c r="F17" s="98"/>
       <c r="G17" s="99"/>
       <c r="H17" s="100"/>
-      <c r="I17" s="562"/>
-      <c r="J17" s="563"/>
+      <c r="I17" s="543"/>
+      <c r="J17" s="544"/>
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" thickBot="1">
       <c r="A18" s="37"/>
@@ -18464,18 +18473,18 @@
       <c r="I18" s="37"/>
     </row>
     <row r="19" spans="1:10" ht="24" customHeight="1">
-      <c r="A19" s="564" t="s">
+      <c r="A19" s="545" t="s">
         <v>125</v>
       </c>
-      <c r="B19" s="565"/>
-      <c r="C19" s="565"/>
-      <c r="D19" s="565"/>
-      <c r="E19" s="565"/>
-      <c r="F19" s="565"/>
-      <c r="G19" s="565"/>
-      <c r="H19" s="565"/>
-      <c r="I19" s="565"/>
-      <c r="J19" s="566"/>
+      <c r="B19" s="546"/>
+      <c r="C19" s="546"/>
+      <c r="D19" s="546"/>
+      <c r="E19" s="546"/>
+      <c r="F19" s="546"/>
+      <c r="G19" s="546"/>
+      <c r="H19" s="546"/>
+      <c r="I19" s="546"/>
+      <c r="J19" s="547"/>
     </row>
     <row r="20" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A20" s="103"/>
@@ -18575,120 +18584,120 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="110"/>
-      <c r="B27" s="507" t="s">
+      <c r="B27" s="499" t="s">
         <v>100</v>
       </c>
-      <c r="C27" s="508"/>
-      <c r="D27" s="528" t="s">
+      <c r="C27" s="500"/>
+      <c r="D27" s="520" t="s">
         <v>186</v>
       </c>
-      <c r="E27" s="529"/>
-      <c r="F27" s="529"/>
-      <c r="G27" s="529"/>
-      <c r="H27" s="529"/>
-      <c r="I27" s="508"/>
+      <c r="E27" s="521"/>
+      <c r="F27" s="521"/>
+      <c r="G27" s="521"/>
+      <c r="H27" s="521"/>
+      <c r="I27" s="500"/>
       <c r="J27" s="111"/>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="112"/>
-      <c r="B28" s="509" t="s">
+      <c r="B28" s="501" t="s">
         <v>116</v>
       </c>
-      <c r="C28" s="510"/>
-      <c r="D28" s="519" t="s">
+      <c r="C28" s="502"/>
+      <c r="D28" s="511" t="s">
         <v>129</v>
       </c>
-      <c r="E28" s="520"/>
-      <c r="F28" s="520"/>
-      <c r="G28" s="520"/>
-      <c r="H28" s="520"/>
-      <c r="I28" s="521"/>
+      <c r="E28" s="512"/>
+      <c r="F28" s="512"/>
+      <c r="G28" s="512"/>
+      <c r="H28" s="512"/>
+      <c r="I28" s="513"/>
       <c r="J28" s="113"/>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="112"/>
-      <c r="B29" s="511"/>
-      <c r="C29" s="512"/>
-      <c r="D29" s="522"/>
-      <c r="E29" s="523"/>
-      <c r="F29" s="523"/>
-      <c r="G29" s="523"/>
-      <c r="H29" s="523"/>
-      <c r="I29" s="524"/>
+      <c r="B29" s="503"/>
+      <c r="C29" s="504"/>
+      <c r="D29" s="514"/>
+      <c r="E29" s="515"/>
+      <c r="F29" s="515"/>
+      <c r="G29" s="515"/>
+      <c r="H29" s="515"/>
+      <c r="I29" s="516"/>
       <c r="J29" s="113"/>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="112"/>
-      <c r="B30" s="513"/>
-      <c r="C30" s="514"/>
-      <c r="D30" s="525"/>
-      <c r="E30" s="526"/>
-      <c r="F30" s="526"/>
-      <c r="G30" s="526"/>
-      <c r="H30" s="526"/>
-      <c r="I30" s="527"/>
+      <c r="B30" s="505"/>
+      <c r="C30" s="506"/>
+      <c r="D30" s="517"/>
+      <c r="E30" s="518"/>
+      <c r="F30" s="518"/>
+      <c r="G30" s="518"/>
+      <c r="H30" s="518"/>
+      <c r="I30" s="519"/>
       <c r="J30" s="113"/>
     </row>
     <row r="31" spans="1:10" ht="27.95" customHeight="1">
       <c r="A31" s="112"/>
-      <c r="B31" s="515" t="s">
+      <c r="B31" s="507" t="s">
         <v>117</v>
       </c>
-      <c r="C31" s="516"/>
-      <c r="D31" s="530" t="s">
+      <c r="C31" s="508"/>
+      <c r="D31" s="522" t="s">
         <v>130</v>
       </c>
-      <c r="E31" s="531"/>
-      <c r="F31" s="531"/>
-      <c r="G31" s="531"/>
-      <c r="H31" s="531"/>
-      <c r="I31" s="532"/>
+      <c r="E31" s="523"/>
+      <c r="F31" s="523"/>
+      <c r="G31" s="523"/>
+      <c r="H31" s="523"/>
+      <c r="I31" s="524"/>
       <c r="J31" s="114"/>
     </row>
     <row r="32" spans="1:10" ht="14.1" customHeight="1">
       <c r="A32" s="112"/>
-      <c r="B32" s="517" t="s">
+      <c r="B32" s="509" t="s">
         <v>118</v>
       </c>
-      <c r="C32" s="518"/>
-      <c r="D32" s="533" t="s">
+      <c r="C32" s="510"/>
+      <c r="D32" s="525" t="s">
         <v>131</v>
       </c>
-      <c r="E32" s="534"/>
-      <c r="F32" s="534"/>
-      <c r="G32" s="534"/>
-      <c r="H32" s="534"/>
-      <c r="I32" s="535"/>
+      <c r="E32" s="526"/>
+      <c r="F32" s="526"/>
+      <c r="G32" s="526"/>
+      <c r="H32" s="526"/>
+      <c r="I32" s="527"/>
       <c r="J32" s="114"/>
     </row>
     <row r="33" spans="1:10" ht="14.1" customHeight="1">
       <c r="A33" s="112"/>
-      <c r="B33" s="513"/>
-      <c r="C33" s="514"/>
-      <c r="D33" s="539" t="s">
+      <c r="B33" s="505"/>
+      <c r="C33" s="506"/>
+      <c r="D33" s="475" t="s">
         <v>132</v>
       </c>
-      <c r="E33" s="540"/>
-      <c r="F33" s="540"/>
-      <c r="G33" s="540"/>
-      <c r="H33" s="540"/>
-      <c r="I33" s="541"/>
+      <c r="E33" s="476"/>
+      <c r="F33" s="476"/>
+      <c r="G33" s="476"/>
+      <c r="H33" s="476"/>
+      <c r="I33" s="477"/>
       <c r="J33" s="114"/>
     </row>
     <row r="34" spans="1:10" ht="27.95" customHeight="1">
       <c r="A34" s="112"/>
-      <c r="B34" s="497" t="s">
+      <c r="B34" s="489" t="s">
         <v>119</v>
       </c>
-      <c r="C34" s="498"/>
-      <c r="D34" s="499" t="s">
+      <c r="C34" s="490"/>
+      <c r="D34" s="491" t="s">
         <v>133</v>
       </c>
-      <c r="E34" s="500"/>
-      <c r="F34" s="500"/>
-      <c r="G34" s="500"/>
-      <c r="H34" s="500"/>
-      <c r="I34" s="501"/>
+      <c r="E34" s="492"/>
+      <c r="F34" s="492"/>
+      <c r="G34" s="492"/>
+      <c r="H34" s="492"/>
+      <c r="I34" s="493"/>
       <c r="J34" s="114"/>
     </row>
     <row r="35" spans="1:10" ht="34.5" customHeight="1" thickBot="1">
@@ -18707,6 +18716,32 @@
     <row r="37" spans="1:10"/>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="E5:J5"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="E15:G15"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="D34:I34"/>
     <mergeCell ref="I17:J17"/>
@@ -18720,32 +18755,6 @@
     <mergeCell ref="B32:C33"/>
     <mergeCell ref="D32:I32"/>
     <mergeCell ref="D33:I33"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="E5:J5"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -18778,18 +18787,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="35.25" customHeight="1">
-      <c r="A1" s="474" t="s">
+      <c r="A1" s="528" t="s">
         <v>148</v>
       </c>
-      <c r="B1" s="474"/>
-      <c r="C1" s="474"/>
-      <c r="D1" s="474"/>
-      <c r="E1" s="474"/>
-      <c r="F1" s="474"/>
-      <c r="G1" s="474"/>
-      <c r="H1" s="474"/>
-      <c r="I1" s="474"/>
-      <c r="J1" s="474"/>
+      <c r="B1" s="528"/>
+      <c r="C1" s="528"/>
+      <c r="D1" s="528"/>
+      <c r="E1" s="528"/>
+      <c r="F1" s="528"/>
+      <c r="G1" s="528"/>
+      <c r="H1" s="528"/>
+      <c r="I1" s="528"/>
+      <c r="J1" s="528"/>
     </row>
     <row r="2" spans="1:10" ht="27.95" customHeight="1" thickBot="1">
       <c r="A2" s="37"/>
@@ -18803,11 +18812,11 @@
       <c r="I2" s="37"/>
     </row>
     <row r="3" spans="1:10" ht="27.95" customHeight="1" thickBot="1">
-      <c r="A3" s="567" t="s">
+      <c r="A3" s="592" t="s">
         <v>113</v>
       </c>
-      <c r="B3" s="568"/>
-      <c r="C3" s="569"/>
+      <c r="B3" s="593"/>
+      <c r="C3" s="594"/>
       <c r="D3" s="38"/>
       <c r="E3" s="38"/>
       <c r="F3" s="38"/>
@@ -18838,10 +18847,10 @@
       <c r="H4" s="122" t="s">
         <v>40</v>
       </c>
-      <c r="I4" s="570" t="s">
+      <c r="I4" s="595" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="571"/>
+      <c r="J4" s="596"/>
     </row>
     <row r="5" spans="1:10" ht="27.95" customHeight="1">
       <c r="A5" s="334" t="s">
@@ -18852,12 +18861,12 @@
         <v>37</v>
       </c>
       <c r="D5" s="125"/>
-      <c r="E5" s="554"/>
-      <c r="F5" s="555"/>
-      <c r="G5" s="555"/>
-      <c r="H5" s="555"/>
-      <c r="I5" s="555"/>
-      <c r="J5" s="556"/>
+      <c r="E5" s="562"/>
+      <c r="F5" s="563"/>
+      <c r="G5" s="563"/>
+      <c r="H5" s="563"/>
+      <c r="I5" s="563"/>
+      <c r="J5" s="564"/>
     </row>
     <row r="6" spans="1:10" ht="27.95" customHeight="1">
       <c r="A6" s="335"/>
@@ -18880,8 +18889,8 @@
         <f>IFERROR(E6*F6*G6,"")</f>
         <v/>
       </c>
-      <c r="I6" s="486"/>
-      <c r="J6" s="487"/>
+      <c r="I6" s="483"/>
+      <c r="J6" s="484"/>
     </row>
     <row r="7" spans="1:10" ht="27.95" customHeight="1">
       <c r="A7" s="336"/>
@@ -18904,8 +18913,8 @@
         <f>IFERROR(E7*F7*G7,"")</f>
         <v/>
       </c>
-      <c r="I7" s="486"/>
-      <c r="J7" s="487"/>
+      <c r="I7" s="483"/>
+      <c r="J7" s="484"/>
     </row>
     <row r="8" spans="1:10" ht="27.95" customHeight="1">
       <c r="A8" s="336"/>
@@ -18928,8 +18937,8 @@
         <f>IFERROR(E8*F8*G8,"")</f>
         <v/>
       </c>
-      <c r="I8" s="486"/>
-      <c r="J8" s="487"/>
+      <c r="I8" s="483"/>
+      <c r="J8" s="484"/>
     </row>
     <row r="9" spans="1:10" ht="27.95" customHeight="1">
       <c r="A9" s="336"/>
@@ -18952,22 +18961,22 @@
         <f>IFERROR(E9*F9*G9,"")</f>
         <v/>
       </c>
-      <c r="I9" s="486"/>
-      <c r="J9" s="487"/>
+      <c r="I9" s="483"/>
+      <c r="J9" s="484"/>
     </row>
     <row r="10" spans="1:10" ht="27.95" customHeight="1">
-      <c r="A10" s="577" t="s">
+      <c r="A10" s="584" t="s">
         <v>60</v>
       </c>
-      <c r="B10" s="578"/>
-      <c r="C10" s="579"/>
+      <c r="B10" s="585"/>
+      <c r="C10" s="586"/>
       <c r="D10" s="128"/>
-      <c r="E10" s="560"/>
-      <c r="F10" s="561"/>
+      <c r="E10" s="551"/>
+      <c r="F10" s="552"/>
       <c r="G10" s="56"/>
       <c r="H10" s="54"/>
-      <c r="I10" s="486"/>
-      <c r="J10" s="487"/>
+      <c r="I10" s="483"/>
+      <c r="J10" s="484"/>
     </row>
     <row r="11" spans="1:10" ht="27.95" customHeight="1">
       <c r="A11" s="334" t="s">
@@ -18978,16 +18987,16 @@
         <v>0</v>
       </c>
       <c r="D11" s="125"/>
-      <c r="E11" s="475" t="s">
+      <c r="E11" s="478" t="s">
         <v>52</v>
       </c>
-      <c r="F11" s="476"/>
+      <c r="F11" s="479"/>
       <c r="G11" s="72">
         <v>0</v>
       </c>
       <c r="H11" s="50"/>
-      <c r="I11" s="495"/>
-      <c r="J11" s="496"/>
+      <c r="I11" s="487"/>
+      <c r="J11" s="488"/>
     </row>
     <row r="12" spans="1:10" ht="27.95" customHeight="1">
       <c r="A12" s="334" t="s">
@@ -18998,16 +19007,16 @@
         <v>14</v>
       </c>
       <c r="D12" s="125"/>
-      <c r="E12" s="475" t="s">
+      <c r="E12" s="478" t="s">
         <v>52</v>
       </c>
-      <c r="F12" s="476"/>
+      <c r="F12" s="479"/>
       <c r="G12" s="72">
         <v>0</v>
       </c>
       <c r="H12" s="50"/>
-      <c r="I12" s="537"/>
-      <c r="J12" s="538"/>
+      <c r="I12" s="473"/>
+      <c r="J12" s="474"/>
     </row>
     <row r="13" spans="1:10" ht="27.95" customHeight="1">
       <c r="A13" s="334" t="s">
@@ -19018,16 +19027,16 @@
         <v>1</v>
       </c>
       <c r="D13" s="125"/>
-      <c r="E13" s="475" t="s">
+      <c r="E13" s="478" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="476"/>
+      <c r="F13" s="479"/>
       <c r="G13" s="49">
         <v>0</v>
       </c>
       <c r="H13" s="50"/>
-      <c r="I13" s="537"/>
-      <c r="J13" s="538"/>
+      <c r="I13" s="473"/>
+      <c r="J13" s="474"/>
     </row>
     <row r="14" spans="1:10" ht="27.95" customHeight="1">
       <c r="A14" s="337" t="s">
@@ -19038,14 +19047,14 @@
         <v>7</v>
       </c>
       <c r="D14" s="125"/>
-      <c r="E14" s="475" t="s">
+      <c r="E14" s="478" t="s">
         <v>65</v>
       </c>
-      <c r="F14" s="476"/>
+      <c r="F14" s="479"/>
       <c r="G14" s="49"/>
       <c r="H14" s="50"/>
-      <c r="I14" s="542"/>
-      <c r="J14" s="543"/>
+      <c r="I14" s="480"/>
+      <c r="J14" s="481"/>
     </row>
     <row r="15" spans="1:10" ht="27.95" customHeight="1">
       <c r="A15" s="337" t="s">
@@ -19056,12 +19065,12 @@
         <v>81</v>
       </c>
       <c r="D15" s="125"/>
-      <c r="E15" s="475"/>
-      <c r="F15" s="476"/>
-      <c r="G15" s="544"/>
+      <c r="E15" s="478"/>
+      <c r="F15" s="479"/>
+      <c r="G15" s="482"/>
       <c r="H15" s="51"/>
-      <c r="I15" s="542"/>
-      <c r="J15" s="543"/>
+      <c r="I15" s="480"/>
+      <c r="J15" s="481"/>
     </row>
     <row r="16" spans="1:10" ht="7.5" customHeight="1">
       <c r="A16" s="338"/>
@@ -19088,8 +19097,8 @@
       <c r="F17" s="136"/>
       <c r="G17" s="137"/>
       <c r="H17" s="138"/>
-      <c r="I17" s="575"/>
-      <c r="J17" s="576"/>
+      <c r="I17" s="590"/>
+      <c r="J17" s="591"/>
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" thickBot="1">
       <c r="A18" s="37"/>
@@ -19103,18 +19112,18 @@
       <c r="I18" s="37"/>
     </row>
     <row r="19" spans="1:10" ht="24" customHeight="1">
-      <c r="A19" s="572" t="s">
+      <c r="A19" s="587" t="s">
         <v>125</v>
       </c>
-      <c r="B19" s="573"/>
-      <c r="C19" s="573"/>
-      <c r="D19" s="573"/>
-      <c r="E19" s="573"/>
-      <c r="F19" s="573"/>
-      <c r="G19" s="573"/>
-      <c r="H19" s="573"/>
-      <c r="I19" s="573"/>
-      <c r="J19" s="574"/>
+      <c r="B19" s="588"/>
+      <c r="C19" s="588"/>
+      <c r="D19" s="588"/>
+      <c r="E19" s="588"/>
+      <c r="F19" s="588"/>
+      <c r="G19" s="588"/>
+      <c r="H19" s="588"/>
+      <c r="I19" s="588"/>
+      <c r="J19" s="589"/>
     </row>
     <row r="20" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A20" s="103"/>
@@ -19214,16 +19223,16 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="110"/>
-      <c r="B27" s="594" t="s">
+      <c r="B27" s="579" t="s">
         <v>192</v>
       </c>
-      <c r="C27" s="595"/>
-      <c r="D27" s="595"/>
-      <c r="E27" s="587"/>
-      <c r="F27" s="586" t="s">
+      <c r="C27" s="580"/>
+      <c r="D27" s="580"/>
+      <c r="E27" s="572"/>
+      <c r="F27" s="571" t="s">
         <v>138</v>
       </c>
-      <c r="G27" s="587"/>
+      <c r="G27" s="572"/>
       <c r="H27" s="197" t="s">
         <v>143</v>
       </c>
@@ -19234,16 +19243,16 @@
     </row>
     <row r="28" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A28" s="112"/>
-      <c r="B28" s="596" t="s">
+      <c r="B28" s="581" t="s">
         <v>135</v>
       </c>
-      <c r="C28" s="597"/>
-      <c r="D28" s="597"/>
-      <c r="E28" s="598"/>
-      <c r="F28" s="588" t="s">
+      <c r="C28" s="582"/>
+      <c r="D28" s="582"/>
+      <c r="E28" s="583"/>
+      <c r="F28" s="573" t="s">
         <v>139</v>
       </c>
-      <c r="G28" s="589"/>
+      <c r="G28" s="574"/>
       <c r="H28" s="140" t="s">
         <v>144</v>
       </c>
@@ -19254,16 +19263,16 @@
     </row>
     <row r="29" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A29" s="112"/>
-      <c r="B29" s="580" t="s">
+      <c r="B29" s="565" t="s">
         <v>136</v>
       </c>
-      <c r="C29" s="581"/>
-      <c r="D29" s="581"/>
-      <c r="E29" s="582"/>
-      <c r="F29" s="590" t="s">
+      <c r="C29" s="566"/>
+      <c r="D29" s="566"/>
+      <c r="E29" s="567"/>
+      <c r="F29" s="575" t="s">
         <v>140</v>
       </c>
-      <c r="G29" s="591"/>
+      <c r="G29" s="576"/>
       <c r="H29" s="141" t="s">
         <v>144</v>
       </c>
@@ -19274,16 +19283,16 @@
     </row>
     <row r="30" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A30" s="112"/>
-      <c r="B30" s="580" t="s">
+      <c r="B30" s="565" t="s">
         <v>137</v>
       </c>
-      <c r="C30" s="581"/>
-      <c r="D30" s="581"/>
-      <c r="E30" s="582"/>
-      <c r="F30" s="590" t="s">
+      <c r="C30" s="566"/>
+      <c r="D30" s="566"/>
+      <c r="E30" s="567"/>
+      <c r="F30" s="575" t="s">
         <v>141</v>
       </c>
-      <c r="G30" s="591"/>
+      <c r="G30" s="576"/>
       <c r="H30" s="141" t="s">
         <v>144</v>
       </c>
@@ -19294,16 +19303,16 @@
     </row>
     <row r="31" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A31" s="112"/>
-      <c r="B31" s="580" t="s">
+      <c r="B31" s="565" t="s">
         <v>145</v>
       </c>
-      <c r="C31" s="581"/>
-      <c r="D31" s="581"/>
-      <c r="E31" s="582"/>
-      <c r="F31" s="590" t="s">
+      <c r="C31" s="566"/>
+      <c r="D31" s="566"/>
+      <c r="E31" s="567"/>
+      <c r="F31" s="575" t="s">
         <v>142</v>
       </c>
-      <c r="G31" s="591"/>
+      <c r="G31" s="576"/>
       <c r="H31" s="141" t="s">
         <v>144</v>
       </c>
@@ -19314,16 +19323,16 @@
     </row>
     <row r="32" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A32" s="112"/>
-      <c r="B32" s="583" t="s">
+      <c r="B32" s="568" t="s">
         <v>263</v>
       </c>
-      <c r="C32" s="584"/>
-      <c r="D32" s="584"/>
-      <c r="E32" s="585"/>
-      <c r="F32" s="592" t="s">
+      <c r="C32" s="569"/>
+      <c r="D32" s="569"/>
+      <c r="E32" s="570"/>
+      <c r="F32" s="577" t="s">
         <v>142</v>
       </c>
-      <c r="G32" s="593"/>
+      <c r="G32" s="578"/>
       <c r="H32" s="198" t="s">
         <v>144</v>
       </c>
@@ -19377,6 +19386,29 @@
     <row r="38" spans="1:10"/>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="E5:J5"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="I11:J11"/>
     <mergeCell ref="B31:E31"/>
     <mergeCell ref="B32:E32"/>
     <mergeCell ref="F27:G27"/>
@@ -19389,29 +19421,6 @@
     <mergeCell ref="B28:E28"/>
     <mergeCell ref="B29:E29"/>
     <mergeCell ref="B30:E30"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="E5:J5"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I9:J9"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -19437,33 +19446,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="35.1" customHeight="1">
-      <c r="A1" s="644" t="s">
+      <c r="A1" s="604" t="s">
         <v>177</v>
       </c>
-      <c r="B1" s="645"/>
-      <c r="C1" s="645"/>
-      <c r="D1" s="645"/>
-      <c r="E1" s="645"/>
-      <c r="F1" s="645"/>
-      <c r="G1" s="645"/>
-      <c r="H1" s="645"/>
-      <c r="I1" s="645"/>
-      <c r="J1" s="645"/>
-      <c r="K1" s="645"/>
-      <c r="L1" s="645"/>
-      <c r="M1" s="645"/>
-      <c r="N1" s="645"/>
-      <c r="O1" s="645"/>
-      <c r="P1" s="645"/>
-      <c r="Q1" s="645"/>
-      <c r="R1" s="645"/>
-      <c r="S1" s="645"/>
-      <c r="T1" s="645"/>
-      <c r="U1" s="645"/>
-      <c r="V1" s="645"/>
-      <c r="W1" s="645"/>
-      <c r="X1" s="645"/>
-      <c r="Y1" s="646"/>
+      <c r="B1" s="605"/>
+      <c r="C1" s="605"/>
+      <c r="D1" s="605"/>
+      <c r="E1" s="605"/>
+      <c r="F1" s="605"/>
+      <c r="G1" s="605"/>
+      <c r="H1" s="605"/>
+      <c r="I1" s="605"/>
+      <c r="J1" s="605"/>
+      <c r="K1" s="605"/>
+      <c r="L1" s="605"/>
+      <c r="M1" s="605"/>
+      <c r="N1" s="605"/>
+      <c r="O1" s="605"/>
+      <c r="P1" s="605"/>
+      <c r="Q1" s="605"/>
+      <c r="R1" s="605"/>
+      <c r="S1" s="605"/>
+      <c r="T1" s="605"/>
+      <c r="U1" s="605"/>
+      <c r="V1" s="605"/>
+      <c r="W1" s="605"/>
+      <c r="X1" s="605"/>
+      <c r="Y1" s="606"/>
     </row>
     <row r="2" spans="1:26" s="152" customFormat="1" ht="21" customHeight="1">
       <c r="A2" s="175"/>
@@ -19489,54 +19498,54 @@
     </row>
     <row r="4" spans="1:26" s="152" customFormat="1" ht="21" customHeight="1">
       <c r="A4" s="177"/>
-      <c r="B4" s="599" t="s">
+      <c r="B4" s="631" t="s">
         <v>149</v>
       </c>
-      <c r="C4" s="600"/>
-      <c r="D4" s="600"/>
-      <c r="E4" s="600"/>
-      <c r="F4" s="600"/>
-      <c r="G4" s="600"/>
-      <c r="H4" s="600"/>
-      <c r="I4" s="600"/>
-      <c r="J4" s="600"/>
-      <c r="K4" s="601"/>
-      <c r="O4" s="599" t="s">
+      <c r="C4" s="632"/>
+      <c r="D4" s="632"/>
+      <c r="E4" s="632"/>
+      <c r="F4" s="632"/>
+      <c r="G4" s="632"/>
+      <c r="H4" s="632"/>
+      <c r="I4" s="632"/>
+      <c r="J4" s="632"/>
+      <c r="K4" s="633"/>
+      <c r="O4" s="631" t="s">
         <v>163</v>
       </c>
-      <c r="P4" s="600"/>
-      <c r="Q4" s="600"/>
-      <c r="R4" s="600"/>
-      <c r="S4" s="600"/>
-      <c r="T4" s="600"/>
-      <c r="U4" s="600"/>
-      <c r="V4" s="600"/>
-      <c r="W4" s="600"/>
-      <c r="X4" s="601"/>
+      <c r="P4" s="632"/>
+      <c r="Q4" s="632"/>
+      <c r="R4" s="632"/>
+      <c r="S4" s="632"/>
+      <c r="T4" s="632"/>
+      <c r="U4" s="632"/>
+      <c r="V4" s="632"/>
+      <c r="W4" s="632"/>
+      <c r="X4" s="633"/>
       <c r="Y4" s="176"/>
     </row>
     <row r="5" spans="1:26" s="152" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A5" s="175"/>
-      <c r="B5" s="602"/>
-      <c r="C5" s="603"/>
-      <c r="D5" s="603"/>
-      <c r="E5" s="603"/>
-      <c r="F5" s="603"/>
-      <c r="G5" s="603"/>
-      <c r="H5" s="603"/>
-      <c r="I5" s="603"/>
-      <c r="J5" s="603"/>
-      <c r="K5" s="604"/>
-      <c r="O5" s="602"/>
-      <c r="P5" s="603"/>
-      <c r="Q5" s="603"/>
-      <c r="R5" s="603"/>
-      <c r="S5" s="603"/>
-      <c r="T5" s="603"/>
-      <c r="U5" s="603"/>
-      <c r="V5" s="603"/>
-      <c r="W5" s="603"/>
-      <c r="X5" s="604"/>
+      <c r="B5" s="634"/>
+      <c r="C5" s="635"/>
+      <c r="D5" s="635"/>
+      <c r="E5" s="635"/>
+      <c r="F5" s="635"/>
+      <c r="G5" s="635"/>
+      <c r="H5" s="635"/>
+      <c r="I5" s="635"/>
+      <c r="J5" s="635"/>
+      <c r="K5" s="636"/>
+      <c r="O5" s="634"/>
+      <c r="P5" s="635"/>
+      <c r="Q5" s="635"/>
+      <c r="R5" s="635"/>
+      <c r="S5" s="635"/>
+      <c r="T5" s="635"/>
+      <c r="U5" s="635"/>
+      <c r="V5" s="635"/>
+      <c r="W5" s="635"/>
+      <c r="X5" s="636"/>
       <c r="Y5" s="176"/>
     </row>
     <row r="6" spans="1:26" s="152" customFormat="1" ht="21" customHeight="1" thickBot="1">
@@ -19558,21 +19567,21 @@
       <c r="D7" s="148"/>
       <c r="E7" s="148"/>
       <c r="F7" s="149"/>
-      <c r="G7" s="614" t="s">
+      <c r="G7" s="640" t="s">
         <v>150</v>
       </c>
-      <c r="H7" s="615"/>
-      <c r="I7" s="615"/>
-      <c r="J7" s="615"/>
-      <c r="K7" s="615"/>
-      <c r="L7" s="615"/>
-      <c r="M7" s="615"/>
-      <c r="N7" s="615"/>
-      <c r="O7" s="615"/>
-      <c r="P7" s="615"/>
-      <c r="Q7" s="615"/>
-      <c r="R7" s="615"/>
-      <c r="S7" s="616"/>
+      <c r="H7" s="641"/>
+      <c r="I7" s="641"/>
+      <c r="J7" s="641"/>
+      <c r="K7" s="641"/>
+      <c r="L7" s="641"/>
+      <c r="M7" s="641"/>
+      <c r="N7" s="641"/>
+      <c r="O7" s="641"/>
+      <c r="P7" s="641"/>
+      <c r="Q7" s="641"/>
+      <c r="R7" s="641"/>
+      <c r="S7" s="642"/>
       <c r="T7" s="193"/>
       <c r="U7" s="153"/>
       <c r="V7" s="153"/>
@@ -19588,19 +19597,19 @@
       <c r="D8" s="148"/>
       <c r="E8" s="148"/>
       <c r="F8" s="149"/>
-      <c r="G8" s="617"/>
-      <c r="H8" s="618"/>
-      <c r="I8" s="618"/>
-      <c r="J8" s="618"/>
-      <c r="K8" s="618"/>
-      <c r="L8" s="618"/>
-      <c r="M8" s="618"/>
-      <c r="N8" s="618"/>
-      <c r="O8" s="618"/>
-      <c r="P8" s="618"/>
-      <c r="Q8" s="618"/>
-      <c r="R8" s="618"/>
-      <c r="S8" s="619"/>
+      <c r="G8" s="643"/>
+      <c r="H8" s="644"/>
+      <c r="I8" s="644"/>
+      <c r="J8" s="644"/>
+      <c r="K8" s="644"/>
+      <c r="L8" s="644"/>
+      <c r="M8" s="644"/>
+      <c r="N8" s="644"/>
+      <c r="O8" s="644"/>
+      <c r="P8" s="644"/>
+      <c r="Q8" s="644"/>
+      <c r="R8" s="644"/>
+      <c r="S8" s="645"/>
       <c r="T8" s="193"/>
       <c r="U8" s="153"/>
       <c r="V8" s="153"/>
@@ -19616,19 +19625,19 @@
       <c r="D9" s="148"/>
       <c r="E9" s="148"/>
       <c r="F9" s="149"/>
-      <c r="G9" s="620"/>
-      <c r="H9" s="621"/>
-      <c r="I9" s="621"/>
-      <c r="J9" s="621"/>
-      <c r="K9" s="621"/>
-      <c r="L9" s="621"/>
-      <c r="M9" s="621"/>
-      <c r="N9" s="621"/>
-      <c r="O9" s="621"/>
-      <c r="P9" s="621"/>
-      <c r="Q9" s="621"/>
-      <c r="R9" s="621"/>
-      <c r="S9" s="622"/>
+      <c r="G9" s="646"/>
+      <c r="H9" s="647"/>
+      <c r="I9" s="647"/>
+      <c r="J9" s="647"/>
+      <c r="K9" s="647"/>
+      <c r="L9" s="647"/>
+      <c r="M9" s="647"/>
+      <c r="N9" s="647"/>
+      <c r="O9" s="647"/>
+      <c r="P9" s="647"/>
+      <c r="Q9" s="647"/>
+      <c r="R9" s="647"/>
+      <c r="S9" s="648"/>
       <c r="T9" s="193"/>
       <c r="U9" s="153"/>
       <c r="V9" s="153"/>
@@ -19679,59 +19688,59 @@
     </row>
     <row r="12" spans="1:26" s="152" customFormat="1" ht="21" customHeight="1">
       <c r="A12" s="178"/>
-      <c r="B12" s="637" t="s">
+      <c r="B12" s="627" t="s">
         <v>151</v>
       </c>
-      <c r="C12" s="629"/>
-      <c r="D12" s="629"/>
-      <c r="E12" s="629"/>
-      <c r="F12" s="629"/>
-      <c r="G12" s="629"/>
-      <c r="H12" s="629"/>
-      <c r="I12" s="629"/>
-      <c r="J12" s="629"/>
-      <c r="K12" s="630"/>
-      <c r="O12" s="637" t="s">
+      <c r="C12" s="610"/>
+      <c r="D12" s="610"/>
+      <c r="E12" s="610"/>
+      <c r="F12" s="610"/>
+      <c r="G12" s="610"/>
+      <c r="H12" s="610"/>
+      <c r="I12" s="610"/>
+      <c r="J12" s="610"/>
+      <c r="K12" s="611"/>
+      <c r="O12" s="627" t="s">
         <v>162</v>
       </c>
-      <c r="P12" s="629"/>
-      <c r="Q12" s="629"/>
-      <c r="R12" s="629"/>
-      <c r="S12" s="629"/>
-      <c r="T12" s="629"/>
-      <c r="U12" s="629"/>
-      <c r="V12" s="629"/>
-      <c r="W12" s="629"/>
-      <c r="X12" s="630"/>
+      <c r="P12" s="610"/>
+      <c r="Q12" s="610"/>
+      <c r="R12" s="610"/>
+      <c r="S12" s="610"/>
+      <c r="T12" s="610"/>
+      <c r="U12" s="610"/>
+      <c r="V12" s="610"/>
+      <c r="W12" s="610"/>
+      <c r="X12" s="611"/>
       <c r="Y12" s="179"/>
       <c r="Z12" s="153"/>
     </row>
     <row r="13" spans="1:26" s="152" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A13" s="178"/>
-      <c r="B13" s="634" t="s">
+      <c r="B13" s="598" t="s">
         <v>161</v>
       </c>
-      <c r="C13" s="635"/>
-      <c r="D13" s="635"/>
-      <c r="E13" s="635"/>
-      <c r="F13" s="635"/>
-      <c r="G13" s="635"/>
-      <c r="H13" s="635"/>
-      <c r="I13" s="635"/>
-      <c r="J13" s="635"/>
-      <c r="K13" s="636"/>
-      <c r="O13" s="634" t="s">
+      <c r="C13" s="599"/>
+      <c r="D13" s="599"/>
+      <c r="E13" s="599"/>
+      <c r="F13" s="599"/>
+      <c r="G13" s="599"/>
+      <c r="H13" s="599"/>
+      <c r="I13" s="599"/>
+      <c r="J13" s="599"/>
+      <c r="K13" s="600"/>
+      <c r="O13" s="598" t="s">
         <v>161</v>
       </c>
-      <c r="P13" s="635"/>
-      <c r="Q13" s="635"/>
-      <c r="R13" s="635"/>
-      <c r="S13" s="635"/>
-      <c r="T13" s="635"/>
-      <c r="U13" s="635"/>
-      <c r="V13" s="635"/>
-      <c r="W13" s="635"/>
-      <c r="X13" s="636"/>
+      <c r="P13" s="599"/>
+      <c r="Q13" s="599"/>
+      <c r="R13" s="599"/>
+      <c r="S13" s="599"/>
+      <c r="T13" s="599"/>
+      <c r="U13" s="599"/>
+      <c r="V13" s="599"/>
+      <c r="W13" s="599"/>
+      <c r="X13" s="600"/>
       <c r="Y13" s="179"/>
       <c r="Z13" s="153"/>
     </row>
@@ -19779,92 +19788,92 @@
     </row>
     <row r="16" spans="1:26" s="152" customFormat="1" ht="21" customHeight="1">
       <c r="A16" s="180"/>
-      <c r="B16" s="605" t="s">
+      <c r="B16" s="615" t="s">
         <v>152</v>
       </c>
-      <c r="C16" s="606"/>
-      <c r="D16" s="606"/>
-      <c r="E16" s="607"/>
+      <c r="C16" s="616"/>
+      <c r="D16" s="616"/>
+      <c r="E16" s="617"/>
       <c r="F16" s="101"/>
       <c r="G16" s="145"/>
-      <c r="H16" s="605" t="s">
+      <c r="H16" s="615" t="s">
         <v>154</v>
       </c>
-      <c r="I16" s="606"/>
-      <c r="J16" s="606"/>
-      <c r="K16" s="607"/>
-      <c r="O16" s="605" t="s">
+      <c r="I16" s="616"/>
+      <c r="J16" s="616"/>
+      <c r="K16" s="617"/>
+      <c r="O16" s="615" t="s">
         <v>164</v>
       </c>
-      <c r="P16" s="606"/>
-      <c r="Q16" s="606"/>
-      <c r="R16" s="607"/>
+      <c r="P16" s="616"/>
+      <c r="Q16" s="616"/>
+      <c r="R16" s="617"/>
       <c r="S16" s="153"/>
       <c r="T16" s="153"/>
-      <c r="U16" s="605" t="s">
+      <c r="U16" s="615" t="s">
         <v>167</v>
       </c>
-      <c r="V16" s="606"/>
-      <c r="W16" s="606"/>
-      <c r="X16" s="607"/>
+      <c r="V16" s="616"/>
+      <c r="W16" s="616"/>
+      <c r="X16" s="617"/>
       <c r="Y16" s="179"/>
       <c r="Z16" s="153"/>
     </row>
     <row r="17" spans="1:26" s="152" customFormat="1" ht="21" customHeight="1">
       <c r="A17" s="180"/>
-      <c r="B17" s="608" t="s">
+      <c r="B17" s="618" t="s">
         <v>153</v>
       </c>
-      <c r="C17" s="609"/>
-      <c r="D17" s="609"/>
-      <c r="E17" s="610"/>
+      <c r="C17" s="619"/>
+      <c r="D17" s="619"/>
+      <c r="E17" s="620"/>
       <c r="F17" s="38"/>
       <c r="G17" s="38"/>
-      <c r="H17" s="608" t="s">
+      <c r="H17" s="618" t="s">
         <v>155</v>
       </c>
-      <c r="I17" s="609"/>
-      <c r="J17" s="609"/>
-      <c r="K17" s="610"/>
-      <c r="O17" s="608" t="s">
+      <c r="I17" s="619"/>
+      <c r="J17" s="619"/>
+      <c r="K17" s="620"/>
+      <c r="O17" s="618" t="s">
         <v>165</v>
       </c>
-      <c r="P17" s="609"/>
-      <c r="Q17" s="609"/>
-      <c r="R17" s="610"/>
+      <c r="P17" s="619"/>
+      <c r="Q17" s="619"/>
+      <c r="R17" s="620"/>
       <c r="S17" s="153"/>
       <c r="T17" s="153"/>
-      <c r="U17" s="608" t="s">
+      <c r="U17" s="618" t="s">
         <v>168</v>
       </c>
-      <c r="V17" s="623"/>
-      <c r="W17" s="623"/>
-      <c r="X17" s="624"/>
+      <c r="V17" s="622"/>
+      <c r="W17" s="622"/>
+      <c r="X17" s="623"/>
       <c r="Y17" s="179"/>
       <c r="Z17" s="153"/>
     </row>
     <row r="18" spans="1:26" s="152" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A18" s="178"/>
-      <c r="B18" s="611"/>
-      <c r="C18" s="612"/>
-      <c r="D18" s="612"/>
-      <c r="E18" s="613"/>
+      <c r="B18" s="637"/>
+      <c r="C18" s="638"/>
+      <c r="D18" s="638"/>
+      <c r="E18" s="639"/>
       <c r="F18" s="147"/>
       <c r="G18" s="146"/>
-      <c r="H18" s="611"/>
-      <c r="I18" s="612"/>
-      <c r="J18" s="612"/>
-      <c r="K18" s="613"/>
-      <c r="O18" s="650"/>
-      <c r="P18" s="609"/>
-      <c r="Q18" s="609"/>
-      <c r="R18" s="610"/>
+      <c r="H18" s="637"/>
+      <c r="I18" s="638"/>
+      <c r="J18" s="638"/>
+      <c r="K18" s="639"/>
+      <c r="O18" s="621"/>
+      <c r="P18" s="619"/>
+      <c r="Q18" s="619"/>
+      <c r="R18" s="620"/>
       <c r="S18" s="153"/>
       <c r="T18" s="153"/>
-      <c r="U18" s="608"/>
-      <c r="V18" s="623"/>
-      <c r="W18" s="623"/>
-      <c r="X18" s="624"/>
+      <c r="U18" s="618"/>
+      <c r="V18" s="622"/>
+      <c r="W18" s="622"/>
+      <c r="X18" s="623"/>
       <c r="Y18" s="179"/>
       <c r="Z18" s="153"/>
     </row>
@@ -19878,57 +19887,57 @@
       <c r="G19" s="144"/>
       <c r="H19" s="144"/>
       <c r="J19" s="169"/>
-      <c r="O19" s="608" t="s">
+      <c r="O19" s="618" t="s">
         <v>166</v>
       </c>
-      <c r="P19" s="623"/>
-      <c r="Q19" s="623"/>
-      <c r="R19" s="624"/>
+      <c r="P19" s="622"/>
+      <c r="Q19" s="622"/>
+      <c r="R19" s="623"/>
       <c r="S19" s="153"/>
       <c r="T19" s="153"/>
-      <c r="U19" s="608"/>
-      <c r="V19" s="623"/>
-      <c r="W19" s="623"/>
-      <c r="X19" s="624"/>
+      <c r="U19" s="618"/>
+      <c r="V19" s="622"/>
+      <c r="W19" s="622"/>
+      <c r="X19" s="623"/>
       <c r="Y19" s="179"/>
       <c r="Z19" s="153"/>
     </row>
     <row r="20" spans="1:26" s="152" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A20" s="110"/>
-      <c r="B20" s="637" t="s">
+      <c r="B20" s="627" t="s">
         <v>156</v>
       </c>
-      <c r="C20" s="629"/>
-      <c r="D20" s="629"/>
-      <c r="E20" s="629"/>
-      <c r="F20" s="629"/>
-      <c r="G20" s="629"/>
-      <c r="H20" s="629"/>
-      <c r="I20" s="629"/>
-      <c r="J20" s="629"/>
-      <c r="K20" s="630"/>
-      <c r="O20" s="625"/>
-      <c r="P20" s="626"/>
-      <c r="Q20" s="626"/>
-      <c r="R20" s="627"/>
-      <c r="U20" s="625"/>
-      <c r="V20" s="626"/>
-      <c r="W20" s="626"/>
-      <c r="X20" s="627"/>
+      <c r="C20" s="610"/>
+      <c r="D20" s="610"/>
+      <c r="E20" s="610"/>
+      <c r="F20" s="610"/>
+      <c r="G20" s="610"/>
+      <c r="H20" s="610"/>
+      <c r="I20" s="610"/>
+      <c r="J20" s="610"/>
+      <c r="K20" s="611"/>
+      <c r="O20" s="624"/>
+      <c r="P20" s="625"/>
+      <c r="Q20" s="625"/>
+      <c r="R20" s="626"/>
+      <c r="U20" s="624"/>
+      <c r="V20" s="625"/>
+      <c r="W20" s="625"/>
+      <c r="X20" s="626"/>
       <c r="Y20" s="176"/>
     </row>
     <row r="21" spans="1:26" s="152" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A21" s="103"/>
-      <c r="B21" s="638"/>
-      <c r="C21" s="639"/>
-      <c r="D21" s="639"/>
-      <c r="E21" s="639"/>
-      <c r="F21" s="639"/>
-      <c r="G21" s="639"/>
-      <c r="H21" s="639"/>
-      <c r="I21" s="639"/>
-      <c r="J21" s="639"/>
-      <c r="K21" s="640"/>
+      <c r="B21" s="628"/>
+      <c r="C21" s="629"/>
+      <c r="D21" s="629"/>
+      <c r="E21" s="629"/>
+      <c r="F21" s="629"/>
+      <c r="G21" s="629"/>
+      <c r="H21" s="629"/>
+      <c r="I21" s="629"/>
+      <c r="J21" s="629"/>
+      <c r="K21" s="630"/>
       <c r="Q21" s="171"/>
       <c r="W21" s="171"/>
       <c r="Y21" s="176"/>
@@ -19963,82 +19972,82 @@
     </row>
     <row r="24" spans="1:26" s="152" customFormat="1" ht="21" customHeight="1">
       <c r="A24" s="181"/>
-      <c r="B24" s="628" t="s">
+      <c r="B24" s="601" t="s">
         <v>157</v>
       </c>
-      <c r="C24" s="629"/>
-      <c r="D24" s="629"/>
-      <c r="E24" s="629"/>
-      <c r="F24" s="629"/>
-      <c r="G24" s="629"/>
-      <c r="H24" s="629"/>
-      <c r="I24" s="629"/>
-      <c r="J24" s="629"/>
-      <c r="K24" s="630"/>
-      <c r="O24" s="628" t="s">
+      <c r="C24" s="610"/>
+      <c r="D24" s="610"/>
+      <c r="E24" s="610"/>
+      <c r="F24" s="610"/>
+      <c r="G24" s="610"/>
+      <c r="H24" s="610"/>
+      <c r="I24" s="610"/>
+      <c r="J24" s="610"/>
+      <c r="K24" s="611"/>
+      <c r="O24" s="601" t="s">
         <v>169</v>
       </c>
-      <c r="P24" s="629"/>
-      <c r="Q24" s="629"/>
-      <c r="R24" s="629"/>
-      <c r="S24" s="629"/>
-      <c r="T24" s="629"/>
-      <c r="U24" s="629"/>
-      <c r="V24" s="629"/>
-      <c r="W24" s="629"/>
-      <c r="X24" s="630"/>
+      <c r="P24" s="610"/>
+      <c r="Q24" s="610"/>
+      <c r="R24" s="610"/>
+      <c r="S24" s="610"/>
+      <c r="T24" s="610"/>
+      <c r="U24" s="610"/>
+      <c r="V24" s="610"/>
+      <c r="W24" s="610"/>
+      <c r="X24" s="611"/>
       <c r="Y24" s="176"/>
     </row>
     <row r="25" spans="1:26" s="152" customFormat="1" ht="21" customHeight="1">
       <c r="A25" s="182"/>
-      <c r="B25" s="631"/>
-      <c r="C25" s="632"/>
-      <c r="D25" s="632"/>
-      <c r="E25" s="632"/>
-      <c r="F25" s="632"/>
-      <c r="G25" s="632"/>
-      <c r="H25" s="632"/>
-      <c r="I25" s="632"/>
-      <c r="J25" s="632"/>
-      <c r="K25" s="633"/>
-      <c r="O25" s="631"/>
-      <c r="P25" s="632"/>
-      <c r="Q25" s="632"/>
-      <c r="R25" s="632"/>
-      <c r="S25" s="632"/>
-      <c r="T25" s="632"/>
-      <c r="U25" s="632"/>
-      <c r="V25" s="632"/>
-      <c r="W25" s="632"/>
-      <c r="X25" s="633"/>
+      <c r="B25" s="612"/>
+      <c r="C25" s="613"/>
+      <c r="D25" s="613"/>
+      <c r="E25" s="613"/>
+      <c r="F25" s="613"/>
+      <c r="G25" s="613"/>
+      <c r="H25" s="613"/>
+      <c r="I25" s="613"/>
+      <c r="J25" s="613"/>
+      <c r="K25" s="614"/>
+      <c r="O25" s="612"/>
+      <c r="P25" s="613"/>
+      <c r="Q25" s="613"/>
+      <c r="R25" s="613"/>
+      <c r="S25" s="613"/>
+      <c r="T25" s="613"/>
+      <c r="U25" s="613"/>
+      <c r="V25" s="613"/>
+      <c r="W25" s="613"/>
+      <c r="X25" s="614"/>
       <c r="Y25" s="176"/>
     </row>
     <row r="26" spans="1:26" s="152" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A26" s="103"/>
-      <c r="B26" s="634" t="s">
+      <c r="B26" s="598" t="s">
         <v>158</v>
       </c>
-      <c r="C26" s="635"/>
-      <c r="D26" s="635"/>
-      <c r="E26" s="635"/>
-      <c r="F26" s="635"/>
-      <c r="G26" s="635"/>
-      <c r="H26" s="635"/>
-      <c r="I26" s="635"/>
-      <c r="J26" s="635"/>
-      <c r="K26" s="636"/>
-      <c r="O26" s="634" t="s">
+      <c r="C26" s="599"/>
+      <c r="D26" s="599"/>
+      <c r="E26" s="599"/>
+      <c r="F26" s="599"/>
+      <c r="G26" s="599"/>
+      <c r="H26" s="599"/>
+      <c r="I26" s="599"/>
+      <c r="J26" s="599"/>
+      <c r="K26" s="600"/>
+      <c r="O26" s="598" t="s">
         <v>158</v>
       </c>
-      <c r="P26" s="635"/>
-      <c r="Q26" s="635"/>
-      <c r="R26" s="635"/>
-      <c r="S26" s="635"/>
-      <c r="T26" s="635"/>
-      <c r="U26" s="635"/>
-      <c r="V26" s="635"/>
-      <c r="W26" s="635"/>
-      <c r="X26" s="636"/>
+      <c r="P26" s="599"/>
+      <c r="Q26" s="599"/>
+      <c r="R26" s="599"/>
+      <c r="S26" s="599"/>
+      <c r="T26" s="599"/>
+      <c r="U26" s="599"/>
+      <c r="V26" s="599"/>
+      <c r="W26" s="599"/>
+      <c r="X26" s="600"/>
       <c r="Y26" s="176"/>
     </row>
     <row r="27" spans="1:26" s="152" customFormat="1" ht="12">
@@ -20069,72 +20078,72 @@
     </row>
     <row r="29" spans="1:26" s="152" customFormat="1" ht="12">
       <c r="A29" s="110"/>
-      <c r="B29" s="628" t="s">
+      <c r="B29" s="601" t="s">
         <v>159</v>
       </c>
-      <c r="C29" s="642"/>
-      <c r="D29" s="642"/>
-      <c r="E29" s="642"/>
-      <c r="F29" s="642"/>
-      <c r="G29" s="642"/>
-      <c r="H29" s="642"/>
-      <c r="I29" s="642"/>
-      <c r="J29" s="642"/>
-      <c r="K29" s="643"/>
-      <c r="O29" s="628" t="s">
+      <c r="C29" s="602"/>
+      <c r="D29" s="602"/>
+      <c r="E29" s="602"/>
+      <c r="F29" s="602"/>
+      <c r="G29" s="602"/>
+      <c r="H29" s="602"/>
+      <c r="I29" s="602"/>
+      <c r="J29" s="602"/>
+      <c r="K29" s="603"/>
+      <c r="O29" s="601" t="s">
         <v>171</v>
       </c>
-      <c r="P29" s="642"/>
-      <c r="Q29" s="642"/>
-      <c r="R29" s="642"/>
-      <c r="S29" s="642"/>
-      <c r="T29" s="642"/>
-      <c r="U29" s="642"/>
-      <c r="V29" s="642"/>
-      <c r="W29" s="642"/>
-      <c r="X29" s="643"/>
+      <c r="P29" s="602"/>
+      <c r="Q29" s="602"/>
+      <c r="R29" s="602"/>
+      <c r="S29" s="602"/>
+      <c r="T29" s="602"/>
+      <c r="U29" s="602"/>
+      <c r="V29" s="602"/>
+      <c r="W29" s="602"/>
+      <c r="X29" s="603"/>
       <c r="Y29" s="176"/>
     </row>
     <row r="30" spans="1:26" s="152" customFormat="1" ht="23.25" customHeight="1" thickBot="1">
       <c r="A30" s="110"/>
-      <c r="B30" s="647"/>
-      <c r="C30" s="648"/>
-      <c r="D30" s="648"/>
-      <c r="E30" s="648"/>
-      <c r="F30" s="648"/>
-      <c r="G30" s="648"/>
-      <c r="H30" s="648"/>
-      <c r="I30" s="648"/>
-      <c r="J30" s="648"/>
-      <c r="K30" s="649"/>
-      <c r="O30" s="634" t="s">
+      <c r="B30" s="607"/>
+      <c r="C30" s="608"/>
+      <c r="D30" s="608"/>
+      <c r="E30" s="608"/>
+      <c r="F30" s="608"/>
+      <c r="G30" s="608"/>
+      <c r="H30" s="608"/>
+      <c r="I30" s="608"/>
+      <c r="J30" s="608"/>
+      <c r="K30" s="609"/>
+      <c r="O30" s="598" t="s">
         <v>173</v>
       </c>
-      <c r="P30" s="635"/>
-      <c r="Q30" s="635"/>
-      <c r="R30" s="635"/>
-      <c r="S30" s="635"/>
-      <c r="T30" s="635"/>
-      <c r="U30" s="635"/>
-      <c r="V30" s="635"/>
-      <c r="W30" s="635"/>
-      <c r="X30" s="636"/>
+      <c r="P30" s="599"/>
+      <c r="Q30" s="599"/>
+      <c r="R30" s="599"/>
+      <c r="S30" s="599"/>
+      <c r="T30" s="599"/>
+      <c r="U30" s="599"/>
+      <c r="V30" s="599"/>
+      <c r="W30" s="599"/>
+      <c r="X30" s="600"/>
       <c r="Y30" s="176"/>
     </row>
     <row r="31" spans="1:26" s="152" customFormat="1" ht="12.75" thickBot="1">
       <c r="A31" s="110"/>
-      <c r="B31" s="634" t="s">
+      <c r="B31" s="598" t="s">
         <v>160</v>
       </c>
-      <c r="C31" s="635"/>
-      <c r="D31" s="635"/>
-      <c r="E31" s="635"/>
-      <c r="F31" s="635"/>
-      <c r="G31" s="635"/>
-      <c r="H31" s="635"/>
-      <c r="I31" s="635"/>
-      <c r="J31" s="635"/>
-      <c r="K31" s="636"/>
+      <c r="C31" s="599"/>
+      <c r="D31" s="599"/>
+      <c r="E31" s="599"/>
+      <c r="F31" s="599"/>
+      <c r="G31" s="599"/>
+      <c r="H31" s="599"/>
+      <c r="I31" s="599"/>
+      <c r="J31" s="599"/>
+      <c r="K31" s="600"/>
       <c r="O31" s="38"/>
       <c r="P31" s="38"/>
       <c r="Q31" s="38"/>
@@ -20172,18 +20181,18 @@
       <c r="G33" s="101"/>
       <c r="H33" s="101"/>
       <c r="I33" s="101"/>
-      <c r="O33" s="628" t="s">
+      <c r="O33" s="601" t="s">
         <v>172</v>
       </c>
-      <c r="P33" s="642"/>
-      <c r="Q33" s="642"/>
-      <c r="R33" s="642"/>
-      <c r="S33" s="642"/>
-      <c r="T33" s="642"/>
-      <c r="U33" s="642"/>
-      <c r="V33" s="642"/>
-      <c r="W33" s="642"/>
-      <c r="X33" s="643"/>
+      <c r="P33" s="602"/>
+      <c r="Q33" s="602"/>
+      <c r="R33" s="602"/>
+      <c r="S33" s="602"/>
+      <c r="T33" s="602"/>
+      <c r="U33" s="602"/>
+      <c r="V33" s="602"/>
+      <c r="W33" s="602"/>
+      <c r="X33" s="603"/>
       <c r="Y33" s="176"/>
     </row>
     <row r="34" spans="1:25" s="152" customFormat="1" ht="21" customHeight="1" thickBot="1">
@@ -20196,18 +20205,18 @@
       <c r="G34" s="101"/>
       <c r="H34" s="101"/>
       <c r="I34" s="101"/>
-      <c r="O34" s="634" t="s">
+      <c r="O34" s="598" t="s">
         <v>170</v>
       </c>
-      <c r="P34" s="635"/>
-      <c r="Q34" s="635"/>
-      <c r="R34" s="635"/>
-      <c r="S34" s="635"/>
-      <c r="T34" s="635"/>
-      <c r="U34" s="635"/>
-      <c r="V34" s="635"/>
-      <c r="W34" s="635"/>
-      <c r="X34" s="636"/>
+      <c r="P34" s="599"/>
+      <c r="Q34" s="599"/>
+      <c r="R34" s="599"/>
+      <c r="S34" s="599"/>
+      <c r="T34" s="599"/>
+      <c r="U34" s="599"/>
+      <c r="V34" s="599"/>
+      <c r="W34" s="599"/>
+      <c r="X34" s="600"/>
       <c r="Y34" s="176"/>
     </row>
     <row r="35" spans="1:25" s="152" customFormat="1" ht="34.5" customHeight="1">
@@ -20222,34 +20231,34 @@
     </row>
     <row r="37" spans="1:25" s="36" customFormat="1" ht="21" customHeight="1">
       <c r="A37" s="184"/>
-      <c r="O37" s="628" t="s">
+      <c r="O37" s="601" t="s">
         <v>174</v>
       </c>
-      <c r="P37" s="642"/>
-      <c r="Q37" s="642"/>
-      <c r="R37" s="642"/>
-      <c r="S37" s="642"/>
-      <c r="T37" s="642"/>
-      <c r="U37" s="642"/>
-      <c r="V37" s="642"/>
-      <c r="W37" s="642"/>
-      <c r="X37" s="643"/>
+      <c r="P37" s="602"/>
+      <c r="Q37" s="602"/>
+      <c r="R37" s="602"/>
+      <c r="S37" s="602"/>
+      <c r="T37" s="602"/>
+      <c r="U37" s="602"/>
+      <c r="V37" s="602"/>
+      <c r="W37" s="602"/>
+      <c r="X37" s="603"/>
       <c r="Y37" s="185"/>
     </row>
     <row r="38" spans="1:25" s="36" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A38" s="184"/>
-      <c r="O38" s="634" t="s">
+      <c r="O38" s="598" t="s">
         <v>175</v>
       </c>
-      <c r="P38" s="635"/>
-      <c r="Q38" s="635"/>
-      <c r="R38" s="635"/>
-      <c r="S38" s="635"/>
-      <c r="T38" s="635"/>
-      <c r="U38" s="635"/>
-      <c r="V38" s="635"/>
-      <c r="W38" s="635"/>
-      <c r="X38" s="636"/>
+      <c r="P38" s="599"/>
+      <c r="Q38" s="599"/>
+      <c r="R38" s="599"/>
+      <c r="S38" s="599"/>
+      <c r="T38" s="599"/>
+      <c r="U38" s="599"/>
+      <c r="V38" s="599"/>
+      <c r="W38" s="599"/>
+      <c r="X38" s="600"/>
       <c r="Y38" s="185"/>
     </row>
     <row r="39" spans="1:25" s="36" customFormat="1" ht="15" customHeight="1">
@@ -20296,34 +20305,49 @@
       <c r="Y40" s="117"/>
     </row>
     <row r="41" spans="1:25" ht="30" customHeight="1">
-      <c r="A41" s="641"/>
-      <c r="B41" s="641"/>
-      <c r="C41" s="641"/>
-      <c r="D41" s="641"/>
-      <c r="E41" s="641"/>
-      <c r="F41" s="641"/>
-      <c r="G41" s="641"/>
-      <c r="H41" s="641"/>
-      <c r="I41" s="641"/>
-      <c r="J41" s="641"/>
-      <c r="K41" s="641"/>
-      <c r="L41" s="641"/>
-      <c r="M41" s="641"/>
-      <c r="N41" s="641"/>
-      <c r="O41" s="641"/>
-      <c r="P41" s="641"/>
-      <c r="Q41" s="641"/>
-      <c r="R41" s="641"/>
-      <c r="S41" s="641"/>
-      <c r="T41" s="641"/>
-      <c r="U41" s="641"/>
-      <c r="V41" s="641"/>
-      <c r="W41" s="641"/>
-      <c r="X41" s="641"/>
-      <c r="Y41" s="641"/>
+      <c r="A41" s="597"/>
+      <c r="B41" s="597"/>
+      <c r="C41" s="597"/>
+      <c r="D41" s="597"/>
+      <c r="E41" s="597"/>
+      <c r="F41" s="597"/>
+      <c r="G41" s="597"/>
+      <c r="H41" s="597"/>
+      <c r="I41" s="597"/>
+      <c r="J41" s="597"/>
+      <c r="K41" s="597"/>
+      <c r="L41" s="597"/>
+      <c r="M41" s="597"/>
+      <c r="N41" s="597"/>
+      <c r="O41" s="597"/>
+      <c r="P41" s="597"/>
+      <c r="Q41" s="597"/>
+      <c r="R41" s="597"/>
+      <c r="S41" s="597"/>
+      <c r="T41" s="597"/>
+      <c r="U41" s="597"/>
+      <c r="V41" s="597"/>
+      <c r="W41" s="597"/>
+      <c r="X41" s="597"/>
+      <c r="Y41" s="597"/>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="B4:K5"/>
+    <mergeCell ref="O4:X5"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B17:E18"/>
+    <mergeCell ref="H16:K16"/>
+    <mergeCell ref="H17:K18"/>
+    <mergeCell ref="G7:S9"/>
+    <mergeCell ref="U17:X20"/>
+    <mergeCell ref="B24:K25"/>
+    <mergeCell ref="B26:K26"/>
+    <mergeCell ref="B12:K12"/>
+    <mergeCell ref="B13:K13"/>
+    <mergeCell ref="O12:X12"/>
+    <mergeCell ref="O13:X13"/>
+    <mergeCell ref="B20:K21"/>
     <mergeCell ref="A41:Y41"/>
     <mergeCell ref="O34:X34"/>
     <mergeCell ref="O37:X37"/>
@@ -20340,21 +20364,6 @@
     <mergeCell ref="O17:R18"/>
     <mergeCell ref="U16:X16"/>
     <mergeCell ref="O19:R20"/>
-    <mergeCell ref="B24:K25"/>
-    <mergeCell ref="B26:K26"/>
-    <mergeCell ref="B12:K12"/>
-    <mergeCell ref="B13:K13"/>
-    <mergeCell ref="O12:X12"/>
-    <mergeCell ref="O13:X13"/>
-    <mergeCell ref="B20:K21"/>
-    <mergeCell ref="B4:K5"/>
-    <mergeCell ref="O4:X5"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="B17:E18"/>
-    <mergeCell ref="H16:K16"/>
-    <mergeCell ref="H17:K18"/>
-    <mergeCell ref="G7:S9"/>
-    <mergeCell ref="U17:X20"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -20384,10 +20393,10 @@
       <c r="C1" s="202"/>
     </row>
     <row r="2" spans="2:7" ht="24.95" customHeight="1">
-      <c r="B2" s="651" t="s">
+      <c r="B2" s="649" t="s">
         <v>100</v>
       </c>
-      <c r="C2" s="651"/>
+      <c r="C2" s="649"/>
       <c r="D2" s="203" t="s">
         <v>199</v>
       </c>
@@ -20402,7 +20411,7 @@
       </c>
     </row>
     <row r="3" spans="2:7" ht="24.95" customHeight="1">
-      <c r="B3" s="651" t="s">
+      <c r="B3" s="649" t="s">
         <v>203</v>
       </c>
       <c r="C3" s="203" t="s">
@@ -20417,12 +20426,12 @@
       <c r="F3" s="204">
         <v>900000</v>
       </c>
-      <c r="G3" s="654" t="s">
+      <c r="G3" s="650" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="4" spans="2:7" ht="24.95" customHeight="1">
-      <c r="B4" s="651"/>
+      <c r="B4" s="649"/>
       <c r="C4" s="203" t="s">
         <v>85</v>
       </c>
@@ -20438,7 +20447,7 @@
         <f>F3*12</f>
         <v>10800000</v>
       </c>
-      <c r="G4" s="655"/>
+      <c r="G4" s="651"/>
     </row>
     <row r="5" spans="2:7" ht="24.95" customHeight="1">
       <c r="B5" s="205"/>
@@ -20455,10 +20464,10 @@
       <c r="C7" s="202"/>
     </row>
     <row r="8" spans="2:7" ht="24.95" customHeight="1">
-      <c r="B8" s="651" t="s">
+      <c r="B8" s="649" t="s">
         <v>100</v>
       </c>
-      <c r="C8" s="651"/>
+      <c r="C8" s="649"/>
       <c r="D8" s="203" t="s">
         <v>199</v>
       </c>
@@ -20473,7 +20482,7 @@
       </c>
     </row>
     <row r="9" spans="2:7" ht="24.95" customHeight="1">
-      <c r="B9" s="651" t="s">
+      <c r="B9" s="649" t="s">
         <v>203</v>
       </c>
       <c r="C9" s="203" t="s">
@@ -20493,7 +20502,7 @@
       </c>
     </row>
     <row r="10" spans="2:7" ht="24.95" customHeight="1" thickBot="1">
-      <c r="B10" s="651"/>
+      <c r="B10" s="649"/>
       <c r="C10" s="203" t="s">
         <v>85</v>
       </c>
@@ -20518,10 +20527,10 @@
       <c r="C12" s="202"/>
     </row>
     <row r="13" spans="2:7" ht="24.95" customHeight="1">
-      <c r="B13" s="651" t="s">
+      <c r="B13" s="649" t="s">
         <v>100</v>
       </c>
-      <c r="C13" s="651"/>
+      <c r="C13" s="649"/>
       <c r="D13" s="203" t="s">
         <v>199</v>
       </c>
@@ -20536,7 +20545,7 @@
       </c>
     </row>
     <row r="14" spans="2:7" ht="24.95" customHeight="1">
-      <c r="B14" s="651" t="s">
+      <c r="B14" s="649" t="s">
         <v>203</v>
       </c>
       <c r="C14" s="203" t="s">
@@ -20556,7 +20565,7 @@
       </c>
     </row>
     <row r="15" spans="2:7" ht="24.95" customHeight="1" thickBot="1">
-      <c r="B15" s="651"/>
+      <c r="B15" s="649"/>
       <c r="C15" s="203" t="s">
         <v>85</v>
       </c>
@@ -20581,10 +20590,10 @@
       <c r="C17" s="202"/>
     </row>
     <row r="18" spans="2:7" ht="24.95" customHeight="1">
-      <c r="B18" s="651" t="s">
+      <c r="B18" s="649" t="s">
         <v>100</v>
       </c>
-      <c r="C18" s="651"/>
+      <c r="C18" s="649"/>
       <c r="D18" s="203" t="s">
         <v>199</v>
       </c>
@@ -20599,7 +20608,7 @@
       </c>
     </row>
     <row r="19" spans="2:7" ht="24.95" customHeight="1">
-      <c r="B19" s="651" t="s">
+      <c r="B19" s="649" t="s">
         <v>203</v>
       </c>
       <c r="C19" s="203" t="s">
@@ -20619,7 +20628,7 @@
       </c>
     </row>
     <row r="20" spans="2:7" ht="24.95" customHeight="1" thickBot="1">
-      <c r="B20" s="651"/>
+      <c r="B20" s="649"/>
       <c r="C20" s="203" t="s">
         <v>85</v>
       </c>
@@ -20639,18 +20648,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="G14:G15"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="G9:G10"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="G14:G15"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/정보통신사업부 견적서 양식_ver2.xlsx
+++ b/정보통신사업부 견적서 양식_ver2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Master\Documents\Project\견적서 자동화 프로젝트\정보통신사업부\.claude\worktrees\blissful-kalam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65C6B104-CBEC-43D0-832E-EF307D08EDB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF199A59-CE3F-4548-9022-08B30A376211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="854" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="854" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VXXXXX" sheetId="6" state="veryHidden" r:id="rId1"/>
@@ -131,7 +131,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="288">
   <si>
     <t>직접경비</t>
     <phoneticPr fontId="67" type="noConversion"/>
@@ -1251,10 +1251,6 @@
   </si>
   <si>
     <t>연면적 5천[㎡] 이상 ~ 1만[㎡] 미만 건축물</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>성능점검 1회, 유지보수관리점검 2회, 유지관리자 위탁 선임(비상주) 1년</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -8365,7 +8361,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="673">
+  <cellXfs count="674">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -9349,6 +9345,24 @@
     <xf numFmtId="231" fontId="133" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="116" fillId="32" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="32" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="32" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="117" fillId="31" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="117" fillId="31" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="117" fillId="31" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="129" fillId="31" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -9370,13 +9384,22 @@
     <xf numFmtId="178" fontId="116" fillId="32" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="162" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="110" fillId="0" borderId="163" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="163" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="164" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="165" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="166" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="109" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -9433,33 +9456,6 @@
     <xf numFmtId="0" fontId="108" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="116" fillId="32" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="116" fillId="32" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="117" fillId="31" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="117" fillId="31" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="117" fillId="31" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="31" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="31" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="31" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="116" fillId="32" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="116" fillId="30" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -9544,6 +9540,36 @@
     <xf numFmtId="0" fontId="110" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="31" fontId="108" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="32" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="31" fontId="116" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -9556,52 +9582,25 @@
     <xf numFmtId="0" fontId="108" fillId="32" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="31" fontId="108" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="110" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="31" fontId="112" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="109" fillId="32" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="109" fillId="32" borderId="162" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="163" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="165" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="232" fontId="116" fillId="29" borderId="31" xfId="1267" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -9706,6 +9705,15 @@
     <xf numFmtId="178" fontId="108" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="117" fillId="31" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="31" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="31" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -10294,20 +10302,11 @@
     <xf numFmtId="0" fontId="167" fillId="35" borderId="28" xfId="1267" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="164" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="166" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="162" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="165" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2468">
@@ -14966,11 +14965,11 @@
       </c>
     </row>
     <row r="9" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="654"/>
-      <c r="B9" s="654"/>
-      <c r="C9" s="654"/>
-      <c r="D9" s="654"/>
-      <c r="E9" s="654"/>
+      <c r="A9" s="658"/>
+      <c r="B9" s="658"/>
+      <c r="C9" s="658"/>
+      <c r="D9" s="658"/>
+      <c r="E9" s="658"/>
       <c r="F9" s="234">
         <f>SUM(F2:F8)</f>
         <v>70200000</v>
@@ -15008,7 +15007,7 @@
   <sheetData>
     <row r="1" spans="1:14" s="261" customFormat="1" ht="17.25" thickBot="1">
       <c r="A1" s="258" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B1" s="259"/>
       <c r="C1" s="260"/>
@@ -15023,39 +15022,39 @@
       <c r="L1" s="259"/>
     </row>
     <row r="2" spans="1:14" s="249" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A2" s="657" t="s">
+      <c r="A2" s="661" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="659" t="s">
+      <c r="B2" s="663" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="661" t="s">
+      <c r="C2" s="665" t="s">
         <v>78</v>
       </c>
-      <c r="D2" s="657" t="s">
+      <c r="D2" s="661" t="s">
         <v>84</v>
       </c>
-      <c r="E2" s="663"/>
-      <c r="F2" s="664" t="s">
+      <c r="E2" s="667"/>
+      <c r="F2" s="668" t="s">
         <v>82</v>
       </c>
-      <c r="G2" s="661"/>
-      <c r="H2" s="665" t="s">
+      <c r="G2" s="665"/>
+      <c r="H2" s="669" t="s">
         <v>87</v>
       </c>
-      <c r="I2" s="666"/>
-      <c r="J2" s="667"/>
-      <c r="K2" s="655" t="s">
+      <c r="I2" s="670"/>
+      <c r="J2" s="671"/>
+      <c r="K2" s="659" t="s">
         <v>259</v>
       </c>
-      <c r="L2" s="655" t="s">
+      <c r="L2" s="659" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:14" s="249" customFormat="1" ht="22.5" customHeight="1" thickBot="1">
-      <c r="A3" s="658"/>
-      <c r="B3" s="660"/>
-      <c r="C3" s="662"/>
+      <c r="A3" s="662"/>
+      <c r="B3" s="664"/>
+      <c r="C3" s="666"/>
       <c r="D3" s="250" t="s">
         <v>83</v>
       </c>
@@ -15069,16 +15068,16 @@
         <v>85</v>
       </c>
       <c r="H3" s="254" t="s">
+        <v>265</v>
+      </c>
+      <c r="I3" s="255" t="s">
         <v>266</v>
-      </c>
-      <c r="I3" s="255" t="s">
-        <v>267</v>
       </c>
       <c r="J3" s="256" t="s">
         <v>86</v>
       </c>
-      <c r="K3" s="656"/>
-      <c r="L3" s="656"/>
+      <c r="K3" s="660"/>
+      <c r="L3" s="660"/>
     </row>
     <row r="4" spans="1:14" s="249" customFormat="1" ht="22.5" customHeight="1">
       <c r="A4" s="263" t="s">
@@ -15338,7 +15337,7 @@
     </row>
     <row r="11" spans="1:14" s="261" customFormat="1" ht="22.5" customHeight="1" thickBot="1">
       <c r="A11" s="258" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B11" s="259"/>
       <c r="C11" s="260"/>
@@ -15354,40 +15353,40 @@
       <c r="N11" s="262"/>
     </row>
     <row r="12" spans="1:14" s="249" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A12" s="657" t="s">
+      <c r="A12" s="661" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="659" t="s">
+      <c r="B12" s="663" t="s">
         <v>90</v>
       </c>
-      <c r="C12" s="661" t="s">
+      <c r="C12" s="665" t="s">
         <v>78</v>
       </c>
-      <c r="D12" s="657" t="s">
+      <c r="D12" s="661" t="s">
         <v>84</v>
       </c>
-      <c r="E12" s="663"/>
-      <c r="F12" s="664" t="s">
+      <c r="E12" s="667"/>
+      <c r="F12" s="668" t="s">
         <v>82</v>
       </c>
-      <c r="G12" s="661"/>
-      <c r="H12" s="665" t="s">
+      <c r="G12" s="665"/>
+      <c r="H12" s="669" t="s">
         <v>87</v>
       </c>
-      <c r="I12" s="666"/>
-      <c r="J12" s="667"/>
-      <c r="K12" s="655" t="s">
+      <c r="I12" s="670"/>
+      <c r="J12" s="671"/>
+      <c r="K12" s="659" t="s">
         <v>259</v>
       </c>
-      <c r="L12" s="655" t="s">
+      <c r="L12" s="659" t="s">
         <v>258</v>
       </c>
       <c r="N12" s="257"/>
     </row>
     <row r="13" spans="1:14" s="249" customFormat="1" ht="22.5" customHeight="1" thickBot="1">
-      <c r="A13" s="658"/>
-      <c r="B13" s="660"/>
-      <c r="C13" s="662"/>
+      <c r="A13" s="662"/>
+      <c r="B13" s="664"/>
+      <c r="C13" s="666"/>
       <c r="D13" s="250" t="s">
         <v>83</v>
       </c>
@@ -15401,16 +15400,16 @@
         <v>85</v>
       </c>
       <c r="H13" s="254" t="s">
+        <v>265</v>
+      </c>
+      <c r="I13" s="255" t="s">
         <v>266</v>
-      </c>
-      <c r="I13" s="255" t="s">
-        <v>267</v>
       </c>
       <c r="J13" s="256" t="s">
         <v>86</v>
       </c>
-      <c r="K13" s="656"/>
-      <c r="L13" s="656"/>
+      <c r="K13" s="660"/>
+      <c r="L13" s="660"/>
       <c r="N13" s="257"/>
     </row>
     <row r="14" spans="1:14" s="249" customFormat="1" ht="22.5" customHeight="1">
@@ -15669,17 +15668,17 @@
     </row>
     <row r="21" spans="1:12" s="304" customFormat="1">
       <c r="A21" s="303" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="22" spans="1:12" s="304" customFormat="1">
       <c r="A22" s="305" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="23" spans="1:12" s="304" customFormat="1">
       <c r="A23" s="305" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
   </sheetData>
@@ -15717,7 +15716,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="261" customFormat="1">
       <c r="A1" s="307" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B1" s="308"/>
       <c r="C1" s="308"/>
@@ -15729,49 +15728,49 @@
     </row>
     <row r="2" spans="1:8" ht="23.25" customHeight="1">
       <c r="A2" s="310" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H2" s="311"/>
     </row>
     <row r="3" spans="1:8" ht="23.25" customHeight="1">
       <c r="A3" s="310" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H3" s="311"/>
     </row>
     <row r="4" spans="1:8" ht="23.25" customHeight="1">
       <c r="A4" s="310" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H4" s="311"/>
     </row>
     <row r="5" spans="1:8" ht="23.25" customHeight="1">
       <c r="A5" s="310" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H5" s="311"/>
     </row>
     <row r="6" spans="1:8" ht="23.25" customHeight="1">
       <c r="A6" s="310" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H6" s="311"/>
     </row>
     <row r="7" spans="1:8" ht="23.25" customHeight="1">
       <c r="A7" s="310" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H7" s="311"/>
     </row>
     <row r="8" spans="1:8" ht="23.25" customHeight="1">
       <c r="A8" s="310" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H8" s="311"/>
     </row>
     <row r="9" spans="1:8" ht="23.25" customHeight="1">
       <c r="A9" s="312" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H9" s="311"/>
     </row>
@@ -16058,7 +16057,7 @@
       <c r="H26" s="190"/>
       <c r="I26" s="190"/>
       <c r="J26" s="191" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="27" spans="1:10" s="78" customFormat="1" ht="13.5">
@@ -16091,7 +16090,7 @@
     </row>
     <row r="29" spans="1:10" ht="30" hidden="1" customHeight="1">
       <c r="D29" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>
@@ -16200,7 +16199,7 @@
     </row>
     <row r="3" spans="1:28" s="6" customFormat="1" ht="39.75" customHeight="1">
       <c r="A3" s="402" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B3" s="403"/>
       <c r="C3" s="403"/>
@@ -16420,12 +16419,12 @@
       </c>
       <c r="V9" s="400"/>
       <c r="W9" s="400"/>
-      <c r="X9" s="355" t="s">
+      <c r="X9" s="361" t="s">
         <v>67</v>
       </c>
-      <c r="Y9" s="355"/>
-      <c r="Z9" s="355"/>
-      <c r="AA9" s="356"/>
+      <c r="Y9" s="361"/>
+      <c r="Z9" s="361"/>
+      <c r="AA9" s="362"/>
       <c r="AB9" s="5"/>
     </row>
     <row r="10" spans="1:28" s="6" customFormat="1" ht="32.1" customHeight="1">
@@ -16474,15 +16473,15 @@
       </c>
       <c r="D11" s="217"/>
       <c r="E11" s="215"/>
-      <c r="F11" s="418" t="s">
+      <c r="F11" s="428" t="s">
         <v>107</v>
       </c>
-      <c r="G11" s="418"/>
-      <c r="H11" s="418"/>
-      <c r="I11" s="418"/>
-      <c r="J11" s="418"/>
-      <c r="K11" s="418"/>
-      <c r="L11" s="419"/>
+      <c r="G11" s="428"/>
+      <c r="H11" s="428"/>
+      <c r="I11" s="428"/>
+      <c r="J11" s="428"/>
+      <c r="K11" s="428"/>
+      <c r="L11" s="429"/>
       <c r="M11" s="406"/>
       <c r="N11" s="400" t="s">
         <v>27</v>
@@ -16500,12 +16499,12 @@
       </c>
       <c r="V11" s="400"/>
       <c r="W11" s="400"/>
-      <c r="X11" s="426" t="s">
+      <c r="X11" s="422" t="s">
         <v>69</v>
       </c>
-      <c r="Y11" s="426"/>
-      <c r="Z11" s="426"/>
-      <c r="AA11" s="427"/>
+      <c r="Y11" s="422"/>
+      <c r="Z11" s="422"/>
+      <c r="AA11" s="423"/>
       <c r="AB11" s="5"/>
     </row>
     <row r="12" spans="1:28" s="6" customFormat="1" ht="32.1" customHeight="1">
@@ -16522,26 +16521,26 @@
       <c r="K12" s="316"/>
       <c r="L12" s="317"/>
       <c r="M12" s="407"/>
-      <c r="N12" s="436" t="s">
+      <c r="N12" s="435" t="s">
         <v>50</v>
       </c>
-      <c r="O12" s="361"/>
-      <c r="P12" s="361"/>
-      <c r="Q12" s="671"/>
-      <c r="R12" s="360"/>
-      <c r="S12" s="360"/>
-      <c r="T12" s="668"/>
+      <c r="O12" s="436"/>
+      <c r="P12" s="436"/>
+      <c r="Q12" s="366"/>
+      <c r="R12" s="367"/>
+      <c r="S12" s="367"/>
+      <c r="T12" s="368"/>
       <c r="U12" s="400" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="V12" s="400"/>
       <c r="W12" s="400"/>
-      <c r="X12" s="426" t="s">
-        <v>284</v>
-      </c>
-      <c r="Y12" s="426"/>
-      <c r="Z12" s="426"/>
-      <c r="AA12" s="427"/>
+      <c r="X12" s="422" t="s">
+        <v>283</v>
+      </c>
+      <c r="Y12" s="422"/>
+      <c r="Z12" s="422"/>
+      <c r="AA12" s="423"/>
       <c r="AB12" s="5"/>
     </row>
     <row r="13" spans="1:28" s="6" customFormat="1" ht="32.1" customHeight="1" thickBot="1">
@@ -16549,35 +16548,35 @@
         <v>49</v>
       </c>
       <c r="B13" s="216"/>
-      <c r="C13" s="432" t="s">
+      <c r="C13" s="672" t="s">
         <v>108</v>
       </c>
-      <c r="D13" s="432"/>
-      <c r="E13" s="432"/>
-      <c r="F13" s="432"/>
-      <c r="G13" s="432"/>
-      <c r="H13" s="432"/>
-      <c r="I13" s="432"/>
-      <c r="J13" s="432"/>
-      <c r="K13" s="432"/>
-      <c r="L13" s="433"/>
+      <c r="D13" s="672"/>
+      <c r="E13" s="672"/>
+      <c r="F13" s="672"/>
+      <c r="G13" s="672"/>
+      <c r="H13" s="672"/>
+      <c r="I13" s="672"/>
+      <c r="J13" s="672"/>
+      <c r="K13" s="672"/>
+      <c r="L13" s="673"/>
       <c r="M13" s="408"/>
       <c r="N13" s="437"/>
-      <c r="O13" s="362"/>
-      <c r="P13" s="362"/>
-      <c r="Q13" s="672"/>
-      <c r="R13" s="669"/>
-      <c r="S13" s="669"/>
-      <c r="T13" s="670"/>
-      <c r="U13" s="435" t="s">
+      <c r="O13" s="438"/>
+      <c r="P13" s="438"/>
+      <c r="Q13" s="369"/>
+      <c r="R13" s="370"/>
+      <c r="S13" s="370"/>
+      <c r="T13" s="371"/>
+      <c r="U13" s="427" t="s">
         <v>51</v>
       </c>
-      <c r="V13" s="435"/>
-      <c r="W13" s="435"/>
-      <c r="X13" s="428"/>
-      <c r="Y13" s="429"/>
-      <c r="Z13" s="429"/>
-      <c r="AA13" s="430"/>
+      <c r="V13" s="427"/>
+      <c r="W13" s="427"/>
+      <c r="X13" s="424"/>
+      <c r="Y13" s="425"/>
+      <c r="Z13" s="425"/>
+      <c r="AA13" s="426"/>
       <c r="AB13" s="5"/>
     </row>
     <row r="14" spans="1:28" s="6" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -16596,33 +16595,33 @@
       <c r="K14" s="220"/>
       <c r="L14" s="220"/>
       <c r="M14" s="12"/>
-      <c r="N14" s="425"/>
-      <c r="O14" s="425"/>
-      <c r="P14" s="425"/>
-      <c r="Q14" s="431"/>
-      <c r="R14" s="431"/>
-      <c r="S14" s="431"/>
-      <c r="T14" s="431"/>
-      <c r="U14" s="425"/>
-      <c r="V14" s="425"/>
-      <c r="W14" s="425"/>
-      <c r="X14" s="431"/>
-      <c r="Y14" s="431"/>
-      <c r="Z14" s="431"/>
-      <c r="AA14" s="431"/>
+      <c r="N14" s="421"/>
+      <c r="O14" s="421"/>
+      <c r="P14" s="421"/>
+      <c r="Q14" s="432"/>
+      <c r="R14" s="432"/>
+      <c r="S14" s="432"/>
+      <c r="T14" s="432"/>
+      <c r="U14" s="421"/>
+      <c r="V14" s="421"/>
+      <c r="W14" s="421"/>
+      <c r="X14" s="432"/>
+      <c r="Y14" s="432"/>
+      <c r="Z14" s="432"/>
+      <c r="AA14" s="432"/>
       <c r="AB14" s="5"/>
     </row>
     <row r="15" spans="1:28" s="6" customFormat="1" ht="35.1" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="221"/>
       <c r="C15" s="13"/>
-      <c r="D15" s="420" t="s">
+      <c r="D15" s="430" t="s">
         <v>75</v>
       </c>
-      <c r="E15" s="421"/>
-      <c r="F15" s="421"/>
-      <c r="G15" s="421"/>
-      <c r="H15" s="421"/>
+      <c r="E15" s="431"/>
+      <c r="F15" s="431"/>
+      <c r="G15" s="431"/>
+      <c r="H15" s="431"/>
       <c r="I15" s="14"/>
       <c r="J15" s="66">
         <f>E9</f>
@@ -16651,13 +16650,13 @@
       <c r="A16" s="16"/>
       <c r="B16" s="222"/>
       <c r="C16" s="13"/>
-      <c r="D16" s="420" t="s">
+      <c r="D16" s="430" t="s">
         <v>76</v>
       </c>
-      <c r="E16" s="421"/>
-      <c r="F16" s="421"/>
-      <c r="G16" s="421"/>
-      <c r="H16" s="421"/>
+      <c r="E16" s="431"/>
+      <c r="F16" s="431"/>
+      <c r="G16" s="431"/>
+      <c r="H16" s="431"/>
       <c r="I16" s="14"/>
       <c r="J16" s="65"/>
       <c r="K16" s="14"/>
@@ -16683,64 +16682,64 @@
       <c r="A17" s="16"/>
       <c r="B17" s="222"/>
       <c r="C17" s="13"/>
-      <c r="D17" s="420" t="s">
+      <c r="D17" s="430" t="s">
         <v>196</v>
       </c>
-      <c r="E17" s="421"/>
-      <c r="F17" s="421"/>
-      <c r="G17" s="421"/>
-      <c r="H17" s="421"/>
+      <c r="E17" s="431"/>
+      <c r="F17" s="431"/>
+      <c r="G17" s="431"/>
+      <c r="H17" s="431"/>
       <c r="I17" s="14"/>
-      <c r="J17" s="422"/>
-      <c r="K17" s="423"/>
-      <c r="L17" s="423"/>
-      <c r="M17" s="423"/>
-      <c r="N17" s="423"/>
-      <c r="O17" s="423"/>
-      <c r="P17" s="423"/>
-      <c r="Q17" s="423"/>
-      <c r="R17" s="423"/>
-      <c r="S17" s="423"/>
-      <c r="T17" s="423"/>
-      <c r="U17" s="423"/>
-      <c r="V17" s="423"/>
-      <c r="W17" s="423"/>
-      <c r="X17" s="423"/>
-      <c r="Y17" s="423"/>
-      <c r="Z17" s="423"/>
-      <c r="AA17" s="424"/>
+      <c r="J17" s="418"/>
+      <c r="K17" s="419"/>
+      <c r="L17" s="419"/>
+      <c r="M17" s="419"/>
+      <c r="N17" s="419"/>
+      <c r="O17" s="419"/>
+      <c r="P17" s="419"/>
+      <c r="Q17" s="419"/>
+      <c r="R17" s="419"/>
+      <c r="S17" s="419"/>
+      <c r="T17" s="419"/>
+      <c r="U17" s="419"/>
+      <c r="V17" s="419"/>
+      <c r="W17" s="419"/>
+      <c r="X17" s="419"/>
+      <c r="Y17" s="419"/>
+      <c r="Z17" s="419"/>
+      <c r="AA17" s="420"/>
       <c r="AB17" s="15"/>
     </row>
     <row r="18" spans="1:28" s="17" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A18" s="16"/>
       <c r="B18" s="222"/>
       <c r="C18" s="13"/>
-      <c r="D18" s="420" t="s">
+      <c r="D18" s="430" t="s">
         <v>195</v>
       </c>
-      <c r="E18" s="421"/>
-      <c r="F18" s="421"/>
-      <c r="G18" s="421"/>
-      <c r="H18" s="421"/>
+      <c r="E18" s="431"/>
+      <c r="F18" s="431"/>
+      <c r="G18" s="431"/>
+      <c r="H18" s="431"/>
       <c r="I18" s="14"/>
-      <c r="J18" s="449"/>
-      <c r="K18" s="449"/>
-      <c r="L18" s="449"/>
-      <c r="M18" s="449"/>
-      <c r="N18" s="449"/>
-      <c r="O18" s="449"/>
-      <c r="P18" s="449"/>
-      <c r="Q18" s="449"/>
-      <c r="R18" s="375" t="s">
+      <c r="J18" s="450"/>
+      <c r="K18" s="450"/>
+      <c r="L18" s="450"/>
+      <c r="M18" s="450"/>
+      <c r="N18" s="450"/>
+      <c r="O18" s="450"/>
+      <c r="P18" s="450"/>
+      <c r="Q18" s="450"/>
+      <c r="R18" s="384" t="s">
         <v>55</v>
       </c>
-      <c r="S18" s="376"/>
-      <c r="T18" s="376"/>
-      <c r="U18" s="376"/>
-      <c r="V18" s="377"/>
-      <c r="W18" s="438"/>
-      <c r="X18" s="438"/>
-      <c r="Y18" s="438"/>
+      <c r="S18" s="385"/>
+      <c r="T18" s="385"/>
+      <c r="U18" s="385"/>
+      <c r="V18" s="386"/>
+      <c r="W18" s="439"/>
+      <c r="X18" s="439"/>
+      <c r="Y18" s="439"/>
       <c r="Z18" s="247" t="s">
         <v>56</v>
       </c>
@@ -16751,68 +16750,66 @@
       <c r="A19" s="10"/>
       <c r="B19" s="221"/>
       <c r="C19" s="18"/>
-      <c r="D19" s="442" t="s">
+      <c r="D19" s="443" t="s">
         <v>194</v>
       </c>
-      <c r="E19" s="443"/>
-      <c r="F19" s="443"/>
-      <c r="G19" s="443"/>
-      <c r="H19" s="443"/>
+      <c r="E19" s="444"/>
+      <c r="F19" s="444"/>
+      <c r="G19" s="444"/>
+      <c r="H19" s="444"/>
       <c r="I19" s="19"/>
-      <c r="J19" s="449"/>
-      <c r="K19" s="449"/>
-      <c r="L19" s="449"/>
-      <c r="M19" s="449"/>
-      <c r="N19" s="449"/>
-      <c r="O19" s="449"/>
-      <c r="P19" s="449"/>
-      <c r="Q19" s="449"/>
-      <c r="R19" s="375" t="s">
+      <c r="J19" s="450"/>
+      <c r="K19" s="450"/>
+      <c r="L19" s="450"/>
+      <c r="M19" s="450"/>
+      <c r="N19" s="450"/>
+      <c r="O19" s="450"/>
+      <c r="P19" s="450"/>
+      <c r="Q19" s="450"/>
+      <c r="R19" s="384" t="s">
         <v>198</v>
       </c>
-      <c r="S19" s="376"/>
-      <c r="T19" s="376"/>
-      <c r="U19" s="376"/>
-      <c r="V19" s="377"/>
-      <c r="W19" s="378"/>
-      <c r="X19" s="379"/>
-      <c r="Y19" s="379"/>
-      <c r="Z19" s="379"/>
-      <c r="AA19" s="380"/>
+      <c r="S19" s="385"/>
+      <c r="T19" s="385"/>
+      <c r="U19" s="385"/>
+      <c r="V19" s="386"/>
+      <c r="W19" s="387"/>
+      <c r="X19" s="388"/>
+      <c r="Y19" s="388"/>
+      <c r="Z19" s="388"/>
+      <c r="AA19" s="389"/>
       <c r="AB19" s="15"/>
     </row>
     <row r="20" spans="1:28" s="6" customFormat="1" ht="35.1" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="221"/>
       <c r="C20" s="13"/>
-      <c r="D20" s="420" t="s">
+      <c r="D20" s="430" t="s">
         <v>197</v>
       </c>
-      <c r="E20" s="421"/>
-      <c r="F20" s="421"/>
-      <c r="G20" s="421"/>
-      <c r="H20" s="421"/>
+      <c r="E20" s="431"/>
+      <c r="F20" s="431"/>
+      <c r="G20" s="431"/>
+      <c r="H20" s="431"/>
       <c r="I20" s="14"/>
-      <c r="J20" s="447" t="s">
-        <v>264</v>
-      </c>
-      <c r="K20" s="447"/>
-      <c r="L20" s="447"/>
-      <c r="M20" s="447"/>
-      <c r="N20" s="447"/>
-      <c r="O20" s="447"/>
-      <c r="P20" s="447"/>
-      <c r="Q20" s="447"/>
-      <c r="R20" s="447"/>
-      <c r="S20" s="447"/>
-      <c r="T20" s="447"/>
-      <c r="U20" s="447"/>
-      <c r="V20" s="447"/>
-      <c r="W20" s="447"/>
-      <c r="X20" s="447"/>
-      <c r="Y20" s="447"/>
-      <c r="Z20" s="447"/>
-      <c r="AA20" s="448"/>
+      <c r="J20" s="448"/>
+      <c r="K20" s="448"/>
+      <c r="L20" s="448"/>
+      <c r="M20" s="448"/>
+      <c r="N20" s="448"/>
+      <c r="O20" s="448"/>
+      <c r="P20" s="448"/>
+      <c r="Q20" s="448"/>
+      <c r="R20" s="448"/>
+      <c r="S20" s="448"/>
+      <c r="T20" s="448"/>
+      <c r="U20" s="448"/>
+      <c r="V20" s="448"/>
+      <c r="W20" s="448"/>
+      <c r="X20" s="448"/>
+      <c r="Y20" s="448"/>
+      <c r="Z20" s="448"/>
+      <c r="AA20" s="449"/>
       <c r="AB20" s="15"/>
     </row>
     <row r="21" spans="1:28" s="6" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -16847,46 +16844,46 @@
     <row r="22" spans="1:28" s="23" customFormat="1" ht="47.1" customHeight="1">
       <c r="A22" s="20"/>
       <c r="B22" s="21"/>
-      <c r="C22" s="450" t="s">
+      <c r="C22" s="451" t="s">
+        <v>286</v>
+      </c>
+      <c r="D22" s="452"/>
+      <c r="E22" s="452"/>
+      <c r="F22" s="452"/>
+      <c r="G22" s="359" t="s">
         <v>287</v>
       </c>
-      <c r="D22" s="451"/>
-      <c r="E22" s="451"/>
-      <c r="F22" s="451"/>
-      <c r="G22" s="353" t="s">
-        <v>288</v>
-      </c>
-      <c r="H22" s="353"/>
-      <c r="I22" s="353"/>
-      <c r="J22" s="353"/>
-      <c r="K22" s="354"/>
-      <c r="L22" s="444" t="s">
+      <c r="H22" s="359"/>
+      <c r="I22" s="359"/>
+      <c r="J22" s="359"/>
+      <c r="K22" s="360"/>
+      <c r="L22" s="445" t="s">
         <v>19</v>
       </c>
-      <c r="M22" s="445"/>
-      <c r="N22" s="445"/>
-      <c r="O22" s="446">
+      <c r="M22" s="446"/>
+      <c r="N22" s="446"/>
+      <c r="O22" s="447">
         <f>V22</f>
         <v>0</v>
       </c>
-      <c r="P22" s="446"/>
-      <c r="Q22" s="446"/>
-      <c r="R22" s="446"/>
-      <c r="S22" s="446"/>
+      <c r="P22" s="447"/>
+      <c r="Q22" s="447"/>
+      <c r="R22" s="447"/>
+      <c r="S22" s="447"/>
       <c r="T22" s="69" t="s">
         <v>20</v>
       </c>
       <c r="U22" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="V22" s="441">
+      <c r="V22" s="442">
         <f>T28</f>
         <v>0</v>
       </c>
-      <c r="W22" s="441"/>
-      <c r="X22" s="441"/>
-      <c r="Y22" s="441"/>
-      <c r="Z22" s="441"/>
+      <c r="W22" s="442"/>
+      <c r="X22" s="442"/>
+      <c r="Y22" s="442"/>
+      <c r="Z22" s="442"/>
       <c r="AA22" s="70" t="s">
         <v>31</v>
       </c>
@@ -16898,40 +16895,40 @@
       <c r="C23" s="218" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="366" t="s">
+      <c r="D23" s="375" t="s">
         <v>22</v>
       </c>
-      <c r="E23" s="367"/>
-      <c r="F23" s="367"/>
-      <c r="G23" s="367"/>
-      <c r="H23" s="367"/>
-      <c r="I23" s="367"/>
-      <c r="J23" s="367"/>
-      <c r="K23" s="368"/>
-      <c r="L23" s="439" t="s">
+      <c r="E23" s="376"/>
+      <c r="F23" s="376"/>
+      <c r="G23" s="376"/>
+      <c r="H23" s="376"/>
+      <c r="I23" s="376"/>
+      <c r="J23" s="376"/>
+      <c r="K23" s="377"/>
+      <c r="L23" s="440" t="s">
         <v>33</v>
       </c>
-      <c r="M23" s="432"/>
-      <c r="N23" s="432"/>
-      <c r="O23" s="432"/>
-      <c r="P23" s="439" t="s">
+      <c r="M23" s="433"/>
+      <c r="N23" s="433"/>
+      <c r="O23" s="433"/>
+      <c r="P23" s="440" t="s">
         <v>34</v>
       </c>
-      <c r="Q23" s="432"/>
-      <c r="R23" s="432"/>
-      <c r="S23" s="440"/>
-      <c r="T23" s="439" t="s">
+      <c r="Q23" s="433"/>
+      <c r="R23" s="433"/>
+      <c r="S23" s="441"/>
+      <c r="T23" s="440" t="s">
         <v>23</v>
       </c>
-      <c r="U23" s="432"/>
-      <c r="V23" s="432"/>
-      <c r="W23" s="432"/>
-      <c r="X23" s="440"/>
-      <c r="Y23" s="432" t="s">
+      <c r="U23" s="433"/>
+      <c r="V23" s="433"/>
+      <c r="W23" s="433"/>
+      <c r="X23" s="441"/>
+      <c r="Y23" s="433" t="s">
         <v>38</v>
       </c>
-      <c r="Z23" s="432"/>
-      <c r="AA23" s="440"/>
+      <c r="Z23" s="433"/>
+      <c r="AA23" s="441"/>
       <c r="AB23" s="5"/>
     </row>
     <row r="24" spans="1:28" s="6" customFormat="1" ht="35.1" customHeight="1">
@@ -16940,36 +16937,36 @@
       <c r="C24" s="62">
         <v>1</v>
       </c>
-      <c r="D24" s="363" t="s">
+      <c r="D24" s="372" t="s">
         <v>91</v>
       </c>
-      <c r="E24" s="364"/>
-      <c r="F24" s="364"/>
-      <c r="G24" s="364"/>
-      <c r="H24" s="364"/>
-      <c r="I24" s="364"/>
-      <c r="J24" s="364"/>
-      <c r="K24" s="365"/>
-      <c r="L24" s="366" t="s">
+      <c r="E24" s="373"/>
+      <c r="F24" s="373"/>
+      <c r="G24" s="373"/>
+      <c r="H24" s="373"/>
+      <c r="I24" s="373"/>
+      <c r="J24" s="373"/>
+      <c r="K24" s="374"/>
+      <c r="L24" s="375" t="s">
         <v>89</v>
       </c>
-      <c r="M24" s="367"/>
-      <c r="N24" s="367"/>
-      <c r="O24" s="368"/>
-      <c r="P24" s="369"/>
-      <c r="Q24" s="370"/>
-      <c r="R24" s="370"/>
-      <c r="S24" s="371"/>
-      <c r="T24" s="372"/>
-      <c r="U24" s="373"/>
-      <c r="V24" s="373"/>
-      <c r="W24" s="373"/>
-      <c r="X24" s="374"/>
-      <c r="Y24" s="461" t="s">
+      <c r="M24" s="376"/>
+      <c r="N24" s="376"/>
+      <c r="O24" s="377"/>
+      <c r="P24" s="378"/>
+      <c r="Q24" s="379"/>
+      <c r="R24" s="379"/>
+      <c r="S24" s="380"/>
+      <c r="T24" s="381"/>
+      <c r="U24" s="382"/>
+      <c r="V24" s="382"/>
+      <c r="W24" s="382"/>
+      <c r="X24" s="383"/>
+      <c r="Y24" s="462" t="s">
         <v>105</v>
       </c>
-      <c r="Z24" s="461"/>
-      <c r="AA24" s="462"/>
+      <c r="Z24" s="462"/>
+      <c r="AA24" s="463"/>
       <c r="AB24" s="5"/>
     </row>
     <row r="25" spans="1:28" s="6" customFormat="1" ht="35.1" customHeight="1">
@@ -16978,36 +16975,36 @@
       <c r="C25" s="61">
         <v>2</v>
       </c>
-      <c r="D25" s="363" t="s">
+      <c r="D25" s="372" t="s">
         <v>92</v>
       </c>
-      <c r="E25" s="364"/>
-      <c r="F25" s="364"/>
-      <c r="G25" s="364"/>
-      <c r="H25" s="364"/>
-      <c r="I25" s="364"/>
-      <c r="J25" s="364"/>
-      <c r="K25" s="365"/>
-      <c r="L25" s="463" t="s">
+      <c r="E25" s="373"/>
+      <c r="F25" s="373"/>
+      <c r="G25" s="373"/>
+      <c r="H25" s="373"/>
+      <c r="I25" s="373"/>
+      <c r="J25" s="373"/>
+      <c r="K25" s="374"/>
+      <c r="L25" s="464" t="s">
         <v>44</v>
       </c>
-      <c r="M25" s="464"/>
-      <c r="N25" s="464"/>
-      <c r="O25" s="465"/>
-      <c r="P25" s="466"/>
-      <c r="Q25" s="467"/>
-      <c r="R25" s="467"/>
-      <c r="S25" s="468"/>
-      <c r="T25" s="469"/>
-      <c r="U25" s="470"/>
-      <c r="V25" s="470"/>
-      <c r="W25" s="470"/>
-      <c r="X25" s="471"/>
-      <c r="Y25" s="461" t="s">
-        <v>265</v>
-      </c>
-      <c r="Z25" s="461"/>
-      <c r="AA25" s="462"/>
+      <c r="M25" s="465"/>
+      <c r="N25" s="465"/>
+      <c r="O25" s="466"/>
+      <c r="P25" s="467"/>
+      <c r="Q25" s="468"/>
+      <c r="R25" s="468"/>
+      <c r="S25" s="469"/>
+      <c r="T25" s="470"/>
+      <c r="U25" s="471"/>
+      <c r="V25" s="471"/>
+      <c r="W25" s="471"/>
+      <c r="X25" s="472"/>
+      <c r="Y25" s="462" t="s">
+        <v>264</v>
+      </c>
+      <c r="Z25" s="462"/>
+      <c r="AA25" s="463"/>
       <c r="AB25" s="5"/>
     </row>
     <row r="26" spans="1:28" s="6" customFormat="1" ht="35.1" customHeight="1">
@@ -17016,132 +17013,132 @@
       <c r="C26" s="61">
         <v>3</v>
       </c>
-      <c r="D26" s="363" t="s">
+      <c r="D26" s="372" t="s">
         <v>88</v>
       </c>
-      <c r="E26" s="364"/>
-      <c r="F26" s="364"/>
-      <c r="G26" s="364"/>
-      <c r="H26" s="364"/>
-      <c r="I26" s="364"/>
-      <c r="J26" s="364"/>
-      <c r="K26" s="365"/>
-      <c r="L26" s="366" t="s">
+      <c r="E26" s="373"/>
+      <c r="F26" s="373"/>
+      <c r="G26" s="373"/>
+      <c r="H26" s="373"/>
+      <c r="I26" s="373"/>
+      <c r="J26" s="373"/>
+      <c r="K26" s="374"/>
+      <c r="L26" s="375" t="s">
         <v>44</v>
       </c>
-      <c r="M26" s="367"/>
-      <c r="N26" s="367"/>
-      <c r="O26" s="368"/>
-      <c r="P26" s="369"/>
-      <c r="Q26" s="370"/>
-      <c r="R26" s="370"/>
-      <c r="S26" s="371"/>
-      <c r="T26" s="372"/>
-      <c r="U26" s="373"/>
-      <c r="V26" s="373"/>
-      <c r="W26" s="373"/>
-      <c r="X26" s="374"/>
-      <c r="Y26" s="461"/>
-      <c r="Z26" s="461"/>
-      <c r="AA26" s="462"/>
+      <c r="M26" s="376"/>
+      <c r="N26" s="376"/>
+      <c r="O26" s="377"/>
+      <c r="P26" s="378"/>
+      <c r="Q26" s="379"/>
+      <c r="R26" s="379"/>
+      <c r="S26" s="380"/>
+      <c r="T26" s="381"/>
+      <c r="U26" s="382"/>
+      <c r="V26" s="382"/>
+      <c r="W26" s="382"/>
+      <c r="X26" s="383"/>
+      <c r="Y26" s="462"/>
+      <c r="Z26" s="462"/>
+      <c r="AA26" s="463"/>
       <c r="AB26" s="5"/>
     </row>
     <row r="27" spans="1:28" s="28" customFormat="1" ht="35.1" customHeight="1">
       <c r="A27" s="25"/>
       <c r="B27" s="26"/>
-      <c r="C27" s="381" t="s">
+      <c r="C27" s="354" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="381"/>
-      <c r="E27" s="381"/>
-      <c r="F27" s="381"/>
-      <c r="G27" s="381"/>
-      <c r="H27" s="381"/>
-      <c r="I27" s="381"/>
-      <c r="J27" s="381"/>
-      <c r="K27" s="382"/>
-      <c r="L27" s="389"/>
-      <c r="M27" s="381"/>
-      <c r="N27" s="381"/>
-      <c r="O27" s="382"/>
-      <c r="P27" s="458"/>
-      <c r="Q27" s="459"/>
-      <c r="R27" s="459"/>
-      <c r="S27" s="460"/>
-      <c r="T27" s="357"/>
-      <c r="U27" s="358"/>
-      <c r="V27" s="358"/>
-      <c r="W27" s="358"/>
-      <c r="X27" s="359"/>
-      <c r="Y27" s="461"/>
-      <c r="Z27" s="461"/>
-      <c r="AA27" s="462"/>
+      <c r="D27" s="354"/>
+      <c r="E27" s="354"/>
+      <c r="F27" s="354"/>
+      <c r="G27" s="354"/>
+      <c r="H27" s="354"/>
+      <c r="I27" s="354"/>
+      <c r="J27" s="354"/>
+      <c r="K27" s="355"/>
+      <c r="L27" s="353"/>
+      <c r="M27" s="354"/>
+      <c r="N27" s="354"/>
+      <c r="O27" s="355"/>
+      <c r="P27" s="459"/>
+      <c r="Q27" s="460"/>
+      <c r="R27" s="460"/>
+      <c r="S27" s="461"/>
+      <c r="T27" s="363"/>
+      <c r="U27" s="364"/>
+      <c r="V27" s="364"/>
+      <c r="W27" s="364"/>
+      <c r="X27" s="365"/>
+      <c r="Y27" s="462"/>
+      <c r="Z27" s="462"/>
+      <c r="AA27" s="463"/>
       <c r="AB27" s="27"/>
     </row>
     <row r="28" spans="1:28" s="28" customFormat="1" ht="39.75" customHeight="1">
       <c r="A28" s="25"/>
       <c r="B28" s="26"/>
-      <c r="C28" s="386" t="s">
+      <c r="C28" s="473" t="s">
         <v>93</v>
       </c>
-      <c r="D28" s="387"/>
-      <c r="E28" s="387"/>
-      <c r="F28" s="387"/>
-      <c r="G28" s="387"/>
-      <c r="H28" s="387"/>
-      <c r="I28" s="387"/>
-      <c r="J28" s="387"/>
-      <c r="K28" s="387"/>
-      <c r="L28" s="387"/>
-      <c r="M28" s="387"/>
-      <c r="N28" s="387"/>
-      <c r="O28" s="387"/>
-      <c r="P28" s="387"/>
-      <c r="Q28" s="387"/>
-      <c r="R28" s="387"/>
-      <c r="S28" s="388"/>
-      <c r="T28" s="383"/>
-      <c r="U28" s="384"/>
-      <c r="V28" s="384"/>
-      <c r="W28" s="384"/>
-      <c r="X28" s="385"/>
-      <c r="Y28" s="452" t="s">
+      <c r="D28" s="474"/>
+      <c r="E28" s="474"/>
+      <c r="F28" s="474"/>
+      <c r="G28" s="474"/>
+      <c r="H28" s="474"/>
+      <c r="I28" s="474"/>
+      <c r="J28" s="474"/>
+      <c r="K28" s="474"/>
+      <c r="L28" s="474"/>
+      <c r="M28" s="474"/>
+      <c r="N28" s="474"/>
+      <c r="O28" s="474"/>
+      <c r="P28" s="474"/>
+      <c r="Q28" s="474"/>
+      <c r="R28" s="474"/>
+      <c r="S28" s="475"/>
+      <c r="T28" s="356"/>
+      <c r="U28" s="357"/>
+      <c r="V28" s="357"/>
+      <c r="W28" s="357"/>
+      <c r="X28" s="358"/>
+      <c r="Y28" s="453" t="s">
         <v>207</v>
       </c>
-      <c r="Z28" s="453"/>
-      <c r="AA28" s="454"/>
+      <c r="Z28" s="454"/>
+      <c r="AA28" s="455"/>
       <c r="AB28" s="27"/>
     </row>
     <row r="29" spans="1:28" s="28" customFormat="1" ht="39.75" customHeight="1">
       <c r="A29" s="25"/>
       <c r="B29" s="26"/>
-      <c r="C29" s="386" t="s">
+      <c r="C29" s="473" t="s">
         <v>106</v>
       </c>
-      <c r="D29" s="387"/>
-      <c r="E29" s="387"/>
-      <c r="F29" s="387"/>
-      <c r="G29" s="387"/>
-      <c r="H29" s="387"/>
-      <c r="I29" s="387"/>
-      <c r="J29" s="387"/>
-      <c r="K29" s="387"/>
-      <c r="L29" s="387"/>
-      <c r="M29" s="387"/>
-      <c r="N29" s="387"/>
-      <c r="O29" s="387"/>
-      <c r="P29" s="387"/>
-      <c r="Q29" s="387"/>
-      <c r="R29" s="387"/>
-      <c r="S29" s="388"/>
-      <c r="T29" s="383"/>
-      <c r="U29" s="384"/>
-      <c r="V29" s="384"/>
-      <c r="W29" s="384"/>
-      <c r="X29" s="385"/>
-      <c r="Y29" s="455"/>
-      <c r="Z29" s="456"/>
-      <c r="AA29" s="457"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
+      <c r="G29" s="474"/>
+      <c r="H29" s="474"/>
+      <c r="I29" s="474"/>
+      <c r="J29" s="474"/>
+      <c r="K29" s="474"/>
+      <c r="L29" s="474"/>
+      <c r="M29" s="474"/>
+      <c r="N29" s="474"/>
+      <c r="O29" s="474"/>
+      <c r="P29" s="474"/>
+      <c r="Q29" s="474"/>
+      <c r="R29" s="474"/>
+      <c r="S29" s="475"/>
+      <c r="T29" s="356"/>
+      <c r="U29" s="357"/>
+      <c r="V29" s="357"/>
+      <c r="W29" s="357"/>
+      <c r="X29" s="358"/>
+      <c r="Y29" s="456"/>
+      <c r="Z29" s="457"/>
+      <c r="AA29" s="458"/>
       <c r="AB29" s="27"/>
     </row>
     <row r="30" spans="1:28" s="6" customFormat="1" ht="24" customHeight="1">
@@ -17414,6 +17411,9 @@
     <mergeCell ref="Y26:AA26"/>
     <mergeCell ref="Y27:AA27"/>
     <mergeCell ref="Y25:AA25"/>
+    <mergeCell ref="T29:X29"/>
+    <mergeCell ref="C28:S28"/>
+    <mergeCell ref="C29:S29"/>
     <mergeCell ref="D23:K23"/>
     <mergeCell ref="X14:AA14"/>
     <mergeCell ref="W18:Y18"/>
@@ -17430,6 +17430,15 @@
     <mergeCell ref="Y23:AA23"/>
     <mergeCell ref="P23:S23"/>
     <mergeCell ref="C22:F22"/>
+    <mergeCell ref="J17:AA17"/>
+    <mergeCell ref="U14:W14"/>
+    <mergeCell ref="X11:AA11"/>
+    <mergeCell ref="X13:AA13"/>
+    <mergeCell ref="X12:AA12"/>
+    <mergeCell ref="U13:W13"/>
+    <mergeCell ref="U12:W12"/>
+    <mergeCell ref="F11:L11"/>
+    <mergeCell ref="D17:H17"/>
     <mergeCell ref="D16:H16"/>
     <mergeCell ref="N14:P14"/>
     <mergeCell ref="Q14:T14"/>
@@ -17437,13 +17446,6 @@
     <mergeCell ref="F14:J14"/>
     <mergeCell ref="D15:H15"/>
     <mergeCell ref="N12:P13"/>
-    <mergeCell ref="J17:AA17"/>
-    <mergeCell ref="U14:W14"/>
-    <mergeCell ref="X11:AA11"/>
-    <mergeCell ref="X13:AA13"/>
-    <mergeCell ref="X12:AA12"/>
-    <mergeCell ref="U13:W13"/>
-    <mergeCell ref="U12:W12"/>
     <mergeCell ref="A2:AA2"/>
     <mergeCell ref="S4:AA4"/>
     <mergeCell ref="N9:P9"/>
@@ -17467,9 +17469,6 @@
     <mergeCell ref="P30:S30"/>
     <mergeCell ref="T30:X30"/>
     <mergeCell ref="Y30:AA30"/>
-    <mergeCell ref="T29:X29"/>
-    <mergeCell ref="C28:S28"/>
-    <mergeCell ref="C29:S29"/>
     <mergeCell ref="L27:O27"/>
     <mergeCell ref="T28:X28"/>
     <mergeCell ref="G22:K22"/>
@@ -17486,8 +17485,6 @@
     <mergeCell ref="R19:V19"/>
     <mergeCell ref="W19:AA19"/>
     <mergeCell ref="C27:K27"/>
-    <mergeCell ref="F11:L11"/>
-    <mergeCell ref="D17:H17"/>
   </mergeCells>
   <phoneticPr fontId="95" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -17519,18 +17516,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="35.25" customHeight="1">
-      <c r="A1" s="528" t="s">
+      <c r="A1" s="532" t="s">
         <v>115</v>
       </c>
-      <c r="B1" s="528"/>
-      <c r="C1" s="528"/>
-      <c r="D1" s="528"/>
-      <c r="E1" s="528"/>
-      <c r="F1" s="528"/>
-      <c r="G1" s="528"/>
-      <c r="H1" s="528"/>
-      <c r="I1" s="528"/>
-      <c r="J1" s="528"/>
+      <c r="B1" s="532"/>
+      <c r="C1" s="532"/>
+      <c r="D1" s="532"/>
+      <c r="E1" s="532"/>
+      <c r="F1" s="532"/>
+      <c r="G1" s="532"/>
+      <c r="H1" s="532"/>
+      <c r="I1" s="532"/>
+      <c r="J1" s="532"/>
     </row>
     <row r="2" spans="1:10" ht="27.95" customHeight="1" thickBot="1">
       <c r="A2" s="37"/>
@@ -17544,11 +17541,11 @@
       <c r="I2" s="37"/>
     </row>
     <row r="3" spans="1:10" ht="27.95" customHeight="1" thickBot="1">
-      <c r="A3" s="537" t="s">
+      <c r="A3" s="541" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="538"/>
-      <c r="C3" s="539"/>
+      <c r="B3" s="542"/>
+      <c r="C3" s="543"/>
       <c r="D3" s="38"/>
       <c r="E3" s="38"/>
       <c r="F3" s="38"/>
@@ -17567,20 +17564,20 @@
       <c r="D4" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="E4" s="530" t="s">
+      <c r="E4" s="534" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="531"/>
+      <c r="F4" s="535"/>
       <c r="G4" s="42" t="s">
         <v>2</v>
       </c>
       <c r="H4" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="I4" s="535" t="s">
+      <c r="I4" s="539" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="536"/>
+      <c r="J4" s="540"/>
     </row>
     <row r="5" spans="1:10" ht="27.95" customHeight="1">
       <c r="A5" s="320" t="s">
@@ -17591,12 +17588,12 @@
         <v>4</v>
       </c>
       <c r="D5" s="45"/>
-      <c r="E5" s="540"/>
-      <c r="F5" s="541"/>
-      <c r="G5" s="541"/>
-      <c r="H5" s="541"/>
-      <c r="I5" s="541"/>
-      <c r="J5" s="542"/>
+      <c r="E5" s="544"/>
+      <c r="F5" s="545"/>
+      <c r="G5" s="545"/>
+      <c r="H5" s="545"/>
+      <c r="I5" s="545"/>
+      <c r="J5" s="546"/>
     </row>
     <row r="6" spans="1:10" ht="27.95" customHeight="1">
       <c r="A6" s="321"/>
@@ -17609,12 +17606,12 @@
       <c r="D6" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="485"/>
-      <c r="F6" s="529"/>
+      <c r="E6" s="489"/>
+      <c r="F6" s="533"/>
       <c r="G6" s="46"/>
       <c r="H6" s="47"/>
-      <c r="I6" s="483"/>
-      <c r="J6" s="484"/>
+      <c r="I6" s="487"/>
+      <c r="J6" s="488"/>
     </row>
     <row r="7" spans="1:10" ht="27.95" customHeight="1">
       <c r="A7" s="321"/>
@@ -17627,12 +17624,12 @@
       <c r="D7" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="485"/>
-      <c r="F7" s="529"/>
+      <c r="E7" s="489"/>
+      <c r="F7" s="533"/>
       <c r="G7" s="46"/>
       <c r="H7" s="47"/>
-      <c r="I7" s="483"/>
-      <c r="J7" s="484"/>
+      <c r="I7" s="487"/>
+      <c r="J7" s="488"/>
     </row>
     <row r="8" spans="1:10" ht="27.95" customHeight="1">
       <c r="A8" s="321"/>
@@ -17645,12 +17642,12 @@
       <c r="D8" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="E8" s="485"/>
-      <c r="F8" s="529"/>
+      <c r="E8" s="489"/>
+      <c r="F8" s="533"/>
       <c r="G8" s="46"/>
       <c r="H8" s="47"/>
-      <c r="I8" s="483"/>
-      <c r="J8" s="484"/>
+      <c r="I8" s="487"/>
+      <c r="J8" s="488"/>
     </row>
     <row r="9" spans="1:10" ht="27.95" customHeight="1">
       <c r="A9" s="321"/>
@@ -17663,26 +17660,26 @@
       <c r="D9" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="E9" s="485"/>
-      <c r="F9" s="529"/>
+      <c r="E9" s="489"/>
+      <c r="F9" s="533"/>
       <c r="G9" s="47"/>
       <c r="H9" s="47"/>
-      <c r="I9" s="483"/>
-      <c r="J9" s="484"/>
+      <c r="I9" s="487"/>
+      <c r="J9" s="488"/>
     </row>
     <row r="10" spans="1:10" ht="27.95" customHeight="1">
-      <c r="A10" s="532" t="s">
+      <c r="A10" s="536" t="s">
         <v>61</v>
       </c>
-      <c r="B10" s="533"/>
-      <c r="C10" s="534"/>
+      <c r="B10" s="537"/>
+      <c r="C10" s="538"/>
       <c r="D10" s="55"/>
-      <c r="E10" s="485"/>
-      <c r="F10" s="486"/>
+      <c r="E10" s="489"/>
+      <c r="F10" s="490"/>
       <c r="G10" s="46"/>
       <c r="H10" s="47"/>
-      <c r="I10" s="483"/>
-      <c r="J10" s="484"/>
+      <c r="I10" s="487"/>
+      <c r="J10" s="488"/>
     </row>
     <row r="11" spans="1:10" ht="27.95" customHeight="1">
       <c r="A11" s="320" t="s">
@@ -17695,18 +17692,18 @@
       <c r="D11" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="E11" s="478" t="s">
+      <c r="E11" s="482" t="s">
         <v>46</v>
       </c>
-      <c r="F11" s="479"/>
+      <c r="F11" s="483"/>
       <c r="G11" s="49">
         <v>0.1</v>
       </c>
       <c r="H11" s="50"/>
-      <c r="I11" s="487" t="s">
+      <c r="I11" s="491" t="s">
         <v>59</v>
       </c>
-      <c r="J11" s="488"/>
+      <c r="J11" s="492"/>
     </row>
     <row r="12" spans="1:10" ht="27.95" customHeight="1">
       <c r="A12" s="320" t="s">
@@ -17719,18 +17716,18 @@
       <c r="D12" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="478" t="s">
+      <c r="E12" s="482" t="s">
         <v>46</v>
       </c>
-      <c r="F12" s="479"/>
+      <c r="F12" s="483"/>
       <c r="G12" s="49">
         <v>1.1000000000000001</v>
       </c>
       <c r="H12" s="50"/>
-      <c r="I12" s="473" t="s">
+      <c r="I12" s="477" t="s">
         <v>17</v>
       </c>
-      <c r="J12" s="474"/>
+      <c r="J12" s="478"/>
     </row>
     <row r="13" spans="1:10" ht="27.95" customHeight="1">
       <c r="A13" s="320" t="s">
@@ -17743,18 +17740,18 @@
       <c r="D13" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="E13" s="478" t="s">
+      <c r="E13" s="482" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="479"/>
+      <c r="F13" s="483"/>
       <c r="G13" s="49">
         <v>0.2</v>
       </c>
       <c r="H13" s="50"/>
-      <c r="I13" s="473" t="s">
+      <c r="I13" s="477" t="s">
         <v>15</v>
       </c>
-      <c r="J13" s="474"/>
+      <c r="J13" s="478"/>
     </row>
     <row r="14" spans="1:10" ht="27.95" customHeight="1">
       <c r="A14" s="320" t="s">
@@ -17765,14 +17762,14 @@
         <v>64</v>
       </c>
       <c r="D14" s="48"/>
-      <c r="E14" s="478" t="s">
+      <c r="E14" s="482" t="s">
         <v>65</v>
       </c>
-      <c r="F14" s="479"/>
+      <c r="F14" s="483"/>
       <c r="G14" s="49"/>
       <c r="H14" s="68"/>
-      <c r="I14" s="480"/>
-      <c r="J14" s="481"/>
+      <c r="I14" s="484"/>
+      <c r="J14" s="485"/>
     </row>
     <row r="15" spans="1:10" ht="27.95" customHeight="1">
       <c r="A15" s="320" t="s">
@@ -17783,12 +17780,12 @@
         <v>77</v>
       </c>
       <c r="D15" s="48"/>
-      <c r="E15" s="478"/>
-      <c r="F15" s="479"/>
-      <c r="G15" s="482"/>
+      <c r="E15" s="482"/>
+      <c r="F15" s="483"/>
+      <c r="G15" s="486"/>
       <c r="H15" s="68"/>
-      <c r="I15" s="480"/>
-      <c r="J15" s="481"/>
+      <c r="I15" s="484"/>
+      <c r="J15" s="485"/>
     </row>
     <row r="16" spans="1:10" ht="7.5" customHeight="1">
       <c r="A16" s="322"/>
@@ -17815,8 +17812,8 @@
       <c r="F17" s="327"/>
       <c r="G17" s="328"/>
       <c r="H17" s="329"/>
-      <c r="I17" s="497"/>
-      <c r="J17" s="498"/>
+      <c r="I17" s="501"/>
+      <c r="J17" s="502"/>
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" thickBot="1">
       <c r="A18" s="37"/>
@@ -17830,18 +17827,18 @@
       <c r="I18" s="37"/>
     </row>
     <row r="19" spans="1:10" ht="24" customHeight="1">
-      <c r="A19" s="494" t="s">
+      <c r="A19" s="498" t="s">
         <v>125</v>
       </c>
-      <c r="B19" s="495"/>
-      <c r="C19" s="495"/>
-      <c r="D19" s="495"/>
-      <c r="E19" s="495"/>
-      <c r="F19" s="495"/>
-      <c r="G19" s="495"/>
-      <c r="H19" s="495"/>
-      <c r="I19" s="495"/>
-      <c r="J19" s="496"/>
+      <c r="B19" s="499"/>
+      <c r="C19" s="499"/>
+      <c r="D19" s="499"/>
+      <c r="E19" s="499"/>
+      <c r="F19" s="499"/>
+      <c r="G19" s="499"/>
+      <c r="H19" s="499"/>
+      <c r="I19" s="499"/>
+      <c r="J19" s="500"/>
     </row>
     <row r="20" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A20" s="103"/>
@@ -17941,120 +17938,120 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="110"/>
-      <c r="B27" s="499" t="s">
+      <c r="B27" s="503" t="s">
         <v>100</v>
       </c>
-      <c r="C27" s="500"/>
-      <c r="D27" s="520" t="s">
+      <c r="C27" s="504"/>
+      <c r="D27" s="524" t="s">
         <v>120</v>
       </c>
-      <c r="E27" s="521"/>
-      <c r="F27" s="521"/>
-      <c r="G27" s="521"/>
-      <c r="H27" s="521"/>
-      <c r="I27" s="500"/>
+      <c r="E27" s="525"/>
+      <c r="F27" s="525"/>
+      <c r="G27" s="525"/>
+      <c r="H27" s="525"/>
+      <c r="I27" s="504"/>
       <c r="J27" s="111"/>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="112"/>
-      <c r="B28" s="501" t="s">
+      <c r="B28" s="505" t="s">
         <v>116</v>
       </c>
-      <c r="C28" s="502"/>
-      <c r="D28" s="511" t="s">
+      <c r="C28" s="506"/>
+      <c r="D28" s="515" t="s">
         <v>126</v>
       </c>
-      <c r="E28" s="512"/>
-      <c r="F28" s="512"/>
-      <c r="G28" s="512"/>
-      <c r="H28" s="512"/>
-      <c r="I28" s="513"/>
+      <c r="E28" s="516"/>
+      <c r="F28" s="516"/>
+      <c r="G28" s="516"/>
+      <c r="H28" s="516"/>
+      <c r="I28" s="517"/>
       <c r="J28" s="113"/>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="112"/>
-      <c r="B29" s="503"/>
-      <c r="C29" s="504"/>
-      <c r="D29" s="514"/>
-      <c r="E29" s="515"/>
-      <c r="F29" s="515"/>
-      <c r="G29" s="515"/>
-      <c r="H29" s="515"/>
-      <c r="I29" s="516"/>
+      <c r="B29" s="507"/>
+      <c r="C29" s="508"/>
+      <c r="D29" s="518"/>
+      <c r="E29" s="519"/>
+      <c r="F29" s="519"/>
+      <c r="G29" s="519"/>
+      <c r="H29" s="519"/>
+      <c r="I29" s="520"/>
       <c r="J29" s="113"/>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="112"/>
-      <c r="B30" s="505"/>
-      <c r="C30" s="506"/>
-      <c r="D30" s="517"/>
-      <c r="E30" s="518"/>
-      <c r="F30" s="518"/>
-      <c r="G30" s="518"/>
-      <c r="H30" s="518"/>
-      <c r="I30" s="519"/>
+      <c r="B30" s="509"/>
+      <c r="C30" s="510"/>
+      <c r="D30" s="521"/>
+      <c r="E30" s="522"/>
+      <c r="F30" s="522"/>
+      <c r="G30" s="522"/>
+      <c r="H30" s="522"/>
+      <c r="I30" s="523"/>
       <c r="J30" s="113"/>
     </row>
     <row r="31" spans="1:10" ht="27.95" customHeight="1">
       <c r="A31" s="112"/>
-      <c r="B31" s="507" t="s">
+      <c r="B31" s="511" t="s">
         <v>117</v>
       </c>
-      <c r="C31" s="508"/>
-      <c r="D31" s="522" t="s">
+      <c r="C31" s="512"/>
+      <c r="D31" s="526" t="s">
         <v>121</v>
       </c>
-      <c r="E31" s="523"/>
-      <c r="F31" s="523"/>
-      <c r="G31" s="523"/>
-      <c r="H31" s="523"/>
-      <c r="I31" s="524"/>
+      <c r="E31" s="527"/>
+      <c r="F31" s="527"/>
+      <c r="G31" s="527"/>
+      <c r="H31" s="527"/>
+      <c r="I31" s="528"/>
       <c r="J31" s="114"/>
     </row>
     <row r="32" spans="1:10" ht="14.1" customHeight="1">
       <c r="A32" s="112"/>
-      <c r="B32" s="509" t="s">
+      <c r="B32" s="513" t="s">
         <v>118</v>
       </c>
-      <c r="C32" s="510"/>
-      <c r="D32" s="525" t="s">
+      <c r="C32" s="514"/>
+      <c r="D32" s="529" t="s">
         <v>122</v>
       </c>
-      <c r="E32" s="526"/>
-      <c r="F32" s="526"/>
-      <c r="G32" s="526"/>
-      <c r="H32" s="526"/>
-      <c r="I32" s="527"/>
+      <c r="E32" s="530"/>
+      <c r="F32" s="530"/>
+      <c r="G32" s="530"/>
+      <c r="H32" s="530"/>
+      <c r="I32" s="531"/>
       <c r="J32" s="114"/>
     </row>
     <row r="33" spans="1:10" ht="14.1" customHeight="1">
       <c r="A33" s="112"/>
-      <c r="B33" s="505"/>
-      <c r="C33" s="506"/>
-      <c r="D33" s="475" t="s">
+      <c r="B33" s="509"/>
+      <c r="C33" s="510"/>
+      <c r="D33" s="479" t="s">
         <v>123</v>
       </c>
-      <c r="E33" s="476"/>
-      <c r="F33" s="476"/>
-      <c r="G33" s="476"/>
-      <c r="H33" s="476"/>
-      <c r="I33" s="477"/>
+      <c r="E33" s="480"/>
+      <c r="F33" s="480"/>
+      <c r="G33" s="480"/>
+      <c r="H33" s="480"/>
+      <c r="I33" s="481"/>
       <c r="J33" s="114"/>
     </row>
     <row r="34" spans="1:10" ht="27.95" customHeight="1">
       <c r="A34" s="112"/>
-      <c r="B34" s="489" t="s">
+      <c r="B34" s="493" t="s">
         <v>119</v>
       </c>
-      <c r="C34" s="490"/>
-      <c r="D34" s="491" t="s">
+      <c r="C34" s="494"/>
+      <c r="D34" s="495" t="s">
         <v>124</v>
       </c>
-      <c r="E34" s="492"/>
-      <c r="F34" s="492"/>
-      <c r="G34" s="492"/>
-      <c r="H34" s="492"/>
-      <c r="I34" s="493"/>
+      <c r="E34" s="496"/>
+      <c r="F34" s="496"/>
+      <c r="G34" s="496"/>
+      <c r="H34" s="496"/>
+      <c r="I34" s="497"/>
       <c r="J34" s="114"/>
     </row>
     <row r="35" spans="1:10" ht="34.5" customHeight="1" thickBot="1">
@@ -18070,16 +18067,16 @@
       <c r="J35" s="332"/>
     </row>
     <row r="36" spans="1:10" ht="30" customHeight="1">
-      <c r="A36" s="472"/>
-      <c r="B36" s="472"/>
-      <c r="C36" s="472"/>
-      <c r="D36" s="472"/>
-      <c r="E36" s="472"/>
-      <c r="F36" s="472"/>
-      <c r="G36" s="472"/>
-      <c r="H36" s="472"/>
-      <c r="I36" s="472"/>
-      <c r="J36" s="472"/>
+      <c r="A36" s="476"/>
+      <c r="B36" s="476"/>
+      <c r="C36" s="476"/>
+      <c r="D36" s="476"/>
+      <c r="E36" s="476"/>
+      <c r="F36" s="476"/>
+      <c r="G36" s="476"/>
+      <c r="H36" s="476"/>
+      <c r="I36" s="476"/>
+      <c r="J36" s="476"/>
     </row>
     <row r="37" spans="1:10"/>
     <row r="38" spans="1:10" hidden="1">
@@ -18160,18 +18157,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="35.25" customHeight="1">
-      <c r="A1" s="528" t="s">
+      <c r="A1" s="532" t="s">
         <v>128</v>
       </c>
-      <c r="B1" s="528"/>
-      <c r="C1" s="528"/>
-      <c r="D1" s="528"/>
-      <c r="E1" s="528"/>
-      <c r="F1" s="528"/>
-      <c r="G1" s="528"/>
-      <c r="H1" s="528"/>
-      <c r="I1" s="528"/>
-      <c r="J1" s="528"/>
+      <c r="B1" s="532"/>
+      <c r="C1" s="532"/>
+      <c r="D1" s="532"/>
+      <c r="E1" s="532"/>
+      <c r="F1" s="532"/>
+      <c r="G1" s="532"/>
+      <c r="H1" s="532"/>
+      <c r="I1" s="532"/>
+      <c r="J1" s="532"/>
     </row>
     <row r="2" spans="1:10" ht="27.95" customHeight="1" thickBot="1">
       <c r="A2" s="37"/>
@@ -18185,11 +18182,11 @@
       <c r="I2" s="37"/>
     </row>
     <row r="3" spans="1:10" ht="27.95" customHeight="1" thickBot="1">
-      <c r="A3" s="555" t="s">
+      <c r="A3" s="559" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="556"/>
-      <c r="C3" s="557"/>
+      <c r="B3" s="560"/>
+      <c r="C3" s="561"/>
       <c r="D3" s="38"/>
       <c r="E3" s="38"/>
       <c r="F3" s="38"/>
@@ -18208,20 +18205,20 @@
       <c r="D4" s="83" t="s">
         <v>41</v>
       </c>
-      <c r="E4" s="558" t="s">
+      <c r="E4" s="562" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="559"/>
+      <c r="F4" s="563"/>
       <c r="G4" s="84" t="s">
         <v>2</v>
       </c>
       <c r="H4" s="84" t="s">
         <v>40</v>
       </c>
-      <c r="I4" s="560" t="s">
+      <c r="I4" s="564" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="561"/>
+      <c r="J4" s="565"/>
     </row>
     <row r="5" spans="1:10" ht="27.95" customHeight="1">
       <c r="A5" s="341" t="s">
@@ -18232,14 +18229,14 @@
         <v>37</v>
       </c>
       <c r="D5" s="87"/>
-      <c r="E5" s="562" t="s">
-        <v>286</v>
-      </c>
-      <c r="F5" s="563"/>
-      <c r="G5" s="563"/>
-      <c r="H5" s="563"/>
-      <c r="I5" s="563"/>
-      <c r="J5" s="564"/>
+      <c r="E5" s="566" t="s">
+        <v>285</v>
+      </c>
+      <c r="F5" s="567"/>
+      <c r="G5" s="567"/>
+      <c r="H5" s="567"/>
+      <c r="I5" s="567"/>
+      <c r="J5" s="568"/>
     </row>
     <row r="6" spans="1:10" ht="27.95" customHeight="1">
       <c r="A6" s="342"/>
@@ -18252,12 +18249,12 @@
       <c r="D6" s="90" t="s">
         <v>53</v>
       </c>
-      <c r="E6" s="553"/>
-      <c r="F6" s="554"/>
+      <c r="E6" s="557"/>
+      <c r="F6" s="558"/>
       <c r="G6" s="46"/>
       <c r="H6" s="54"/>
-      <c r="I6" s="483"/>
-      <c r="J6" s="484"/>
+      <c r="I6" s="487"/>
+      <c r="J6" s="488"/>
     </row>
     <row r="7" spans="1:10" ht="27.95" customHeight="1">
       <c r="A7" s="343"/>
@@ -18270,12 +18267,12 @@
       <c r="D7" s="90" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="553"/>
-      <c r="F7" s="554"/>
+      <c r="E7" s="557"/>
+      <c r="F7" s="558"/>
       <c r="G7" s="46"/>
       <c r="H7" s="54"/>
-      <c r="I7" s="483"/>
-      <c r="J7" s="484"/>
+      <c r="I7" s="487"/>
+      <c r="J7" s="488"/>
     </row>
     <row r="8" spans="1:10" ht="27.95" customHeight="1">
       <c r="A8" s="343"/>
@@ -18288,12 +18285,12 @@
       <c r="D8" s="90" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="553"/>
-      <c r="F8" s="554"/>
+      <c r="E8" s="557"/>
+      <c r="F8" s="558"/>
       <c r="G8" s="46"/>
       <c r="H8" s="54"/>
-      <c r="I8" s="483"/>
-      <c r="J8" s="484"/>
+      <c r="I8" s="487"/>
+      <c r="J8" s="488"/>
     </row>
     <row r="9" spans="1:10" ht="27.95" customHeight="1">
       <c r="A9" s="343"/>
@@ -18306,26 +18303,26 @@
       <c r="D9" s="90" t="s">
         <v>53</v>
       </c>
-      <c r="E9" s="553"/>
-      <c r="F9" s="554"/>
+      <c r="E9" s="557"/>
+      <c r="F9" s="558"/>
       <c r="G9" s="47"/>
       <c r="H9" s="54"/>
-      <c r="I9" s="483"/>
-      <c r="J9" s="484"/>
+      <c r="I9" s="487"/>
+      <c r="J9" s="488"/>
     </row>
     <row r="10" spans="1:10" ht="27.95" customHeight="1">
-      <c r="A10" s="548" t="s">
+      <c r="A10" s="552" t="s">
         <v>60</v>
       </c>
-      <c r="B10" s="549"/>
-      <c r="C10" s="550"/>
+      <c r="B10" s="553"/>
+      <c r="C10" s="554"/>
       <c r="D10" s="90"/>
-      <c r="E10" s="551"/>
-      <c r="F10" s="552"/>
+      <c r="E10" s="555"/>
+      <c r="F10" s="556"/>
       <c r="G10" s="56"/>
       <c r="H10" s="54"/>
-      <c r="I10" s="483"/>
-      <c r="J10" s="484"/>
+      <c r="I10" s="487"/>
+      <c r="J10" s="488"/>
     </row>
     <row r="11" spans="1:10" ht="27.95" customHeight="1">
       <c r="A11" s="341" t="s">
@@ -18338,18 +18335,18 @@
       <c r="D11" s="246" t="s">
         <v>261</v>
       </c>
-      <c r="E11" s="478" t="s">
+      <c r="E11" s="482" t="s">
         <v>52</v>
       </c>
-      <c r="F11" s="479"/>
+      <c r="F11" s="483"/>
       <c r="G11" s="72">
         <v>0.1</v>
       </c>
       <c r="H11" s="50"/>
-      <c r="I11" s="487" t="s">
+      <c r="I11" s="491" t="s">
         <v>59</v>
       </c>
-      <c r="J11" s="488"/>
+      <c r="J11" s="492"/>
     </row>
     <row r="12" spans="1:10" ht="27.95" customHeight="1">
       <c r="A12" s="341" t="s">
@@ -18362,18 +18359,18 @@
       <c r="D12" s="246" t="s">
         <v>261</v>
       </c>
-      <c r="E12" s="478" t="s">
+      <c r="E12" s="482" t="s">
         <v>52</v>
       </c>
-      <c r="F12" s="479"/>
+      <c r="F12" s="483"/>
       <c r="G12" s="72">
         <v>1.1000000000000001</v>
       </c>
       <c r="H12" s="50"/>
-      <c r="I12" s="473" t="s">
+      <c r="I12" s="477" t="s">
         <v>17</v>
       </c>
-      <c r="J12" s="474"/>
+      <c r="J12" s="478"/>
     </row>
     <row r="13" spans="1:10" ht="27.95" customHeight="1">
       <c r="A13" s="341" t="s">
@@ -18386,18 +18383,18 @@
       <c r="D13" s="246" t="s">
         <v>261</v>
       </c>
-      <c r="E13" s="478" t="s">
+      <c r="E13" s="482" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="479"/>
+      <c r="F13" s="483"/>
       <c r="G13" s="49">
         <v>0.2</v>
       </c>
       <c r="H13" s="50"/>
-      <c r="I13" s="473" t="s">
+      <c r="I13" s="477" t="s">
         <v>15</v>
       </c>
-      <c r="J13" s="474"/>
+      <c r="J13" s="478"/>
     </row>
     <row r="14" spans="1:10" ht="27.95" customHeight="1">
       <c r="A14" s="344" t="s">
@@ -18408,14 +18405,14 @@
         <v>7</v>
       </c>
       <c r="D14" s="87"/>
-      <c r="E14" s="478" t="s">
+      <c r="E14" s="482" t="s">
         <v>65</v>
       </c>
-      <c r="F14" s="479"/>
+      <c r="F14" s="483"/>
       <c r="G14" s="49"/>
       <c r="H14" s="68"/>
-      <c r="I14" s="480"/>
-      <c r="J14" s="481"/>
+      <c r="I14" s="484"/>
+      <c r="J14" s="485"/>
     </row>
     <row r="15" spans="1:10" ht="27.95" customHeight="1">
       <c r="A15" s="344" t="s">
@@ -18426,12 +18423,12 @@
         <v>81</v>
       </c>
       <c r="D15" s="87"/>
-      <c r="E15" s="478"/>
-      <c r="F15" s="479"/>
-      <c r="G15" s="482"/>
+      <c r="E15" s="482"/>
+      <c r="F15" s="483"/>
+      <c r="G15" s="486"/>
       <c r="H15" s="51"/>
-      <c r="I15" s="480"/>
-      <c r="J15" s="481"/>
+      <c r="I15" s="484"/>
+      <c r="J15" s="485"/>
     </row>
     <row r="16" spans="1:10" ht="7.5" customHeight="1">
       <c r="A16" s="338"/>
@@ -18458,8 +18455,8 @@
       <c r="F17" s="98"/>
       <c r="G17" s="99"/>
       <c r="H17" s="100"/>
-      <c r="I17" s="543"/>
-      <c r="J17" s="544"/>
+      <c r="I17" s="547"/>
+      <c r="J17" s="548"/>
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" thickBot="1">
       <c r="A18" s="37"/>
@@ -18473,18 +18470,18 @@
       <c r="I18" s="37"/>
     </row>
     <row r="19" spans="1:10" ht="24" customHeight="1">
-      <c r="A19" s="545" t="s">
+      <c r="A19" s="549" t="s">
         <v>125</v>
       </c>
-      <c r="B19" s="546"/>
-      <c r="C19" s="546"/>
-      <c r="D19" s="546"/>
-      <c r="E19" s="546"/>
-      <c r="F19" s="546"/>
-      <c r="G19" s="546"/>
-      <c r="H19" s="546"/>
-      <c r="I19" s="546"/>
-      <c r="J19" s="547"/>
+      <c r="B19" s="550"/>
+      <c r="C19" s="550"/>
+      <c r="D19" s="550"/>
+      <c r="E19" s="550"/>
+      <c r="F19" s="550"/>
+      <c r="G19" s="550"/>
+      <c r="H19" s="550"/>
+      <c r="I19" s="550"/>
+      <c r="J19" s="551"/>
     </row>
     <row r="20" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A20" s="103"/>
@@ -18584,120 +18581,120 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="110"/>
-      <c r="B27" s="499" t="s">
+      <c r="B27" s="503" t="s">
         <v>100</v>
       </c>
-      <c r="C27" s="500"/>
-      <c r="D27" s="520" t="s">
+      <c r="C27" s="504"/>
+      <c r="D27" s="524" t="s">
         <v>186</v>
       </c>
-      <c r="E27" s="521"/>
-      <c r="F27" s="521"/>
-      <c r="G27" s="521"/>
-      <c r="H27" s="521"/>
-      <c r="I27" s="500"/>
+      <c r="E27" s="525"/>
+      <c r="F27" s="525"/>
+      <c r="G27" s="525"/>
+      <c r="H27" s="525"/>
+      <c r="I27" s="504"/>
       <c r="J27" s="111"/>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="112"/>
-      <c r="B28" s="501" t="s">
+      <c r="B28" s="505" t="s">
         <v>116</v>
       </c>
-      <c r="C28" s="502"/>
-      <c r="D28" s="511" t="s">
+      <c r="C28" s="506"/>
+      <c r="D28" s="515" t="s">
         <v>129</v>
       </c>
-      <c r="E28" s="512"/>
-      <c r="F28" s="512"/>
-      <c r="G28" s="512"/>
-      <c r="H28" s="512"/>
-      <c r="I28" s="513"/>
+      <c r="E28" s="516"/>
+      <c r="F28" s="516"/>
+      <c r="G28" s="516"/>
+      <c r="H28" s="516"/>
+      <c r="I28" s="517"/>
       <c r="J28" s="113"/>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="112"/>
-      <c r="B29" s="503"/>
-      <c r="C29" s="504"/>
-      <c r="D29" s="514"/>
-      <c r="E29" s="515"/>
-      <c r="F29" s="515"/>
-      <c r="G29" s="515"/>
-      <c r="H29" s="515"/>
-      <c r="I29" s="516"/>
+      <c r="B29" s="507"/>
+      <c r="C29" s="508"/>
+      <c r="D29" s="518"/>
+      <c r="E29" s="519"/>
+      <c r="F29" s="519"/>
+      <c r="G29" s="519"/>
+      <c r="H29" s="519"/>
+      <c r="I29" s="520"/>
       <c r="J29" s="113"/>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="112"/>
-      <c r="B30" s="505"/>
-      <c r="C30" s="506"/>
-      <c r="D30" s="517"/>
-      <c r="E30" s="518"/>
-      <c r="F30" s="518"/>
-      <c r="G30" s="518"/>
-      <c r="H30" s="518"/>
-      <c r="I30" s="519"/>
+      <c r="B30" s="509"/>
+      <c r="C30" s="510"/>
+      <c r="D30" s="521"/>
+      <c r="E30" s="522"/>
+      <c r="F30" s="522"/>
+      <c r="G30" s="522"/>
+      <c r="H30" s="522"/>
+      <c r="I30" s="523"/>
       <c r="J30" s="113"/>
     </row>
     <row r="31" spans="1:10" ht="27.95" customHeight="1">
       <c r="A31" s="112"/>
-      <c r="B31" s="507" t="s">
+      <c r="B31" s="511" t="s">
         <v>117</v>
       </c>
-      <c r="C31" s="508"/>
-      <c r="D31" s="522" t="s">
+      <c r="C31" s="512"/>
+      <c r="D31" s="526" t="s">
         <v>130</v>
       </c>
-      <c r="E31" s="523"/>
-      <c r="F31" s="523"/>
-      <c r="G31" s="523"/>
-      <c r="H31" s="523"/>
-      <c r="I31" s="524"/>
+      <c r="E31" s="527"/>
+      <c r="F31" s="527"/>
+      <c r="G31" s="527"/>
+      <c r="H31" s="527"/>
+      <c r="I31" s="528"/>
       <c r="J31" s="114"/>
     </row>
     <row r="32" spans="1:10" ht="14.1" customHeight="1">
       <c r="A32" s="112"/>
-      <c r="B32" s="509" t="s">
+      <c r="B32" s="513" t="s">
         <v>118</v>
       </c>
-      <c r="C32" s="510"/>
-      <c r="D32" s="525" t="s">
+      <c r="C32" s="514"/>
+      <c r="D32" s="529" t="s">
         <v>131</v>
       </c>
-      <c r="E32" s="526"/>
-      <c r="F32" s="526"/>
-      <c r="G32" s="526"/>
-      <c r="H32" s="526"/>
-      <c r="I32" s="527"/>
+      <c r="E32" s="530"/>
+      <c r="F32" s="530"/>
+      <c r="G32" s="530"/>
+      <c r="H32" s="530"/>
+      <c r="I32" s="531"/>
       <c r="J32" s="114"/>
     </row>
     <row r="33" spans="1:10" ht="14.1" customHeight="1">
       <c r="A33" s="112"/>
-      <c r="B33" s="505"/>
-      <c r="C33" s="506"/>
-      <c r="D33" s="475" t="s">
+      <c r="B33" s="509"/>
+      <c r="C33" s="510"/>
+      <c r="D33" s="479" t="s">
         <v>132</v>
       </c>
-      <c r="E33" s="476"/>
-      <c r="F33" s="476"/>
-      <c r="G33" s="476"/>
-      <c r="H33" s="476"/>
-      <c r="I33" s="477"/>
+      <c r="E33" s="480"/>
+      <c r="F33" s="480"/>
+      <c r="G33" s="480"/>
+      <c r="H33" s="480"/>
+      <c r="I33" s="481"/>
       <c r="J33" s="114"/>
     </row>
     <row r="34" spans="1:10" ht="27.95" customHeight="1">
       <c r="A34" s="112"/>
-      <c r="B34" s="489" t="s">
+      <c r="B34" s="493" t="s">
         <v>119</v>
       </c>
-      <c r="C34" s="490"/>
-      <c r="D34" s="491" t="s">
+      <c r="C34" s="494"/>
+      <c r="D34" s="495" t="s">
         <v>133</v>
       </c>
-      <c r="E34" s="492"/>
-      <c r="F34" s="492"/>
-      <c r="G34" s="492"/>
-      <c r="H34" s="492"/>
-      <c r="I34" s="493"/>
+      <c r="E34" s="496"/>
+      <c r="F34" s="496"/>
+      <c r="G34" s="496"/>
+      <c r="H34" s="496"/>
+      <c r="I34" s="497"/>
       <c r="J34" s="114"/>
     </row>
     <row r="35" spans="1:10" ht="34.5" customHeight="1" thickBot="1">
@@ -18787,18 +18784,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="35.25" customHeight="1">
-      <c r="A1" s="528" t="s">
+      <c r="A1" s="532" t="s">
         <v>148</v>
       </c>
-      <c r="B1" s="528"/>
-      <c r="C1" s="528"/>
-      <c r="D1" s="528"/>
-      <c r="E1" s="528"/>
-      <c r="F1" s="528"/>
-      <c r="G1" s="528"/>
-      <c r="H1" s="528"/>
-      <c r="I1" s="528"/>
-      <c r="J1" s="528"/>
+      <c r="B1" s="532"/>
+      <c r="C1" s="532"/>
+      <c r="D1" s="532"/>
+      <c r="E1" s="532"/>
+      <c r="F1" s="532"/>
+      <c r="G1" s="532"/>
+      <c r="H1" s="532"/>
+      <c r="I1" s="532"/>
+      <c r="J1" s="532"/>
     </row>
     <row r="2" spans="1:10" ht="27.95" customHeight="1" thickBot="1">
       <c r="A2" s="37"/>
@@ -18812,11 +18809,11 @@
       <c r="I2" s="37"/>
     </row>
     <row r="3" spans="1:10" ht="27.95" customHeight="1" thickBot="1">
-      <c r="A3" s="592" t="s">
+      <c r="A3" s="596" t="s">
         <v>113</v>
       </c>
-      <c r="B3" s="593"/>
-      <c r="C3" s="594"/>
+      <c r="B3" s="597"/>
+      <c r="C3" s="598"/>
       <c r="D3" s="38"/>
       <c r="E3" s="38"/>
       <c r="F3" s="38"/>
@@ -18847,10 +18844,10 @@
       <c r="H4" s="122" t="s">
         <v>40</v>
       </c>
-      <c r="I4" s="595" t="s">
+      <c r="I4" s="599" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="596"/>
+      <c r="J4" s="600"/>
     </row>
     <row r="5" spans="1:10" ht="27.95" customHeight="1">
       <c r="A5" s="334" t="s">
@@ -18861,12 +18858,12 @@
         <v>37</v>
       </c>
       <c r="D5" s="125"/>
-      <c r="E5" s="562"/>
-      <c r="F5" s="563"/>
-      <c r="G5" s="563"/>
-      <c r="H5" s="563"/>
-      <c r="I5" s="563"/>
-      <c r="J5" s="564"/>
+      <c r="E5" s="566"/>
+      <c r="F5" s="567"/>
+      <c r="G5" s="567"/>
+      <c r="H5" s="567"/>
+      <c r="I5" s="567"/>
+      <c r="J5" s="568"/>
     </row>
     <row r="6" spans="1:10" ht="27.95" customHeight="1">
       <c r="A6" s="335"/>
@@ -18889,8 +18886,8 @@
         <f>IFERROR(E6*F6*G6,"")</f>
         <v/>
       </c>
-      <c r="I6" s="483"/>
-      <c r="J6" s="484"/>
+      <c r="I6" s="487"/>
+      <c r="J6" s="488"/>
     </row>
     <row r="7" spans="1:10" ht="27.95" customHeight="1">
       <c r="A7" s="336"/>
@@ -18913,8 +18910,8 @@
         <f>IFERROR(E7*F7*G7,"")</f>
         <v/>
       </c>
-      <c r="I7" s="483"/>
-      <c r="J7" s="484"/>
+      <c r="I7" s="487"/>
+      <c r="J7" s="488"/>
     </row>
     <row r="8" spans="1:10" ht="27.95" customHeight="1">
       <c r="A8" s="336"/>
@@ -18937,8 +18934,8 @@
         <f>IFERROR(E8*F8*G8,"")</f>
         <v/>
       </c>
-      <c r="I8" s="483"/>
-      <c r="J8" s="484"/>
+      <c r="I8" s="487"/>
+      <c r="J8" s="488"/>
     </row>
     <row r="9" spans="1:10" ht="27.95" customHeight="1">
       <c r="A9" s="336"/>
@@ -18961,22 +18958,22 @@
         <f>IFERROR(E9*F9*G9,"")</f>
         <v/>
       </c>
-      <c r="I9" s="483"/>
-      <c r="J9" s="484"/>
+      <c r="I9" s="487"/>
+      <c r="J9" s="488"/>
     </row>
     <row r="10" spans="1:10" ht="27.95" customHeight="1">
-      <c r="A10" s="584" t="s">
+      <c r="A10" s="588" t="s">
         <v>60</v>
       </c>
-      <c r="B10" s="585"/>
-      <c r="C10" s="586"/>
+      <c r="B10" s="589"/>
+      <c r="C10" s="590"/>
       <c r="D10" s="128"/>
-      <c r="E10" s="551"/>
-      <c r="F10" s="552"/>
+      <c r="E10" s="555"/>
+      <c r="F10" s="556"/>
       <c r="G10" s="56"/>
       <c r="H10" s="54"/>
-      <c r="I10" s="483"/>
-      <c r="J10" s="484"/>
+      <c r="I10" s="487"/>
+      <c r="J10" s="488"/>
     </row>
     <row r="11" spans="1:10" ht="27.95" customHeight="1">
       <c r="A11" s="334" t="s">
@@ -18987,16 +18984,16 @@
         <v>0</v>
       </c>
       <c r="D11" s="125"/>
-      <c r="E11" s="478" t="s">
+      <c r="E11" s="482" t="s">
         <v>52</v>
       </c>
-      <c r="F11" s="479"/>
+      <c r="F11" s="483"/>
       <c r="G11" s="72">
         <v>0</v>
       </c>
       <c r="H11" s="50"/>
-      <c r="I11" s="487"/>
-      <c r="J11" s="488"/>
+      <c r="I11" s="491"/>
+      <c r="J11" s="492"/>
     </row>
     <row r="12" spans="1:10" ht="27.95" customHeight="1">
       <c r="A12" s="334" t="s">
@@ -19007,16 +19004,16 @@
         <v>14</v>
       </c>
       <c r="D12" s="125"/>
-      <c r="E12" s="478" t="s">
+      <c r="E12" s="482" t="s">
         <v>52</v>
       </c>
-      <c r="F12" s="479"/>
+      <c r="F12" s="483"/>
       <c r="G12" s="72">
         <v>0</v>
       </c>
       <c r="H12" s="50"/>
-      <c r="I12" s="473"/>
-      <c r="J12" s="474"/>
+      <c r="I12" s="477"/>
+      <c r="J12" s="478"/>
     </row>
     <row r="13" spans="1:10" ht="27.95" customHeight="1">
       <c r="A13" s="334" t="s">
@@ -19027,16 +19024,16 @@
         <v>1</v>
       </c>
       <c r="D13" s="125"/>
-      <c r="E13" s="478" t="s">
+      <c r="E13" s="482" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="479"/>
+      <c r="F13" s="483"/>
       <c r="G13" s="49">
         <v>0</v>
       </c>
       <c r="H13" s="50"/>
-      <c r="I13" s="473"/>
-      <c r="J13" s="474"/>
+      <c r="I13" s="477"/>
+      <c r="J13" s="478"/>
     </row>
     <row r="14" spans="1:10" ht="27.95" customHeight="1">
       <c r="A14" s="337" t="s">
@@ -19047,14 +19044,14 @@
         <v>7</v>
       </c>
       <c r="D14" s="125"/>
-      <c r="E14" s="478" t="s">
+      <c r="E14" s="482" t="s">
         <v>65</v>
       </c>
-      <c r="F14" s="479"/>
+      <c r="F14" s="483"/>
       <c r="G14" s="49"/>
       <c r="H14" s="50"/>
-      <c r="I14" s="480"/>
-      <c r="J14" s="481"/>
+      <c r="I14" s="484"/>
+      <c r="J14" s="485"/>
     </row>
     <row r="15" spans="1:10" ht="27.95" customHeight="1">
       <c r="A15" s="337" t="s">
@@ -19065,12 +19062,12 @@
         <v>81</v>
       </c>
       <c r="D15" s="125"/>
-      <c r="E15" s="478"/>
-      <c r="F15" s="479"/>
-      <c r="G15" s="482"/>
+      <c r="E15" s="482"/>
+      <c r="F15" s="483"/>
+      <c r="G15" s="486"/>
       <c r="H15" s="51"/>
-      <c r="I15" s="480"/>
-      <c r="J15" s="481"/>
+      <c r="I15" s="484"/>
+      <c r="J15" s="485"/>
     </row>
     <row r="16" spans="1:10" ht="7.5" customHeight="1">
       <c r="A16" s="338"/>
@@ -19097,8 +19094,8 @@
       <c r="F17" s="136"/>
       <c r="G17" s="137"/>
       <c r="H17" s="138"/>
-      <c r="I17" s="590"/>
-      <c r="J17" s="591"/>
+      <c r="I17" s="594"/>
+      <c r="J17" s="595"/>
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" thickBot="1">
       <c r="A18" s="37"/>
@@ -19112,18 +19109,18 @@
       <c r="I18" s="37"/>
     </row>
     <row r="19" spans="1:10" ht="24" customHeight="1">
-      <c r="A19" s="587" t="s">
+      <c r="A19" s="591" t="s">
         <v>125</v>
       </c>
-      <c r="B19" s="588"/>
-      <c r="C19" s="588"/>
-      <c r="D19" s="588"/>
-      <c r="E19" s="588"/>
-      <c r="F19" s="588"/>
-      <c r="G19" s="588"/>
-      <c r="H19" s="588"/>
-      <c r="I19" s="588"/>
-      <c r="J19" s="589"/>
+      <c r="B19" s="592"/>
+      <c r="C19" s="592"/>
+      <c r="D19" s="592"/>
+      <c r="E19" s="592"/>
+      <c r="F19" s="592"/>
+      <c r="G19" s="592"/>
+      <c r="H19" s="592"/>
+      <c r="I19" s="592"/>
+      <c r="J19" s="593"/>
     </row>
     <row r="20" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A20" s="103"/>
@@ -19223,16 +19220,16 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="110"/>
-      <c r="B27" s="579" t="s">
+      <c r="B27" s="583" t="s">
         <v>192</v>
       </c>
-      <c r="C27" s="580"/>
-      <c r="D27" s="580"/>
-      <c r="E27" s="572"/>
-      <c r="F27" s="571" t="s">
+      <c r="C27" s="584"/>
+      <c r="D27" s="584"/>
+      <c r="E27" s="576"/>
+      <c r="F27" s="575" t="s">
         <v>138</v>
       </c>
-      <c r="G27" s="572"/>
+      <c r="G27" s="576"/>
       <c r="H27" s="197" t="s">
         <v>143</v>
       </c>
@@ -19243,16 +19240,16 @@
     </row>
     <row r="28" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A28" s="112"/>
-      <c r="B28" s="581" t="s">
+      <c r="B28" s="585" t="s">
         <v>135</v>
       </c>
-      <c r="C28" s="582"/>
-      <c r="D28" s="582"/>
-      <c r="E28" s="583"/>
-      <c r="F28" s="573" t="s">
+      <c r="C28" s="586"/>
+      <c r="D28" s="586"/>
+      <c r="E28" s="587"/>
+      <c r="F28" s="577" t="s">
         <v>139</v>
       </c>
-      <c r="G28" s="574"/>
+      <c r="G28" s="578"/>
       <c r="H28" s="140" t="s">
         <v>144</v>
       </c>
@@ -19263,16 +19260,16 @@
     </row>
     <row r="29" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A29" s="112"/>
-      <c r="B29" s="565" t="s">
+      <c r="B29" s="569" t="s">
         <v>136</v>
       </c>
-      <c r="C29" s="566"/>
-      <c r="D29" s="566"/>
-      <c r="E29" s="567"/>
-      <c r="F29" s="575" t="s">
+      <c r="C29" s="570"/>
+      <c r="D29" s="570"/>
+      <c r="E29" s="571"/>
+      <c r="F29" s="579" t="s">
         <v>140</v>
       </c>
-      <c r="G29" s="576"/>
+      <c r="G29" s="580"/>
       <c r="H29" s="141" t="s">
         <v>144</v>
       </c>
@@ -19283,16 +19280,16 @@
     </row>
     <row r="30" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A30" s="112"/>
-      <c r="B30" s="565" t="s">
+      <c r="B30" s="569" t="s">
         <v>137</v>
       </c>
-      <c r="C30" s="566"/>
-      <c r="D30" s="566"/>
-      <c r="E30" s="567"/>
-      <c r="F30" s="575" t="s">
+      <c r="C30" s="570"/>
+      <c r="D30" s="570"/>
+      <c r="E30" s="571"/>
+      <c r="F30" s="579" t="s">
         <v>141</v>
       </c>
-      <c r="G30" s="576"/>
+      <c r="G30" s="580"/>
       <c r="H30" s="141" t="s">
         <v>144</v>
       </c>
@@ -19303,16 +19300,16 @@
     </row>
     <row r="31" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A31" s="112"/>
-      <c r="B31" s="565" t="s">
+      <c r="B31" s="569" t="s">
         <v>145</v>
       </c>
-      <c r="C31" s="566"/>
-      <c r="D31" s="566"/>
-      <c r="E31" s="567"/>
-      <c r="F31" s="575" t="s">
+      <c r="C31" s="570"/>
+      <c r="D31" s="570"/>
+      <c r="E31" s="571"/>
+      <c r="F31" s="579" t="s">
         <v>142</v>
       </c>
-      <c r="G31" s="576"/>
+      <c r="G31" s="580"/>
       <c r="H31" s="141" t="s">
         <v>144</v>
       </c>
@@ -19323,16 +19320,16 @@
     </row>
     <row r="32" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A32" s="112"/>
-      <c r="B32" s="568" t="s">
+      <c r="B32" s="572" t="s">
         <v>263</v>
       </c>
-      <c r="C32" s="569"/>
-      <c r="D32" s="569"/>
-      <c r="E32" s="570"/>
-      <c r="F32" s="577" t="s">
+      <c r="C32" s="573"/>
+      <c r="D32" s="573"/>
+      <c r="E32" s="574"/>
+      <c r="F32" s="581" t="s">
         <v>142</v>
       </c>
-      <c r="G32" s="578"/>
+      <c r="G32" s="582"/>
       <c r="H32" s="198" t="s">
         <v>144</v>
       </c>
@@ -19446,33 +19443,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="35.1" customHeight="1">
-      <c r="A1" s="604" t="s">
+      <c r="A1" s="608" t="s">
         <v>177</v>
       </c>
-      <c r="B1" s="605"/>
-      <c r="C1" s="605"/>
-      <c r="D1" s="605"/>
-      <c r="E1" s="605"/>
-      <c r="F1" s="605"/>
-      <c r="G1" s="605"/>
-      <c r="H1" s="605"/>
-      <c r="I1" s="605"/>
-      <c r="J1" s="605"/>
-      <c r="K1" s="605"/>
-      <c r="L1" s="605"/>
-      <c r="M1" s="605"/>
-      <c r="N1" s="605"/>
-      <c r="O1" s="605"/>
-      <c r="P1" s="605"/>
-      <c r="Q1" s="605"/>
-      <c r="R1" s="605"/>
-      <c r="S1" s="605"/>
-      <c r="T1" s="605"/>
-      <c r="U1" s="605"/>
-      <c r="V1" s="605"/>
-      <c r="W1" s="605"/>
-      <c r="X1" s="605"/>
-      <c r="Y1" s="606"/>
+      <c r="B1" s="609"/>
+      <c r="C1" s="609"/>
+      <c r="D1" s="609"/>
+      <c r="E1" s="609"/>
+      <c r="F1" s="609"/>
+      <c r="G1" s="609"/>
+      <c r="H1" s="609"/>
+      <c r="I1" s="609"/>
+      <c r="J1" s="609"/>
+      <c r="K1" s="609"/>
+      <c r="L1" s="609"/>
+      <c r="M1" s="609"/>
+      <c r="N1" s="609"/>
+      <c r="O1" s="609"/>
+      <c r="P1" s="609"/>
+      <c r="Q1" s="609"/>
+      <c r="R1" s="609"/>
+      <c r="S1" s="609"/>
+      <c r="T1" s="609"/>
+      <c r="U1" s="609"/>
+      <c r="V1" s="609"/>
+      <c r="W1" s="609"/>
+      <c r="X1" s="609"/>
+      <c r="Y1" s="610"/>
     </row>
     <row r="2" spans="1:26" s="152" customFormat="1" ht="21" customHeight="1">
       <c r="A2" s="175"/>
@@ -19498,54 +19495,54 @@
     </row>
     <row r="4" spans="1:26" s="152" customFormat="1" ht="21" customHeight="1">
       <c r="A4" s="177"/>
-      <c r="B4" s="631" t="s">
+      <c r="B4" s="635" t="s">
         <v>149</v>
       </c>
-      <c r="C4" s="632"/>
-      <c r="D4" s="632"/>
-      <c r="E4" s="632"/>
-      <c r="F4" s="632"/>
-      <c r="G4" s="632"/>
-      <c r="H4" s="632"/>
-      <c r="I4" s="632"/>
-      <c r="J4" s="632"/>
-      <c r="K4" s="633"/>
-      <c r="O4" s="631" t="s">
+      <c r="C4" s="636"/>
+      <c r="D4" s="636"/>
+      <c r="E4" s="636"/>
+      <c r="F4" s="636"/>
+      <c r="G4" s="636"/>
+      <c r="H4" s="636"/>
+      <c r="I4" s="636"/>
+      <c r="J4" s="636"/>
+      <c r="K4" s="637"/>
+      <c r="O4" s="635" t="s">
         <v>163</v>
       </c>
-      <c r="P4" s="632"/>
-      <c r="Q4" s="632"/>
-      <c r="R4" s="632"/>
-      <c r="S4" s="632"/>
-      <c r="T4" s="632"/>
-      <c r="U4" s="632"/>
-      <c r="V4" s="632"/>
-      <c r="W4" s="632"/>
-      <c r="X4" s="633"/>
+      <c r="P4" s="636"/>
+      <c r="Q4" s="636"/>
+      <c r="R4" s="636"/>
+      <c r="S4" s="636"/>
+      <c r="T4" s="636"/>
+      <c r="U4" s="636"/>
+      <c r="V4" s="636"/>
+      <c r="W4" s="636"/>
+      <c r="X4" s="637"/>
       <c r="Y4" s="176"/>
     </row>
     <row r="5" spans="1:26" s="152" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A5" s="175"/>
-      <c r="B5" s="634"/>
-      <c r="C5" s="635"/>
-      <c r="D5" s="635"/>
-      <c r="E5" s="635"/>
-      <c r="F5" s="635"/>
-      <c r="G5" s="635"/>
-      <c r="H5" s="635"/>
-      <c r="I5" s="635"/>
-      <c r="J5" s="635"/>
-      <c r="K5" s="636"/>
-      <c r="O5" s="634"/>
-      <c r="P5" s="635"/>
-      <c r="Q5" s="635"/>
-      <c r="R5" s="635"/>
-      <c r="S5" s="635"/>
-      <c r="T5" s="635"/>
-      <c r="U5" s="635"/>
-      <c r="V5" s="635"/>
-      <c r="W5" s="635"/>
-      <c r="X5" s="636"/>
+      <c r="B5" s="638"/>
+      <c r="C5" s="639"/>
+      <c r="D5" s="639"/>
+      <c r="E5" s="639"/>
+      <c r="F5" s="639"/>
+      <c r="G5" s="639"/>
+      <c r="H5" s="639"/>
+      <c r="I5" s="639"/>
+      <c r="J5" s="639"/>
+      <c r="K5" s="640"/>
+      <c r="O5" s="638"/>
+      <c r="P5" s="639"/>
+      <c r="Q5" s="639"/>
+      <c r="R5" s="639"/>
+      <c r="S5" s="639"/>
+      <c r="T5" s="639"/>
+      <c r="U5" s="639"/>
+      <c r="V5" s="639"/>
+      <c r="W5" s="639"/>
+      <c r="X5" s="640"/>
       <c r="Y5" s="176"/>
     </row>
     <row r="6" spans="1:26" s="152" customFormat="1" ht="21" customHeight="1" thickBot="1">
@@ -19567,21 +19564,21 @@
       <c r="D7" s="148"/>
       <c r="E7" s="148"/>
       <c r="F7" s="149"/>
-      <c r="G7" s="640" t="s">
+      <c r="G7" s="644" t="s">
         <v>150</v>
       </c>
-      <c r="H7" s="641"/>
-      <c r="I7" s="641"/>
-      <c r="J7" s="641"/>
-      <c r="K7" s="641"/>
-      <c r="L7" s="641"/>
-      <c r="M7" s="641"/>
-      <c r="N7" s="641"/>
-      <c r="O7" s="641"/>
-      <c r="P7" s="641"/>
-      <c r="Q7" s="641"/>
-      <c r="R7" s="641"/>
-      <c r="S7" s="642"/>
+      <c r="H7" s="645"/>
+      <c r="I7" s="645"/>
+      <c r="J7" s="645"/>
+      <c r="K7" s="645"/>
+      <c r="L7" s="645"/>
+      <c r="M7" s="645"/>
+      <c r="N7" s="645"/>
+      <c r="O7" s="645"/>
+      <c r="P7" s="645"/>
+      <c r="Q7" s="645"/>
+      <c r="R7" s="645"/>
+      <c r="S7" s="646"/>
       <c r="T7" s="193"/>
       <c r="U7" s="153"/>
       <c r="V7" s="153"/>
@@ -19597,19 +19594,19 @@
       <c r="D8" s="148"/>
       <c r="E8" s="148"/>
       <c r="F8" s="149"/>
-      <c r="G8" s="643"/>
-      <c r="H8" s="644"/>
-      <c r="I8" s="644"/>
-      <c r="J8" s="644"/>
-      <c r="K8" s="644"/>
-      <c r="L8" s="644"/>
-      <c r="M8" s="644"/>
-      <c r="N8" s="644"/>
-      <c r="O8" s="644"/>
-      <c r="P8" s="644"/>
-      <c r="Q8" s="644"/>
-      <c r="R8" s="644"/>
-      <c r="S8" s="645"/>
+      <c r="G8" s="647"/>
+      <c r="H8" s="648"/>
+      <c r="I8" s="648"/>
+      <c r="J8" s="648"/>
+      <c r="K8" s="648"/>
+      <c r="L8" s="648"/>
+      <c r="M8" s="648"/>
+      <c r="N8" s="648"/>
+      <c r="O8" s="648"/>
+      <c r="P8" s="648"/>
+      <c r="Q8" s="648"/>
+      <c r="R8" s="648"/>
+      <c r="S8" s="649"/>
       <c r="T8" s="193"/>
       <c r="U8" s="153"/>
       <c r="V8" s="153"/>
@@ -19625,19 +19622,19 @@
       <c r="D9" s="148"/>
       <c r="E9" s="148"/>
       <c r="F9" s="149"/>
-      <c r="G9" s="646"/>
-      <c r="H9" s="647"/>
-      <c r="I9" s="647"/>
-      <c r="J9" s="647"/>
-      <c r="K9" s="647"/>
-      <c r="L9" s="647"/>
-      <c r="M9" s="647"/>
-      <c r="N9" s="647"/>
-      <c r="O9" s="647"/>
-      <c r="P9" s="647"/>
-      <c r="Q9" s="647"/>
-      <c r="R9" s="647"/>
-      <c r="S9" s="648"/>
+      <c r="G9" s="650"/>
+      <c r="H9" s="651"/>
+      <c r="I9" s="651"/>
+      <c r="J9" s="651"/>
+      <c r="K9" s="651"/>
+      <c r="L9" s="651"/>
+      <c r="M9" s="651"/>
+      <c r="N9" s="651"/>
+      <c r="O9" s="651"/>
+      <c r="P9" s="651"/>
+      <c r="Q9" s="651"/>
+      <c r="R9" s="651"/>
+      <c r="S9" s="652"/>
       <c r="T9" s="193"/>
       <c r="U9" s="153"/>
       <c r="V9" s="153"/>
@@ -19688,59 +19685,59 @@
     </row>
     <row r="12" spans="1:26" s="152" customFormat="1" ht="21" customHeight="1">
       <c r="A12" s="178"/>
-      <c r="B12" s="627" t="s">
+      <c r="B12" s="631" t="s">
         <v>151</v>
       </c>
-      <c r="C12" s="610"/>
-      <c r="D12" s="610"/>
-      <c r="E12" s="610"/>
-      <c r="F12" s="610"/>
-      <c r="G12" s="610"/>
-      <c r="H12" s="610"/>
-      <c r="I12" s="610"/>
-      <c r="J12" s="610"/>
-      <c r="K12" s="611"/>
-      <c r="O12" s="627" t="s">
+      <c r="C12" s="614"/>
+      <c r="D12" s="614"/>
+      <c r="E12" s="614"/>
+      <c r="F12" s="614"/>
+      <c r="G12" s="614"/>
+      <c r="H12" s="614"/>
+      <c r="I12" s="614"/>
+      <c r="J12" s="614"/>
+      <c r="K12" s="615"/>
+      <c r="O12" s="631" t="s">
         <v>162</v>
       </c>
-      <c r="P12" s="610"/>
-      <c r="Q12" s="610"/>
-      <c r="R12" s="610"/>
-      <c r="S12" s="610"/>
-      <c r="T12" s="610"/>
-      <c r="U12" s="610"/>
-      <c r="V12" s="610"/>
-      <c r="W12" s="610"/>
-      <c r="X12" s="611"/>
+      <c r="P12" s="614"/>
+      <c r="Q12" s="614"/>
+      <c r="R12" s="614"/>
+      <c r="S12" s="614"/>
+      <c r="T12" s="614"/>
+      <c r="U12" s="614"/>
+      <c r="V12" s="614"/>
+      <c r="W12" s="614"/>
+      <c r="X12" s="615"/>
       <c r="Y12" s="179"/>
       <c r="Z12" s="153"/>
     </row>
     <row r="13" spans="1:26" s="152" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A13" s="178"/>
-      <c r="B13" s="598" t="s">
+      <c r="B13" s="602" t="s">
         <v>161</v>
       </c>
-      <c r="C13" s="599"/>
-      <c r="D13" s="599"/>
-      <c r="E13" s="599"/>
-      <c r="F13" s="599"/>
-      <c r="G13" s="599"/>
-      <c r="H13" s="599"/>
-      <c r="I13" s="599"/>
-      <c r="J13" s="599"/>
-      <c r="K13" s="600"/>
-      <c r="O13" s="598" t="s">
+      <c r="C13" s="603"/>
+      <c r="D13" s="603"/>
+      <c r="E13" s="603"/>
+      <c r="F13" s="603"/>
+      <c r="G13" s="603"/>
+      <c r="H13" s="603"/>
+      <c r="I13" s="603"/>
+      <c r="J13" s="603"/>
+      <c r="K13" s="604"/>
+      <c r="O13" s="602" t="s">
         <v>161</v>
       </c>
-      <c r="P13" s="599"/>
-      <c r="Q13" s="599"/>
-      <c r="R13" s="599"/>
-      <c r="S13" s="599"/>
-      <c r="T13" s="599"/>
-      <c r="U13" s="599"/>
-      <c r="V13" s="599"/>
-      <c r="W13" s="599"/>
-      <c r="X13" s="600"/>
+      <c r="P13" s="603"/>
+      <c r="Q13" s="603"/>
+      <c r="R13" s="603"/>
+      <c r="S13" s="603"/>
+      <c r="T13" s="603"/>
+      <c r="U13" s="603"/>
+      <c r="V13" s="603"/>
+      <c r="W13" s="603"/>
+      <c r="X13" s="604"/>
       <c r="Y13" s="179"/>
       <c r="Z13" s="153"/>
     </row>
@@ -19788,92 +19785,92 @@
     </row>
     <row r="16" spans="1:26" s="152" customFormat="1" ht="21" customHeight="1">
       <c r="A16" s="180"/>
-      <c r="B16" s="615" t="s">
+      <c r="B16" s="619" t="s">
         <v>152</v>
       </c>
-      <c r="C16" s="616"/>
-      <c r="D16" s="616"/>
-      <c r="E16" s="617"/>
+      <c r="C16" s="620"/>
+      <c r="D16" s="620"/>
+      <c r="E16" s="621"/>
       <c r="F16" s="101"/>
       <c r="G16" s="145"/>
-      <c r="H16" s="615" t="s">
+      <c r="H16" s="619" t="s">
         <v>154</v>
       </c>
-      <c r="I16" s="616"/>
-      <c r="J16" s="616"/>
-      <c r="K16" s="617"/>
-      <c r="O16" s="615" t="s">
+      <c r="I16" s="620"/>
+      <c r="J16" s="620"/>
+      <c r="K16" s="621"/>
+      <c r="O16" s="619" t="s">
         <v>164</v>
       </c>
-      <c r="P16" s="616"/>
-      <c r="Q16" s="616"/>
-      <c r="R16" s="617"/>
+      <c r="P16" s="620"/>
+      <c r="Q16" s="620"/>
+      <c r="R16" s="621"/>
       <c r="S16" s="153"/>
       <c r="T16" s="153"/>
-      <c r="U16" s="615" t="s">
+      <c r="U16" s="619" t="s">
         <v>167</v>
       </c>
-      <c r="V16" s="616"/>
-      <c r="W16" s="616"/>
-      <c r="X16" s="617"/>
+      <c r="V16" s="620"/>
+      <c r="W16" s="620"/>
+      <c r="X16" s="621"/>
       <c r="Y16" s="179"/>
       <c r="Z16" s="153"/>
     </row>
     <row r="17" spans="1:26" s="152" customFormat="1" ht="21" customHeight="1">
       <c r="A17" s="180"/>
-      <c r="B17" s="618" t="s">
+      <c r="B17" s="622" t="s">
         <v>153</v>
       </c>
-      <c r="C17" s="619"/>
-      <c r="D17" s="619"/>
-      <c r="E17" s="620"/>
+      <c r="C17" s="623"/>
+      <c r="D17" s="623"/>
+      <c r="E17" s="624"/>
       <c r="F17" s="38"/>
       <c r="G17" s="38"/>
-      <c r="H17" s="618" t="s">
+      <c r="H17" s="622" t="s">
         <v>155</v>
       </c>
-      <c r="I17" s="619"/>
-      <c r="J17" s="619"/>
-      <c r="K17" s="620"/>
-      <c r="O17" s="618" t="s">
+      <c r="I17" s="623"/>
+      <c r="J17" s="623"/>
+      <c r="K17" s="624"/>
+      <c r="O17" s="622" t="s">
         <v>165</v>
       </c>
-      <c r="P17" s="619"/>
-      <c r="Q17" s="619"/>
-      <c r="R17" s="620"/>
+      <c r="P17" s="623"/>
+      <c r="Q17" s="623"/>
+      <c r="R17" s="624"/>
       <c r="S17" s="153"/>
       <c r="T17" s="153"/>
-      <c r="U17" s="618" t="s">
+      <c r="U17" s="622" t="s">
         <v>168</v>
       </c>
-      <c r="V17" s="622"/>
-      <c r="W17" s="622"/>
-      <c r="X17" s="623"/>
+      <c r="V17" s="626"/>
+      <c r="W17" s="626"/>
+      <c r="X17" s="627"/>
       <c r="Y17" s="179"/>
       <c r="Z17" s="153"/>
     </row>
     <row r="18" spans="1:26" s="152" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A18" s="178"/>
-      <c r="B18" s="637"/>
-      <c r="C18" s="638"/>
-      <c r="D18" s="638"/>
-      <c r="E18" s="639"/>
+      <c r="B18" s="641"/>
+      <c r="C18" s="642"/>
+      <c r="D18" s="642"/>
+      <c r="E18" s="643"/>
       <c r="F18" s="147"/>
       <c r="G18" s="146"/>
-      <c r="H18" s="637"/>
-      <c r="I18" s="638"/>
-      <c r="J18" s="638"/>
-      <c r="K18" s="639"/>
-      <c r="O18" s="621"/>
-      <c r="P18" s="619"/>
-      <c r="Q18" s="619"/>
-      <c r="R18" s="620"/>
+      <c r="H18" s="641"/>
+      <c r="I18" s="642"/>
+      <c r="J18" s="642"/>
+      <c r="K18" s="643"/>
+      <c r="O18" s="625"/>
+      <c r="P18" s="623"/>
+      <c r="Q18" s="623"/>
+      <c r="R18" s="624"/>
       <c r="S18" s="153"/>
       <c r="T18" s="153"/>
-      <c r="U18" s="618"/>
-      <c r="V18" s="622"/>
-      <c r="W18" s="622"/>
-      <c r="X18" s="623"/>
+      <c r="U18" s="622"/>
+      <c r="V18" s="626"/>
+      <c r="W18" s="626"/>
+      <c r="X18" s="627"/>
       <c r="Y18" s="179"/>
       <c r="Z18" s="153"/>
     </row>
@@ -19887,57 +19884,57 @@
       <c r="G19" s="144"/>
       <c r="H19" s="144"/>
       <c r="J19" s="169"/>
-      <c r="O19" s="618" t="s">
+      <c r="O19" s="622" t="s">
         <v>166</v>
       </c>
-      <c r="P19" s="622"/>
-      <c r="Q19" s="622"/>
-      <c r="R19" s="623"/>
+      <c r="P19" s="626"/>
+      <c r="Q19" s="626"/>
+      <c r="R19" s="627"/>
       <c r="S19" s="153"/>
       <c r="T19" s="153"/>
-      <c r="U19" s="618"/>
-      <c r="V19" s="622"/>
-      <c r="W19" s="622"/>
-      <c r="X19" s="623"/>
+      <c r="U19" s="622"/>
+      <c r="V19" s="626"/>
+      <c r="W19" s="626"/>
+      <c r="X19" s="627"/>
       <c r="Y19" s="179"/>
       <c r="Z19" s="153"/>
     </row>
     <row r="20" spans="1:26" s="152" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A20" s="110"/>
-      <c r="B20" s="627" t="s">
+      <c r="B20" s="631" t="s">
         <v>156</v>
       </c>
-      <c r="C20" s="610"/>
-      <c r="D20" s="610"/>
-      <c r="E20" s="610"/>
-      <c r="F20" s="610"/>
-      <c r="G20" s="610"/>
-      <c r="H20" s="610"/>
-      <c r="I20" s="610"/>
-      <c r="J20" s="610"/>
-      <c r="K20" s="611"/>
-      <c r="O20" s="624"/>
-      <c r="P20" s="625"/>
-      <c r="Q20" s="625"/>
-      <c r="R20" s="626"/>
-      <c r="U20" s="624"/>
-      <c r="V20" s="625"/>
-      <c r="W20" s="625"/>
-      <c r="X20" s="626"/>
+      <c r="C20" s="614"/>
+      <c r="D20" s="614"/>
+      <c r="E20" s="614"/>
+      <c r="F20" s="614"/>
+      <c r="G20" s="614"/>
+      <c r="H20" s="614"/>
+      <c r="I20" s="614"/>
+      <c r="J20" s="614"/>
+      <c r="K20" s="615"/>
+      <c r="O20" s="628"/>
+      <c r="P20" s="629"/>
+      <c r="Q20" s="629"/>
+      <c r="R20" s="630"/>
+      <c r="U20" s="628"/>
+      <c r="V20" s="629"/>
+      <c r="W20" s="629"/>
+      <c r="X20" s="630"/>
       <c r="Y20" s="176"/>
     </row>
     <row r="21" spans="1:26" s="152" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A21" s="103"/>
-      <c r="B21" s="628"/>
-      <c r="C21" s="629"/>
-      <c r="D21" s="629"/>
-      <c r="E21" s="629"/>
-      <c r="F21" s="629"/>
-      <c r="G21" s="629"/>
-      <c r="H21" s="629"/>
-      <c r="I21" s="629"/>
-      <c r="J21" s="629"/>
-      <c r="K21" s="630"/>
+      <c r="B21" s="632"/>
+      <c r="C21" s="633"/>
+      <c r="D21" s="633"/>
+      <c r="E21" s="633"/>
+      <c r="F21" s="633"/>
+      <c r="G21" s="633"/>
+      <c r="H21" s="633"/>
+      <c r="I21" s="633"/>
+      <c r="J21" s="633"/>
+      <c r="K21" s="634"/>
       <c r="Q21" s="171"/>
       <c r="W21" s="171"/>
       <c r="Y21" s="176"/>
@@ -19972,82 +19969,82 @@
     </row>
     <row r="24" spans="1:26" s="152" customFormat="1" ht="21" customHeight="1">
       <c r="A24" s="181"/>
-      <c r="B24" s="601" t="s">
+      <c r="B24" s="605" t="s">
         <v>157</v>
       </c>
-      <c r="C24" s="610"/>
-      <c r="D24" s="610"/>
-      <c r="E24" s="610"/>
-      <c r="F24" s="610"/>
-      <c r="G24" s="610"/>
-      <c r="H24" s="610"/>
-      <c r="I24" s="610"/>
-      <c r="J24" s="610"/>
-      <c r="K24" s="611"/>
-      <c r="O24" s="601" t="s">
+      <c r="C24" s="614"/>
+      <c r="D24" s="614"/>
+      <c r="E24" s="614"/>
+      <c r="F24" s="614"/>
+      <c r="G24" s="614"/>
+      <c r="H24" s="614"/>
+      <c r="I24" s="614"/>
+      <c r="J24" s="614"/>
+      <c r="K24" s="615"/>
+      <c r="O24" s="605" t="s">
         <v>169</v>
       </c>
-      <c r="P24" s="610"/>
-      <c r="Q24" s="610"/>
-      <c r="R24" s="610"/>
-      <c r="S24" s="610"/>
-      <c r="T24" s="610"/>
-      <c r="U24" s="610"/>
-      <c r="V24" s="610"/>
-      <c r="W24" s="610"/>
-      <c r="X24" s="611"/>
+      <c r="P24" s="614"/>
+      <c r="Q24" s="614"/>
+      <c r="R24" s="614"/>
+      <c r="S24" s="614"/>
+      <c r="T24" s="614"/>
+      <c r="U24" s="614"/>
+      <c r="V24" s="614"/>
+      <c r="W24" s="614"/>
+      <c r="X24" s="615"/>
       <c r="Y24" s="176"/>
     </row>
     <row r="25" spans="1:26" s="152" customFormat="1" ht="21" customHeight="1">
       <c r="A25" s="182"/>
-      <c r="B25" s="612"/>
-      <c r="C25" s="613"/>
-      <c r="D25" s="613"/>
-      <c r="E25" s="613"/>
-      <c r="F25" s="613"/>
-      <c r="G25" s="613"/>
-      <c r="H25" s="613"/>
-      <c r="I25" s="613"/>
-      <c r="J25" s="613"/>
-      <c r="K25" s="614"/>
-      <c r="O25" s="612"/>
-      <c r="P25" s="613"/>
-      <c r="Q25" s="613"/>
-      <c r="R25" s="613"/>
-      <c r="S25" s="613"/>
-      <c r="T25" s="613"/>
-      <c r="U25" s="613"/>
-      <c r="V25" s="613"/>
-      <c r="W25" s="613"/>
-      <c r="X25" s="614"/>
+      <c r="B25" s="616"/>
+      <c r="C25" s="617"/>
+      <c r="D25" s="617"/>
+      <c r="E25" s="617"/>
+      <c r="F25" s="617"/>
+      <c r="G25" s="617"/>
+      <c r="H25" s="617"/>
+      <c r="I25" s="617"/>
+      <c r="J25" s="617"/>
+      <c r="K25" s="618"/>
+      <c r="O25" s="616"/>
+      <c r="P25" s="617"/>
+      <c r="Q25" s="617"/>
+      <c r="R25" s="617"/>
+      <c r="S25" s="617"/>
+      <c r="T25" s="617"/>
+      <c r="U25" s="617"/>
+      <c r="V25" s="617"/>
+      <c r="W25" s="617"/>
+      <c r="X25" s="618"/>
       <c r="Y25" s="176"/>
     </row>
     <row r="26" spans="1:26" s="152" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A26" s="103"/>
-      <c r="B26" s="598" t="s">
+      <c r="B26" s="602" t="s">
         <v>158</v>
       </c>
-      <c r="C26" s="599"/>
-      <c r="D26" s="599"/>
-      <c r="E26" s="599"/>
-      <c r="F26" s="599"/>
-      <c r="G26" s="599"/>
-      <c r="H26" s="599"/>
-      <c r="I26" s="599"/>
-      <c r="J26" s="599"/>
-      <c r="K26" s="600"/>
-      <c r="O26" s="598" t="s">
+      <c r="C26" s="603"/>
+      <c r="D26" s="603"/>
+      <c r="E26" s="603"/>
+      <c r="F26" s="603"/>
+      <c r="G26" s="603"/>
+      <c r="H26" s="603"/>
+      <c r="I26" s="603"/>
+      <c r="J26" s="603"/>
+      <c r="K26" s="604"/>
+      <c r="O26" s="602" t="s">
         <v>158</v>
       </c>
-      <c r="P26" s="599"/>
-      <c r="Q26" s="599"/>
-      <c r="R26" s="599"/>
-      <c r="S26" s="599"/>
-      <c r="T26" s="599"/>
-      <c r="U26" s="599"/>
-      <c r="V26" s="599"/>
-      <c r="W26" s="599"/>
-      <c r="X26" s="600"/>
+      <c r="P26" s="603"/>
+      <c r="Q26" s="603"/>
+      <c r="R26" s="603"/>
+      <c r="S26" s="603"/>
+      <c r="T26" s="603"/>
+      <c r="U26" s="603"/>
+      <c r="V26" s="603"/>
+      <c r="W26" s="603"/>
+      <c r="X26" s="604"/>
       <c r="Y26" s="176"/>
     </row>
     <row r="27" spans="1:26" s="152" customFormat="1" ht="12">
@@ -20078,72 +20075,72 @@
     </row>
     <row r="29" spans="1:26" s="152" customFormat="1" ht="12">
       <c r="A29" s="110"/>
-      <c r="B29" s="601" t="s">
+      <c r="B29" s="605" t="s">
         <v>159</v>
       </c>
-      <c r="C29" s="602"/>
-      <c r="D29" s="602"/>
-      <c r="E29" s="602"/>
-      <c r="F29" s="602"/>
-      <c r="G29" s="602"/>
-      <c r="H29" s="602"/>
-      <c r="I29" s="602"/>
-      <c r="J29" s="602"/>
-      <c r="K29" s="603"/>
-      <c r="O29" s="601" t="s">
+      <c r="C29" s="606"/>
+      <c r="D29" s="606"/>
+      <c r="E29" s="606"/>
+      <c r="F29" s="606"/>
+      <c r="G29" s="606"/>
+      <c r="H29" s="606"/>
+      <c r="I29" s="606"/>
+      <c r="J29" s="606"/>
+      <c r="K29" s="607"/>
+      <c r="O29" s="605" t="s">
         <v>171</v>
       </c>
-      <c r="P29" s="602"/>
-      <c r="Q29" s="602"/>
-      <c r="R29" s="602"/>
-      <c r="S29" s="602"/>
-      <c r="T29" s="602"/>
-      <c r="U29" s="602"/>
-      <c r="V29" s="602"/>
-      <c r="W29" s="602"/>
-      <c r="X29" s="603"/>
+      <c r="P29" s="606"/>
+      <c r="Q29" s="606"/>
+      <c r="R29" s="606"/>
+      <c r="S29" s="606"/>
+      <c r="T29" s="606"/>
+      <c r="U29" s="606"/>
+      <c r="V29" s="606"/>
+      <c r="W29" s="606"/>
+      <c r="X29" s="607"/>
       <c r="Y29" s="176"/>
     </row>
     <row r="30" spans="1:26" s="152" customFormat="1" ht="23.25" customHeight="1" thickBot="1">
       <c r="A30" s="110"/>
-      <c r="B30" s="607"/>
-      <c r="C30" s="608"/>
-      <c r="D30" s="608"/>
-      <c r="E30" s="608"/>
-      <c r="F30" s="608"/>
-      <c r="G30" s="608"/>
-      <c r="H30" s="608"/>
-      <c r="I30" s="608"/>
-      <c r="J30" s="608"/>
-      <c r="K30" s="609"/>
-      <c r="O30" s="598" t="s">
+      <c r="B30" s="611"/>
+      <c r="C30" s="612"/>
+      <c r="D30" s="612"/>
+      <c r="E30" s="612"/>
+      <c r="F30" s="612"/>
+      <c r="G30" s="612"/>
+      <c r="H30" s="612"/>
+      <c r="I30" s="612"/>
+      <c r="J30" s="612"/>
+      <c r="K30" s="613"/>
+      <c r="O30" s="602" t="s">
         <v>173</v>
       </c>
-      <c r="P30" s="599"/>
-      <c r="Q30" s="599"/>
-      <c r="R30" s="599"/>
-      <c r="S30" s="599"/>
-      <c r="T30" s="599"/>
-      <c r="U30" s="599"/>
-      <c r="V30" s="599"/>
-      <c r="W30" s="599"/>
-      <c r="X30" s="600"/>
+      <c r="P30" s="603"/>
+      <c r="Q30" s="603"/>
+      <c r="R30" s="603"/>
+      <c r="S30" s="603"/>
+      <c r="T30" s="603"/>
+      <c r="U30" s="603"/>
+      <c r="V30" s="603"/>
+      <c r="W30" s="603"/>
+      <c r="X30" s="604"/>
       <c r="Y30" s="176"/>
     </row>
     <row r="31" spans="1:26" s="152" customFormat="1" ht="12.75" thickBot="1">
       <c r="A31" s="110"/>
-      <c r="B31" s="598" t="s">
+      <c r="B31" s="602" t="s">
         <v>160</v>
       </c>
-      <c r="C31" s="599"/>
-      <c r="D31" s="599"/>
-      <c r="E31" s="599"/>
-      <c r="F31" s="599"/>
-      <c r="G31" s="599"/>
-      <c r="H31" s="599"/>
-      <c r="I31" s="599"/>
-      <c r="J31" s="599"/>
-      <c r="K31" s="600"/>
+      <c r="C31" s="603"/>
+      <c r="D31" s="603"/>
+      <c r="E31" s="603"/>
+      <c r="F31" s="603"/>
+      <c r="G31" s="603"/>
+      <c r="H31" s="603"/>
+      <c r="I31" s="603"/>
+      <c r="J31" s="603"/>
+      <c r="K31" s="604"/>
       <c r="O31" s="38"/>
       <c r="P31" s="38"/>
       <c r="Q31" s="38"/>
@@ -20181,18 +20178,18 @@
       <c r="G33" s="101"/>
       <c r="H33" s="101"/>
       <c r="I33" s="101"/>
-      <c r="O33" s="601" t="s">
+      <c r="O33" s="605" t="s">
         <v>172</v>
       </c>
-      <c r="P33" s="602"/>
-      <c r="Q33" s="602"/>
-      <c r="R33" s="602"/>
-      <c r="S33" s="602"/>
-      <c r="T33" s="602"/>
-      <c r="U33" s="602"/>
-      <c r="V33" s="602"/>
-      <c r="W33" s="602"/>
-      <c r="X33" s="603"/>
+      <c r="P33" s="606"/>
+      <c r="Q33" s="606"/>
+      <c r="R33" s="606"/>
+      <c r="S33" s="606"/>
+      <c r="T33" s="606"/>
+      <c r="U33" s="606"/>
+      <c r="V33" s="606"/>
+      <c r="W33" s="606"/>
+      <c r="X33" s="607"/>
       <c r="Y33" s="176"/>
     </row>
     <row r="34" spans="1:25" s="152" customFormat="1" ht="21" customHeight="1" thickBot="1">
@@ -20205,18 +20202,18 @@
       <c r="G34" s="101"/>
       <c r="H34" s="101"/>
       <c r="I34" s="101"/>
-      <c r="O34" s="598" t="s">
+      <c r="O34" s="602" t="s">
         <v>170</v>
       </c>
-      <c r="P34" s="599"/>
-      <c r="Q34" s="599"/>
-      <c r="R34" s="599"/>
-      <c r="S34" s="599"/>
-      <c r="T34" s="599"/>
-      <c r="U34" s="599"/>
-      <c r="V34" s="599"/>
-      <c r="W34" s="599"/>
-      <c r="X34" s="600"/>
+      <c r="P34" s="603"/>
+      <c r="Q34" s="603"/>
+      <c r="R34" s="603"/>
+      <c r="S34" s="603"/>
+      <c r="T34" s="603"/>
+      <c r="U34" s="603"/>
+      <c r="V34" s="603"/>
+      <c r="W34" s="603"/>
+      <c r="X34" s="604"/>
       <c r="Y34" s="176"/>
     </row>
     <row r="35" spans="1:25" s="152" customFormat="1" ht="34.5" customHeight="1">
@@ -20231,34 +20228,34 @@
     </row>
     <row r="37" spans="1:25" s="36" customFormat="1" ht="21" customHeight="1">
       <c r="A37" s="184"/>
-      <c r="O37" s="601" t="s">
+      <c r="O37" s="605" t="s">
         <v>174</v>
       </c>
-      <c r="P37" s="602"/>
-      <c r="Q37" s="602"/>
-      <c r="R37" s="602"/>
-      <c r="S37" s="602"/>
-      <c r="T37" s="602"/>
-      <c r="U37" s="602"/>
-      <c r="V37" s="602"/>
-      <c r="W37" s="602"/>
-      <c r="X37" s="603"/>
+      <c r="P37" s="606"/>
+      <c r="Q37" s="606"/>
+      <c r="R37" s="606"/>
+      <c r="S37" s="606"/>
+      <c r="T37" s="606"/>
+      <c r="U37" s="606"/>
+      <c r="V37" s="606"/>
+      <c r="W37" s="606"/>
+      <c r="X37" s="607"/>
       <c r="Y37" s="185"/>
     </row>
     <row r="38" spans="1:25" s="36" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A38" s="184"/>
-      <c r="O38" s="598" t="s">
+      <c r="O38" s="602" t="s">
         <v>175</v>
       </c>
-      <c r="P38" s="599"/>
-      <c r="Q38" s="599"/>
-      <c r="R38" s="599"/>
-      <c r="S38" s="599"/>
-      <c r="T38" s="599"/>
-      <c r="U38" s="599"/>
-      <c r="V38" s="599"/>
-      <c r="W38" s="599"/>
-      <c r="X38" s="600"/>
+      <c r="P38" s="603"/>
+      <c r="Q38" s="603"/>
+      <c r="R38" s="603"/>
+      <c r="S38" s="603"/>
+      <c r="T38" s="603"/>
+      <c r="U38" s="603"/>
+      <c r="V38" s="603"/>
+      <c r="W38" s="603"/>
+      <c r="X38" s="604"/>
       <c r="Y38" s="185"/>
     </row>
     <row r="39" spans="1:25" s="36" customFormat="1" ht="15" customHeight="1">
@@ -20305,31 +20302,31 @@
       <c r="Y40" s="117"/>
     </row>
     <row r="41" spans="1:25" ht="30" customHeight="1">
-      <c r="A41" s="597"/>
-      <c r="B41" s="597"/>
-      <c r="C41" s="597"/>
-      <c r="D41" s="597"/>
-      <c r="E41" s="597"/>
-      <c r="F41" s="597"/>
-      <c r="G41" s="597"/>
-      <c r="H41" s="597"/>
-      <c r="I41" s="597"/>
-      <c r="J41" s="597"/>
-      <c r="K41" s="597"/>
-      <c r="L41" s="597"/>
-      <c r="M41" s="597"/>
-      <c r="N41" s="597"/>
-      <c r="O41" s="597"/>
-      <c r="P41" s="597"/>
-      <c r="Q41" s="597"/>
-      <c r="R41" s="597"/>
-      <c r="S41" s="597"/>
-      <c r="T41" s="597"/>
-      <c r="U41" s="597"/>
-      <c r="V41" s="597"/>
-      <c r="W41" s="597"/>
-      <c r="X41" s="597"/>
-      <c r="Y41" s="597"/>
+      <c r="A41" s="601"/>
+      <c r="B41" s="601"/>
+      <c r="C41" s="601"/>
+      <c r="D41" s="601"/>
+      <c r="E41" s="601"/>
+      <c r="F41" s="601"/>
+      <c r="G41" s="601"/>
+      <c r="H41" s="601"/>
+      <c r="I41" s="601"/>
+      <c r="J41" s="601"/>
+      <c r="K41" s="601"/>
+      <c r="L41" s="601"/>
+      <c r="M41" s="601"/>
+      <c r="N41" s="601"/>
+      <c r="O41" s="601"/>
+      <c r="P41" s="601"/>
+      <c r="Q41" s="601"/>
+      <c r="R41" s="601"/>
+      <c r="S41" s="601"/>
+      <c r="T41" s="601"/>
+      <c r="U41" s="601"/>
+      <c r="V41" s="601"/>
+      <c r="W41" s="601"/>
+      <c r="X41" s="601"/>
+      <c r="Y41" s="601"/>
     </row>
   </sheetData>
   <mergeCells count="31">
@@ -20393,10 +20390,10 @@
       <c r="C1" s="202"/>
     </row>
     <row r="2" spans="2:7" ht="24.95" customHeight="1">
-      <c r="B2" s="649" t="s">
+      <c r="B2" s="653" t="s">
         <v>100</v>
       </c>
-      <c r="C2" s="649"/>
+      <c r="C2" s="653"/>
       <c r="D2" s="203" t="s">
         <v>199</v>
       </c>
@@ -20411,7 +20408,7 @@
       </c>
     </row>
     <row r="3" spans="2:7" ht="24.95" customHeight="1">
-      <c r="B3" s="649" t="s">
+      <c r="B3" s="653" t="s">
         <v>203</v>
       </c>
       <c r="C3" s="203" t="s">
@@ -20426,12 +20423,12 @@
       <c r="F3" s="204">
         <v>900000</v>
       </c>
-      <c r="G3" s="650" t="s">
+      <c r="G3" s="654" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="4" spans="2:7" ht="24.95" customHeight="1">
-      <c r="B4" s="649"/>
+      <c r="B4" s="653"/>
       <c r="C4" s="203" t="s">
         <v>85</v>
       </c>
@@ -20447,7 +20444,7 @@
         <f>F3*12</f>
         <v>10800000</v>
       </c>
-      <c r="G4" s="651"/>
+      <c r="G4" s="655"/>
     </row>
     <row r="5" spans="2:7" ht="24.95" customHeight="1">
       <c r="B5" s="205"/>
@@ -20464,10 +20461,10 @@
       <c r="C7" s="202"/>
     </row>
     <row r="8" spans="2:7" ht="24.95" customHeight="1">
-      <c r="B8" s="649" t="s">
+      <c r="B8" s="653" t="s">
         <v>100</v>
       </c>
-      <c r="C8" s="649"/>
+      <c r="C8" s="653"/>
       <c r="D8" s="203" t="s">
         <v>199</v>
       </c>
@@ -20482,7 +20479,7 @@
       </c>
     </row>
     <row r="9" spans="2:7" ht="24.95" customHeight="1">
-      <c r="B9" s="649" t="s">
+      <c r="B9" s="653" t="s">
         <v>203</v>
       </c>
       <c r="C9" s="203" t="s">
@@ -20497,12 +20494,12 @@
       <c r="F9" s="212">
         <v>900000</v>
       </c>
-      <c r="G9" s="652" t="s">
+      <c r="G9" s="656" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="10" spans="2:7" ht="24.95" customHeight="1" thickBot="1">
-      <c r="B10" s="649"/>
+      <c r="B10" s="653"/>
       <c r="C10" s="203" t="s">
         <v>85</v>
       </c>
@@ -20518,7 +20515,7 @@
         <f>F9*12</f>
         <v>10800000</v>
       </c>
-      <c r="G10" s="653"/>
+      <c r="G10" s="657"/>
     </row>
     <row r="12" spans="2:7" ht="24.95" customHeight="1" thickBot="1">
       <c r="B12" s="202" t="s">
@@ -20527,10 +20524,10 @@
       <c r="C12" s="202"/>
     </row>
     <row r="13" spans="2:7" ht="24.95" customHeight="1">
-      <c r="B13" s="649" t="s">
+      <c r="B13" s="653" t="s">
         <v>100</v>
       </c>
-      <c r="C13" s="649"/>
+      <c r="C13" s="653"/>
       <c r="D13" s="203" t="s">
         <v>199</v>
       </c>
@@ -20545,7 +20542,7 @@
       </c>
     </row>
     <row r="14" spans="2:7" ht="24.95" customHeight="1">
-      <c r="B14" s="649" t="s">
+      <c r="B14" s="653" t="s">
         <v>203</v>
       </c>
       <c r="C14" s="203" t="s">
@@ -20560,12 +20557,12 @@
       <c r="F14" s="212">
         <v>750000</v>
       </c>
-      <c r="G14" s="652" t="s">
+      <c r="G14" s="656" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="15" spans="2:7" ht="24.95" customHeight="1" thickBot="1">
-      <c r="B15" s="649"/>
+      <c r="B15" s="653"/>
       <c r="C15" s="203" t="s">
         <v>85</v>
       </c>
@@ -20581,7 +20578,7 @@
         <f>F14*12</f>
         <v>9000000</v>
       </c>
-      <c r="G15" s="653"/>
+      <c r="G15" s="657"/>
     </row>
     <row r="17" spans="2:7" ht="24.95" customHeight="1" thickBot="1">
       <c r="B17" s="202" t="s">
@@ -20590,10 +20587,10 @@
       <c r="C17" s="202"/>
     </row>
     <row r="18" spans="2:7" ht="24.95" customHeight="1">
-      <c r="B18" s="649" t="s">
+      <c r="B18" s="653" t="s">
         <v>100</v>
       </c>
-      <c r="C18" s="649"/>
+      <c r="C18" s="653"/>
       <c r="D18" s="203" t="s">
         <v>199</v>
       </c>
@@ -20608,7 +20605,7 @@
       </c>
     </row>
     <row r="19" spans="2:7" ht="24.95" customHeight="1">
-      <c r="B19" s="649" t="s">
+      <c r="B19" s="653" t="s">
         <v>203</v>
       </c>
       <c r="C19" s="203" t="s">
@@ -20623,12 +20620,12 @@
       <c r="F19" s="212">
         <v>650000</v>
       </c>
-      <c r="G19" s="652" t="s">
+      <c r="G19" s="656" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="20" spans="2:7" ht="24.95" customHeight="1" thickBot="1">
-      <c r="B20" s="649"/>
+      <c r="B20" s="653"/>
       <c r="C20" s="203" t="s">
         <v>85</v>
       </c>
@@ -20644,7 +20641,7 @@
         <f>F19*12</f>
         <v>7800000</v>
       </c>
-      <c r="G20" s="653"/>
+      <c r="G20" s="657"/>
     </row>
   </sheetData>
   <mergeCells count="12">
